--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DFE5CC-0A1F-4D82-94EE-23852C065E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB4F6D4-0E2E-4E22-9E60-B60A43DE5748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="840" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="294">
   <si>
     <t>Component list</t>
   </si>
@@ -242,15 +242,9 @@
     <t>Clamshell 22 Double-sided contacts/up and down connection Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
   </si>
   <si>
-    <t>2A Surface Mount Square Pins 2mm 4mm -40℃~+105℃ 1 8 2mm 1x8P SMD,P=2mm Pin Headers ROHS</t>
-  </si>
-  <si>
     <t>CONN FPC/FFC 12POS .5MM</t>
   </si>
   <si>
-    <t>4 POS 2.54mm Pin Header Male single row Right Angle SMD</t>
-  </si>
-  <si>
     <t>FIXED IND 2.2UH 1.5A 160MOHM SMD</t>
   </si>
   <si>
@@ -464,9 +458,6 @@
     <t>GJM1555C1HR80WB01D</t>
   </si>
   <si>
-    <t>1220-1108G0Z090CR02</t>
-  </si>
-  <si>
     <t>MGFL2012F100MT-LF</t>
   </si>
   <si>
@@ -554,12 +545,6 @@
     <t>XFCN</t>
   </si>
   <si>
-    <t>Wcon</t>
-  </si>
-  <si>
-    <t>RTLECS</t>
-  </si>
-  <si>
     <t>TDK</t>
   </si>
   <si>
@@ -794,9 +779,6 @@
     <t>C285870</t>
   </si>
   <si>
-    <t>C920922</t>
-  </si>
-  <si>
     <t>C521237</t>
   </si>
   <si>
@@ -893,21 +875,12 @@
     <t>Alibaba</t>
   </si>
   <si>
-    <t xml:space="preserve">Need Quotation from custom Supplier </t>
-  </si>
-  <si>
-    <t>1220-1104G0Z090CR02</t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
     <t>------</t>
   </si>
   <si>
-    <t>C920925</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Component Cost </t>
   </si>
   <si>
@@ -918,6 +891,27 @@
   </si>
   <si>
     <t>Custom Supplier Quotation</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 8POS 2.54MM</t>
+  </si>
+  <si>
+    <t>61300811121</t>
+  </si>
+  <si>
+    <t>Wurth Electronics</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 4POS 2.54MM</t>
+  </si>
+  <si>
+    <t>61300411121</t>
+  </si>
+  <si>
+    <t>C2935914</t>
+  </si>
+  <si>
+    <t>C2935910</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1692,6 +1686,30 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1717,27 +1735,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2108,8 +2105,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="88"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2125,15 +2122,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="84"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="92"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2157,7 +2154,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="81"/>
+      <c r="R3" s="89"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2181,7 +2178,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="82"/>
+      <c r="R4" s="90"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2205,7 +2202,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="82"/>
+      <c r="R5" s="90"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2225,7 +2222,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="82"/>
+      <c r="R6" s="90"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2245,7 +2242,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="82"/>
+      <c r="R7" s="90"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2265,11 +2262,11 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="82"/>
+      <c r="R8" s="90"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="83" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="32" t="s">
@@ -2279,51 +2276,51 @@
         <v>57</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G9" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="K9" s="84" t="s">
+        <v>223</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="M9" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="H9" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="N9" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="J9" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="K9" s="92" t="s">
-        <v>228</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="M9" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="N9" s="32" t="s">
-        <v>231</v>
-      </c>
       <c r="O9" s="32" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="P9" s="32" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="Q9" s="32" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="93">
+      <c r="B10" s="85">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -2334,22 +2331,22 @@
         <v>58</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G10" s="65" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I10" s="60" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J10" s="51" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K10" s="54">
         <v>3</v>
@@ -2362,7 +2359,7 @@
         <v>20</v>
       </c>
       <c r="N10" s="76" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O10" s="42">
         <v>7.2800000000000004E-2</v>
@@ -2376,7 +2373,7 @@
     </row>
     <row r="11" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="94">
+      <c r="B11" s="86">
         <f t="shared" ref="B11:B55" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
@@ -2387,22 +2384,22 @@
         <v>59</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G11" s="61" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I11" s="61" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K11" s="55">
         <v>24</v>
@@ -2415,7 +2412,7 @@
         <v>150</v>
       </c>
       <c r="N11" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O11" s="35">
         <v>6.7000000000000002E-3</v>
@@ -2429,7 +2426,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="94">
+      <c r="B12" s="86">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
@@ -2440,22 +2437,22 @@
         <v>60</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G12" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I12" s="62" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K12" s="56">
         <v>1</v>
@@ -2468,7 +2465,7 @@
         <v>20</v>
       </c>
       <c r="N12" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O12" s="34">
         <v>1.3599999999999999E-2</v>
@@ -2482,7 +2479,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="94">
+      <c r="B13" s="86">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2493,22 +2490,22 @@
         <v>61</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G13" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K13" s="55">
         <v>8</v>
@@ -2521,7 +2518,7 @@
         <v>100</v>
       </c>
       <c r="N13" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O13" s="35">
         <v>1.4E-3</v>
@@ -2535,7 +2532,7 @@
     </row>
     <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="94">
+      <c r="B14" s="86">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
@@ -2546,22 +2543,22 @@
         <v>62</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G14" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I14" s="62" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="K14" s="56">
         <v>3</v>
@@ -2574,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="N14" s="79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O14" s="34">
         <v>1.7600000000000001E-2</v>
@@ -2588,7 +2585,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="94">
+      <c r="B15" s="86">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2599,22 +2596,22 @@
         <v>63</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G15" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I15" s="61" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K15" s="55">
         <v>8</v>
@@ -2627,7 +2624,7 @@
         <v>50</v>
       </c>
       <c r="N15" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O15" s="35">
         <v>6.4000000000000003E-3</v>
@@ -2641,7 +2638,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="94">
+      <c r="B16" s="86">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
@@ -2652,22 +2649,22 @@
         <v>64</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G16" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H16" s="53" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I16" s="62" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="K16" s="56">
         <v>1</v>
@@ -2680,7 +2677,7 @@
         <v>10</v>
       </c>
       <c r="N16" s="79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O16" s="37">
         <v>4.8899999999999999E-2</v>
@@ -2694,7 +2691,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="94">
+      <c r="B17" s="86">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2702,25 +2699,25 @@
         <v>18</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I17" s="61" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="J17" s="52" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K17" s="55">
         <v>2</v>
@@ -2733,7 +2730,7 @@
         <v>100</v>
       </c>
       <c r="N17" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O17" s="35">
         <v>1.6000000000000001E-3</v>
@@ -2747,7 +2744,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="94">
+      <c r="B18" s="86">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
@@ -2758,22 +2755,22 @@
         <v>65</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G18" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I18" s="62" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J18" s="53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K18" s="56">
         <v>1</v>
@@ -2786,7 +2783,7 @@
         <v>20</v>
       </c>
       <c r="N18" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O18" s="34">
         <v>2.93E-2</v>
@@ -2800,7 +2797,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="94">
+      <c r="B19" s="86">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2811,22 +2808,22 @@
         <v>66</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G19" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I19" s="61" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J19" s="58" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K19" s="55">
         <v>1</v>
@@ -2839,7 +2836,7 @@
         <v>10</v>
       </c>
       <c r="N19" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O19" s="35">
         <v>8.8900000000000007E-2</v>
@@ -2853,7 +2850,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="94">
+      <c r="B20" s="86">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
@@ -2864,22 +2861,22 @@
         <v>67</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G20" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I20" s="62" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K20" s="56">
         <v>1</v>
@@ -2892,7 +2889,7 @@
         <v>6</v>
       </c>
       <c r="N20" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O20" s="34">
         <v>2.3371</v>
@@ -2906,7 +2903,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="94">
+      <c r="B21" s="86">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2917,22 +2914,22 @@
         <v>68</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G21" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I21" s="61" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J21" s="58" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K21" s="55">
         <v>1</v>
@@ -2945,7 +2942,7 @@
         <v>20</v>
       </c>
       <c r="N21" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O21" s="35">
         <v>4.8399999999999999E-2</v>
@@ -2959,7 +2956,7 @@
     </row>
     <row r="22" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="94">
+      <c r="B22" s="86">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
@@ -2970,22 +2967,22 @@
         <v>69</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G22" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I22" s="62" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K22" s="56">
         <v>1</v>
@@ -2998,7 +2995,7 @@
         <v>6</v>
       </c>
       <c r="N22" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O22" s="34">
         <v>0.18659999999999999</v>
@@ -3010,35 +3007,35 @@
       <c r="Q22" s="34"/>
       <c r="R22" s="34"/>
     </row>
-    <row r="23" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="94">
+      <c r="B23" s="86">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="61" t="s">
-        <v>70</v>
+      <c r="D23" s="52" t="s">
+        <v>287</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="52" t="s">
-        <v>144</v>
+        <v>108</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>288</v>
       </c>
       <c r="G23" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>174</v>
+        <v>289</v>
       </c>
       <c r="I23" s="61" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="J23" s="58" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K23" s="55">
         <v>1</v>
@@ -3048,24 +3045,24 @@
         <v>5</v>
       </c>
       <c r="M23" s="31">
-        <v>6</v>
-      </c>
-      <c r="N23" s="77" t="s">
-        <v>233</v>
+        <v>10</v>
+      </c>
+      <c r="N23" s="88" t="s">
+        <v>228</v>
       </c>
       <c r="O23" s="35">
-        <v>0.3054</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="P23" s="35">
         <f t="shared" si="2"/>
-        <v>1.8324</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="Q23" s="35"/>
       <c r="R23" s="35"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="94">
+      <c r="B24" s="86">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
@@ -3073,25 +3070,25 @@
         <v>25</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="H24" s="53" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K24" s="56">
         <v>1</v>
@@ -3104,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="N24" s="79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O24" s="37">
         <v>0.1893</v>
@@ -3116,35 +3113,35 @@
       <c r="Q24" s="34"/>
       <c r="R24" s="34"/>
     </row>
-    <row r="25" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="94">
+      <c r="B25" s="86">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="61" t="s">
-        <v>72</v>
+      <c r="D25" s="63" t="s">
+        <v>290</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="52" t="s">
-        <v>288</v>
+        <v>110</v>
+      </c>
+      <c r="F25" s="58" t="s">
+        <v>291</v>
       </c>
       <c r="G25" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="H25" s="52" t="s">
         <v>289</v>
       </c>
-      <c r="H25" s="52" t="s">
-        <v>175</v>
-      </c>
       <c r="I25" s="61" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J25" s="58" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K25" s="55">
         <v>1</v>
@@ -3154,24 +3151,24 @@
         <v>5</v>
       </c>
       <c r="M25" s="31">
-        <v>6</v>
-      </c>
-      <c r="N25" s="77" t="s">
-        <v>233</v>
+        <v>20</v>
+      </c>
+      <c r="N25" s="88" t="s">
+        <v>228</v>
       </c>
       <c r="O25" s="35">
-        <v>0.21249999999999999</v>
+        <v>2.29E-2</v>
       </c>
       <c r="P25" s="35">
         <f t="shared" si="2"/>
-        <v>1.2749999999999999</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="Q25" s="35"/>
       <c r="R25" s="35"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="94">
+      <c r="B26" s="86">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
@@ -3179,25 +3176,25 @@
         <v>27</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F26" s="53" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G26" s="66" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="H26" s="53" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I26" s="66" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="J26" s="53" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K26" s="56">
         <v>1</v>
@@ -3210,21 +3207,23 @@
         <v>7</v>
       </c>
       <c r="N26" s="78" t="s">
-        <v>286</v>
-      </c>
-      <c r="O26" s="34"/>
+        <v>280</v>
+      </c>
+      <c r="O26" s="34">
+        <v>0.25</v>
+      </c>
       <c r="P26" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" s="72" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R26" s="34"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="94">
+      <c r="B27" s="86">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3232,25 +3231,25 @@
         <v>28</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G27" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I27" s="61" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J27" s="52" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K27" s="55">
         <v>1</v>
@@ -3263,7 +3262,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O27" s="35">
         <v>0.1575</v>
@@ -3277,7 +3276,7 @@
     </row>
     <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="94">
+      <c r="B28" s="86">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
@@ -3285,25 +3284,25 @@
         <v>29</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G28" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H28" s="53" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I28" s="62" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="J28" s="53" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K28" s="56">
         <v>1</v>
@@ -3316,7 +3315,7 @@
         <v>10</v>
       </c>
       <c r="N28" s="79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O28" s="37">
         <v>4.4400000000000002E-2</v>
@@ -3330,7 +3329,7 @@
     </row>
     <row r="29" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="94">
+      <c r="B29" s="86">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3338,25 +3337,25 @@
         <v>30</v>
       </c>
       <c r="D29" s="61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G29" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H29" s="52" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I29" s="61" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="J29" s="52" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K29" s="55">
         <v>1</v>
@@ -3369,7 +3368,7 @@
         <v>10</v>
       </c>
       <c r="N29" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O29" s="35">
         <v>5.7299999999999997E-2</v>
@@ -3383,7 +3382,7 @@
     </row>
     <row r="30" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="94">
+      <c r="B30" s="86">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
@@ -3391,25 +3390,25 @@
         <v>31</v>
       </c>
       <c r="D30" s="62" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G30" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H30" s="53" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I30" s="62" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K30" s="56">
         <v>1</v>
@@ -3422,7 +3421,7 @@
         <v>10</v>
       </c>
       <c r="N30" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O30" s="34">
         <v>6.4600000000000005E-2</v>
@@ -3436,7 +3435,7 @@
     </row>
     <row r="31" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="94">
+      <c r="B31" s="86">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3444,25 +3443,25 @@
         <v>32</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G31" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H31" s="52" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I31" s="61" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J31" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K31" s="55">
         <v>1</v>
@@ -3475,7 +3474,7 @@
         <v>50</v>
       </c>
       <c r="N31" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O31" s="35">
         <v>8.6E-3</v>
@@ -3489,7 +3488,7 @@
     </row>
     <row r="32" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="94">
+      <c r="B32" s="86">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
@@ -3497,23 +3496,23 @@
         <v>33</v>
       </c>
       <c r="D32" s="62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G32" s="62"/>
       <c r="H32" s="53" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I32" s="62" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K32" s="56">
         <v>1</v>
@@ -3526,7 +3525,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O32" s="37">
         <v>9.4299999999999995E-2</v>
@@ -3540,7 +3539,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="94">
+      <c r="B33" s="86">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3548,25 +3547,25 @@
         <v>34</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F33" s="68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G33" s="61" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H33" s="52" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I33" s="61" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J33" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K33" s="55">
         <v>2</v>
@@ -3579,7 +3578,7 @@
         <v>50</v>
       </c>
       <c r="N33" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O33" s="35">
         <v>1.7500000000000002E-2</v>
@@ -3593,7 +3592,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="94">
+      <c r="B34" s="86">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
@@ -3601,25 +3600,25 @@
         <v>35</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G34" s="62" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H34" s="53" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I34" s="62" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K34" s="56">
         <v>1</v>
@@ -3632,7 +3631,7 @@
         <v>10</v>
       </c>
       <c r="N34" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O34" s="34">
         <v>5.2400000000000002E-2</v>
@@ -3646,7 +3645,7 @@
     </row>
     <row r="35" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="94">
+      <c r="B35" s="86">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -3654,25 +3653,25 @@
         <v>36</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E35" s="52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G35" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H35" s="52" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J35" s="52" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K35" s="55">
         <v>1</v>
@@ -3685,7 +3684,7 @@
         <v>50</v>
       </c>
       <c r="N35" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O35" s="35">
         <v>1.4200000000000001E-2</v>
@@ -3699,7 +3698,7 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="94">
+      <c r="B36" s="86">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
@@ -3707,25 +3706,25 @@
         <v>37</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F36" s="53" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G36" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H36" s="53" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I36" s="62" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="J36" s="53" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K36" s="56">
         <v>4</v>
@@ -3738,7 +3737,7 @@
         <v>100</v>
       </c>
       <c r="N36" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O36" s="34">
         <v>5.9999999999999995E-4</v>
@@ -3752,7 +3751,7 @@
     </row>
     <row r="37" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="94">
+      <c r="B37" s="86">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -3760,25 +3759,25 @@
         <v>38</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G37" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I37" s="61" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J37" s="52" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K37" s="55">
         <v>10</v>
@@ -3791,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O37" s="35">
         <v>6.9999999999999999E-4</v>
@@ -3805,7 +3804,7 @@
     </row>
     <row r="38" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="94">
+      <c r="B38" s="86">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
@@ -3813,25 +3812,25 @@
         <v>39</v>
       </c>
       <c r="D38" s="62" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F38" s="53" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G38" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H38" s="53" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I38" s="62" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J38" s="53" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K38" s="56">
         <v>1</v>
@@ -3844,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="N38" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O38" s="34">
         <v>5.0000000000000001E-4</v>
@@ -3858,7 +3857,7 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="94">
+      <c r="B39" s="86">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -3866,25 +3865,25 @@
         <v>40</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E39" s="52" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F39" s="68" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G39" s="61" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H39" s="52" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I39" s="61" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J39" s="52" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K39" s="55">
         <v>7</v>
@@ -3897,7 +3896,7 @@
         <v>100</v>
       </c>
       <c r="N39" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O39" s="35">
         <v>6.9999999999999999E-4</v>
@@ -3911,7 +3910,7 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="94">
+      <c r="B40" s="86">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
@@ -3919,25 +3918,25 @@
         <v>41</v>
       </c>
       <c r="D40" s="62" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G40" s="62" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H40" s="53" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I40" s="62" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="J40" s="53" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="K40" s="56">
         <v>2</v>
@@ -3950,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O40" s="34">
         <v>8.0000000000000004E-4</v>
@@ -3964,7 +3963,7 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="94">
+      <c r="B41" s="86">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -3972,25 +3971,25 @@
         <v>42</v>
       </c>
       <c r="D41" s="61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E41" s="52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F41" s="68" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G41" s="61" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="H41" s="52" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I41" s="61" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="J41" s="52" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K41" s="55">
         <v>2</v>
@@ -4003,7 +4002,7 @@
         <v>100</v>
       </c>
       <c r="N41" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O41" s="35">
         <v>3.5999999999999999E-3</v>
@@ -4017,7 +4016,7 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="94">
+      <c r="B42" s="86">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
@@ -4025,25 +4024,25 @@
         <v>43</v>
       </c>
       <c r="D42" s="62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F42" s="53" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G42" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H42" s="53" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I42" s="62" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J42" s="53" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K42" s="56">
         <v>1</v>
@@ -4056,7 +4055,7 @@
         <v>50</v>
       </c>
       <c r="N42" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O42" s="34">
         <v>6.9999999999999999E-4</v>
@@ -4070,7 +4069,7 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="94">
+      <c r="B43" s="86">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -4078,23 +4077,23 @@
         <v>44</v>
       </c>
       <c r="D43" s="61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F43" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G43" s="63"/>
       <c r="H43" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I43" s="63" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J43" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K43" s="55">
         <v>3</v>
@@ -4104,23 +4103,23 @@
         <v>15</v>
       </c>
       <c r="M43" s="70" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="N43" s="70" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="O43" s="70" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P43" s="70" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Q43" s="70"/>
       <c r="R43" s="70"/>
     </row>
     <row r="44" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="94">
+      <c r="B44" s="86">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
@@ -4128,25 +4127,25 @@
         <v>45</v>
       </c>
       <c r="D44" s="62" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F44" s="53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G44" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H44" s="53" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I44" s="62" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K44" s="56">
         <v>1</v>
@@ -4159,7 +4158,7 @@
         <v>10</v>
       </c>
       <c r="N44" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O44" s="34">
         <v>5.91E-2</v>
@@ -4173,7 +4172,7 @@
     </row>
     <row r="45" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="94">
+      <c r="B45" s="86">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -4181,25 +4180,25 @@
         <v>46</v>
       </c>
       <c r="D45" s="61" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F45" s="52" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H45" s="52" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I45" s="63" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J45" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K45" s="55">
         <v>1</v>
@@ -4212,21 +4211,23 @@
         <v>6</v>
       </c>
       <c r="N45" s="77" t="s">
-        <v>286</v>
-      </c>
-      <c r="O45" s="35"/>
+        <v>280</v>
+      </c>
+      <c r="O45" s="35">
+        <v>3.2</v>
+      </c>
       <c r="P45" s="35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19.200000000000003</v>
       </c>
       <c r="Q45" s="71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R45" s="35"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="94">
+      <c r="B46" s="86">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
@@ -4234,25 +4235,25 @@
         <v>47</v>
       </c>
       <c r="D46" s="62" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F46" s="53" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G46" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H46" s="53" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I46" s="62" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K46" s="56">
         <v>1</v>
@@ -4265,7 +4266,7 @@
         <v>6</v>
       </c>
       <c r="N46" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O46" s="34">
         <v>0.47070000000000001</v>
@@ -4279,7 +4280,7 @@
     </row>
     <row r="47" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="94">
+      <c r="B47" s="86">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -4287,25 +4288,25 @@
         <v>48</v>
       </c>
       <c r="D47" s="61" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G47" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H47" s="52" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I47" s="63" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J47" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K47" s="55">
         <v>1</v>
@@ -4318,7 +4319,7 @@
         <v>6</v>
       </c>
       <c r="N47" s="77" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O47" s="35">
         <v>1.8</v>
@@ -4328,13 +4329,13 @@
         <v>10.8</v>
       </c>
       <c r="Q47" s="71" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="R47" s="35"/>
     </row>
     <row r="48" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="94">
+      <c r="B48" s="86">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
@@ -4342,25 +4343,25 @@
         <v>49</v>
       </c>
       <c r="D48" s="62" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F48" s="53" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G48" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H48" s="53" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I48" s="62" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K48" s="56">
         <v>1</v>
@@ -4373,7 +4374,7 @@
         <v>6</v>
       </c>
       <c r="N48" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O48" s="34">
         <v>13.1333</v>
@@ -4387,7 +4388,7 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="94">
+      <c r="B49" s="86">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -4395,25 +4396,25 @@
         <v>50</v>
       </c>
       <c r="D49" s="61" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E49" s="52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G49" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H49" s="52" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I49" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J49" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K49" s="55">
         <v>1</v>
@@ -4426,21 +4427,23 @@
         <v>6</v>
       </c>
       <c r="N49" s="77" t="s">
-        <v>286</v>
-      </c>
-      <c r="O49" s="35"/>
+        <v>280</v>
+      </c>
+      <c r="O49" s="35">
+        <v>11.45</v>
+      </c>
       <c r="P49" s="35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>68.699999999999989</v>
       </c>
       <c r="Q49" s="71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R49" s="35"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="94">
+      <c r="B50" s="86">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
@@ -4448,25 +4451,25 @@
         <v>51</v>
       </c>
       <c r="D50" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F50" s="53" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G50" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H50" s="53" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I50" s="62" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="J50" s="59" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K50" s="56">
         <v>1</v>
@@ -4479,7 +4482,7 @@
         <v>6</v>
       </c>
       <c r="N50" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O50" s="34">
         <v>2.851</v>
@@ -4493,7 +4496,7 @@
     </row>
     <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="94">
+      <c r="B51" s="86">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -4501,25 +4504,25 @@
         <v>52</v>
       </c>
       <c r="D51" s="61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E51" s="52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H51" s="52" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I51" s="61" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J51" s="58" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K51" s="55">
         <v>1</v>
@@ -4532,7 +4535,7 @@
         <v>6</v>
       </c>
       <c r="N51" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O51" s="35">
         <v>4.3278999999999996</v>
@@ -4546,7 +4549,7 @@
     </row>
     <row r="52" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="94">
+      <c r="B52" s="86">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
@@ -4554,25 +4557,25 @@
         <v>53</v>
       </c>
       <c r="D52" s="62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F52" s="53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G52" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H52" s="53" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I52" s="62" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J52" s="59" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K52" s="56">
         <v>1</v>
@@ -4585,7 +4588,7 @@
         <v>10</v>
       </c>
       <c r="N52" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O52" s="34">
         <v>2.0400000000000001E-2</v>
@@ -4599,7 +4602,7 @@
     </row>
     <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="94">
+      <c r="B53" s="86">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -4607,25 +4610,25 @@
         <v>54</v>
       </c>
       <c r="D53" s="61" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F53" s="52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G53" s="63" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H53" s="52" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I53" s="61" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J53" s="52" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="K53" s="55">
         <v>2</v>
@@ -4638,7 +4641,7 @@
         <v>11</v>
       </c>
       <c r="N53" s="77" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O53" s="35">
         <v>0.27989999999999998</v>
@@ -4652,7 +4655,7 @@
     </row>
     <row r="54" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="94">
+      <c r="B54" s="86">
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
@@ -4660,25 +4663,25 @@
         <v>55</v>
       </c>
       <c r="D54" s="62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F54" s="53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G54" s="66" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H54" s="53" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I54" s="62" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J54" s="53" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K54" s="56">
         <v>1</v>
@@ -4691,7 +4694,7 @@
         <v>10</v>
       </c>
       <c r="N54" s="78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O54" s="34">
         <v>9.8500000000000004E-2</v>
@@ -4705,7 +4708,7 @@
     </row>
     <row r="55" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="B55" s="95">
+      <c r="B55" s="87">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -4713,25 +4716,25 @@
         <v>56</v>
       </c>
       <c r="D55" s="64" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E55" s="75" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F55" s="75" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G55" s="67" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H55" s="75" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I55" s="64" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J55" s="75" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K55" s="57">
         <v>1</v>
@@ -4744,7 +4747,7 @@
         <v>10</v>
       </c>
       <c r="N55" s="80" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O55" s="46">
         <v>0.13439999999999999</v>
@@ -4771,14 +4774,14 @@
       <c r="J56" s="73"/>
       <c r="K56" s="73"/>
       <c r="L56" s="73"/>
-      <c r="M56" s="85" t="s">
-        <v>292</v>
-      </c>
-      <c r="N56" s="86"/>
-      <c r="O56" s="86"/>
-      <c r="P56" s="90">
+      <c r="M56" s="93" t="s">
+        <v>283</v>
+      </c>
+      <c r="N56" s="94"/>
+      <c r="O56" s="94"/>
+      <c r="P56" s="82">
         <f>SUM(P10:P55)</f>
-        <v>175.22320000000002</v>
+        <v>262.65479999999997</v>
       </c>
       <c r="Q56" s="73"/>
       <c r="R56" s="74"/>
@@ -4798,14 +4801,14 @@
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
       <c r="L57" s="43"/>
-      <c r="M57" s="85" t="s">
-        <v>293</v>
-      </c>
-      <c r="N57" s="86"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="89">
+      <c r="M57" s="93" t="s">
+        <v>284</v>
+      </c>
+      <c r="N57" s="94"/>
+      <c r="O57" s="94"/>
+      <c r="P57" s="81">
         <f>P56/5</f>
-        <v>35.044640000000001</v>
+        <v>52.530959999999993</v>
       </c>
       <c r="Q57" s="43"/>
       <c r="R57" s="44"/>
@@ -4837,33 +4840,33 @@
     <hyperlink ref="N28" r:id="rId16" xr:uid="{E0EBA58F-E359-4BCB-A2C9-9C49D150A629}"/>
     <hyperlink ref="N29" r:id="rId17" xr:uid="{30630BC0-7DB5-4073-8F22-E28F5B42FCE1}"/>
     <hyperlink ref="N32" r:id="rId18" xr:uid="{D7F6D37C-1F7B-418B-9244-5EC422B2C736}"/>
-    <hyperlink ref="N23" r:id="rId19" xr:uid="{E0ED9725-D02A-4442-A6F9-3CFC551F883D}"/>
-    <hyperlink ref="N30" r:id="rId20" xr:uid="{7EC7E3F1-93CD-45A5-BAEC-2E96006DD4BC}"/>
-    <hyperlink ref="N31" r:id="rId21" xr:uid="{DAFC4B5E-88AC-4044-8DE5-E6B95F9FA94C}"/>
-    <hyperlink ref="N33" r:id="rId22" xr:uid="{FC25DD16-B062-4971-87F3-FBBA153342C7}"/>
-    <hyperlink ref="N34" r:id="rId23" xr:uid="{BA75FE37-D1AE-4A06-A7D6-2FC24E19A57B}"/>
-    <hyperlink ref="N35" r:id="rId24" xr:uid="{98223D7D-7BBA-4B3D-BFE2-9CB1E02D92C6}"/>
-    <hyperlink ref="N37" r:id="rId25" xr:uid="{F2FCE814-68EB-42CA-B801-47EACCC9D840}"/>
-    <hyperlink ref="N38" r:id="rId26" xr:uid="{B8B83BF6-E82D-4A6D-9C89-2F85CAB04646}"/>
-    <hyperlink ref="N42" r:id="rId27" xr:uid="{377F7D05-CD56-46CE-86C7-8359A58D6174}"/>
-    <hyperlink ref="N39" r:id="rId28" xr:uid="{5BC7FB0B-A7A9-4A4F-B0AF-D93D90BD0257}"/>
-    <hyperlink ref="N40" r:id="rId29" xr:uid="{42342919-596A-4C59-8816-01D385B759CB}"/>
-    <hyperlink ref="N41" r:id="rId30" xr:uid="{5D8F6C78-4114-4B09-9296-33D8E0033965}"/>
-    <hyperlink ref="N44" r:id="rId31" xr:uid="{30A94DA1-5BD4-4155-A48B-F08C168CF099}"/>
-    <hyperlink ref="N46" r:id="rId32" xr:uid="{C3F3FC15-3DA9-4B1A-84AC-5A582D205C55}"/>
-    <hyperlink ref="N48" r:id="rId33" xr:uid="{3A097DB9-C3B3-436E-8B87-273AE27C3FB3}"/>
-    <hyperlink ref="N50" r:id="rId34" xr:uid="{0763754B-803A-440F-9046-E7656CF9DB82}"/>
-    <hyperlink ref="N51" r:id="rId35" xr:uid="{4C3FCDA1-65D2-4395-9426-3E1F29BD784A}"/>
-    <hyperlink ref="N52" r:id="rId36" xr:uid="{A4B71E3E-7A98-4CCB-A3C2-8B949A858D06}"/>
-    <hyperlink ref="N53" r:id="rId37" xr:uid="{8DCBF280-B1E4-481C-8762-45E69BB689C9}"/>
-    <hyperlink ref="N54" r:id="rId38" xr:uid="{9D7C6330-6521-4E77-B082-7293A2D402F7}"/>
-    <hyperlink ref="N55" r:id="rId39" xr:uid="{60E4F958-BD03-4950-AA1A-E5483E7B8267}"/>
-    <hyperlink ref="N36" r:id="rId40" xr:uid="{019A488B-4FF7-4C4E-B4AC-B360044B8376}"/>
-    <hyperlink ref="N45" r:id="rId41" xr:uid="{422359C3-822C-4FAA-8878-23A1A61D0F74}"/>
-    <hyperlink ref="N47" r:id="rId42" xr:uid="{1814BF9F-58FE-400D-907F-EAC26C6361E4}"/>
-    <hyperlink ref="N49" r:id="rId43" xr:uid="{1CD03380-9BD7-47D9-B053-5A646F2458CF}"/>
-    <hyperlink ref="N25" r:id="rId44" xr:uid="{C3342E82-DFB2-4931-8A30-5876E10BAB15}"/>
-    <hyperlink ref="N26" r:id="rId45" xr:uid="{3DEFF66E-912E-4F2F-97AB-FACD57B0039F}"/>
+    <hyperlink ref="N30" r:id="rId19" xr:uid="{7EC7E3F1-93CD-45A5-BAEC-2E96006DD4BC}"/>
+    <hyperlink ref="N31" r:id="rId20" xr:uid="{DAFC4B5E-88AC-4044-8DE5-E6B95F9FA94C}"/>
+    <hyperlink ref="N33" r:id="rId21" xr:uid="{FC25DD16-B062-4971-87F3-FBBA153342C7}"/>
+    <hyperlink ref="N34" r:id="rId22" xr:uid="{BA75FE37-D1AE-4A06-A7D6-2FC24E19A57B}"/>
+    <hyperlink ref="N35" r:id="rId23" xr:uid="{98223D7D-7BBA-4B3D-BFE2-9CB1E02D92C6}"/>
+    <hyperlink ref="N37" r:id="rId24" xr:uid="{F2FCE814-68EB-42CA-B801-47EACCC9D840}"/>
+    <hyperlink ref="N38" r:id="rId25" xr:uid="{B8B83BF6-E82D-4A6D-9C89-2F85CAB04646}"/>
+    <hyperlink ref="N42" r:id="rId26" xr:uid="{377F7D05-CD56-46CE-86C7-8359A58D6174}"/>
+    <hyperlink ref="N39" r:id="rId27" xr:uid="{5BC7FB0B-A7A9-4A4F-B0AF-D93D90BD0257}"/>
+    <hyperlink ref="N40" r:id="rId28" xr:uid="{42342919-596A-4C59-8816-01D385B759CB}"/>
+    <hyperlink ref="N41" r:id="rId29" xr:uid="{5D8F6C78-4114-4B09-9296-33D8E0033965}"/>
+    <hyperlink ref="N44" r:id="rId30" xr:uid="{30A94DA1-5BD4-4155-A48B-F08C168CF099}"/>
+    <hyperlink ref="N46" r:id="rId31" xr:uid="{C3F3FC15-3DA9-4B1A-84AC-5A582D205C55}"/>
+    <hyperlink ref="N48" r:id="rId32" xr:uid="{3A097DB9-C3B3-436E-8B87-273AE27C3FB3}"/>
+    <hyperlink ref="N50" r:id="rId33" xr:uid="{0763754B-803A-440F-9046-E7656CF9DB82}"/>
+    <hyperlink ref="N51" r:id="rId34" xr:uid="{4C3FCDA1-65D2-4395-9426-3E1F29BD784A}"/>
+    <hyperlink ref="N52" r:id="rId35" xr:uid="{A4B71E3E-7A98-4CCB-A3C2-8B949A858D06}"/>
+    <hyperlink ref="N53" r:id="rId36" xr:uid="{8DCBF280-B1E4-481C-8762-45E69BB689C9}"/>
+    <hyperlink ref="N54" r:id="rId37" xr:uid="{9D7C6330-6521-4E77-B082-7293A2D402F7}"/>
+    <hyperlink ref="N55" r:id="rId38" xr:uid="{60E4F958-BD03-4950-AA1A-E5483E7B8267}"/>
+    <hyperlink ref="N36" r:id="rId39" xr:uid="{019A488B-4FF7-4C4E-B4AC-B360044B8376}"/>
+    <hyperlink ref="N45" r:id="rId40" xr:uid="{422359C3-822C-4FAA-8878-23A1A61D0F74}"/>
+    <hyperlink ref="N47" r:id="rId41" xr:uid="{1814BF9F-58FE-400D-907F-EAC26C6361E4}"/>
+    <hyperlink ref="N49" r:id="rId42" xr:uid="{1CD03380-9BD7-47D9-B053-5A646F2458CF}"/>
+    <hyperlink ref="N26" r:id="rId43" xr:uid="{3DEFF66E-912E-4F2F-97AB-FACD57B0039F}"/>
+    <hyperlink ref="N23" r:id="rId44" xr:uid="{83A2C1C1-8C25-4D67-A480-302431668718}"/>
+    <hyperlink ref="N25" r:id="rId45" xr:uid="{30D22A24-3F30-4E99-967B-FA4F0FA9B8E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId46"/>

--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB4F6D4-0E2E-4E22-9E60-B60A43DE5748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E92F0D-5710-482F-A02C-BC10C1C0C662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="840" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="296">
   <si>
     <t>Component list</t>
   </si>
@@ -272,9 +272,6 @@
     <t>LED RED CLEAR CHIP SMD</t>
   </si>
   <si>
-    <t>0.1W ±5% ±1500ppm/℃ 25mΩ 0603 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
     <t>RES SMD 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -473,9 +470,6 @@
     <t>XZMDK68W-2</t>
   </si>
   <si>
-    <t>RTT03R025JTP</t>
-  </si>
-  <si>
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
@@ -560,9 +554,6 @@
     <t>SunLED</t>
   </si>
   <si>
-    <t>Relac</t>
-  </si>
-  <si>
     <t>FOJAN</t>
   </si>
   <si>
@@ -704,9 +695,6 @@
     <t>Quantity (1 Board)</t>
   </si>
   <si>
-    <t>Quantity (5Boards)</t>
-  </si>
-  <si>
     <t>LCSC/MOQ/5 Boards</t>
   </si>
   <si>
@@ -797,9 +785,6 @@
     <t>C71911</t>
   </si>
   <si>
-    <t>C158897</t>
-  </si>
-  <si>
     <t>C60490</t>
   </si>
   <si>
@@ -912,6 +897,27 @@
   </si>
   <si>
     <t>C2935910</t>
+  </si>
+  <si>
+    <t>RES SMD 25m Ohms 125mW 0805</t>
+  </si>
+  <si>
+    <t>Res0805</t>
+  </si>
+  <si>
+    <t>0805W8F250MT5E</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL</t>
+  </si>
+  <si>
+    <t>C620515</t>
+  </si>
+  <si>
+    <t>Is part ki Price high ha @urooj custom supplier se Quote le len</t>
+  </si>
+  <si>
+    <t>Quantity (5 Boards)</t>
   </si>
 </sst>
 </file>
@@ -923,7 +929,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1087,8 +1093,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1119,8 +1131,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1367,10 +1391,10 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1380,7 +1404,48 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1395,72 +1460,22 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1470,7 +1485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1600,31 +1615,31 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1651,64 +1666,115 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2105,8 +2171,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="113"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2122,15 +2188,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="92"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="109"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2154,7 +2220,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="89"/>
+      <c r="R3" s="106"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2178,7 +2244,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="90"/>
+      <c r="R4" s="107"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2202,7 +2268,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="90"/>
+      <c r="R5" s="107"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2222,7 +2288,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="90"/>
+      <c r="R6" s="107"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2242,7 +2308,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="90"/>
+      <c r="R7" s="107"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2262,11 +2328,11 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="90"/>
+      <c r="R8" s="107"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="81" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="32" t="s">
@@ -2276,51 +2342,51 @@
         <v>57</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G9" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="K9" s="82" t="s">
         <v>220</v>
       </c>
-      <c r="H9" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="L9" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="M9" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="J9" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="K9" s="84" t="s">
+      <c r="N9" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="O9" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="L9" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="M9" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="N9" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="O9" s="32" t="s">
-        <v>227</v>
-      </c>
       <c r="P9" s="32" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="Q9" s="32" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="85">
+      <c r="B10" s="83">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -2331,22 +2397,22 @@
         <v>58</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G10" s="65" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I10" s="60" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J10" s="51" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K10" s="54">
         <v>3</v>
@@ -2358,8 +2424,8 @@
       <c r="M10" s="41">
         <v>20</v>
       </c>
-      <c r="N10" s="76" t="s">
-        <v>228</v>
+      <c r="N10" s="74" t="s">
+        <v>224</v>
       </c>
       <c r="O10" s="42">
         <v>7.2800000000000004E-2</v>
@@ -2373,7 +2439,7 @@
     </row>
     <row r="11" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="86">
+      <c r="B11" s="83">
         <f t="shared" ref="B11:B55" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
@@ -2384,22 +2450,22 @@
         <v>59</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G11" s="61" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I11" s="61" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K11" s="55">
         <v>24</v>
@@ -2411,23 +2477,23 @@
       <c r="M11" s="31">
         <v>150</v>
       </c>
-      <c r="N11" s="77" t="s">
-        <v>228</v>
+      <c r="N11" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O11" s="35">
-        <v>6.7000000000000002E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="P11" s="35">
         <f t="shared" ref="P11:P55" si="2">O11*M11</f>
-        <v>1.0050000000000001</v>
+        <v>1.095</v>
       </c>
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="86">
-        <f>ROW(B12) - ROW($B$9)</f>
+      <c r="B12" s="83">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="53" t="s">
@@ -2437,22 +2503,22 @@
         <v>60</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G12" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I12" s="62" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K12" s="56">
         <v>1</v>
@@ -2464,8 +2530,8 @@
       <c r="M12" s="30">
         <v>20</v>
       </c>
-      <c r="N12" s="78" t="s">
-        <v>228</v>
+      <c r="N12" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O12" s="34">
         <v>1.3599999999999999E-2</v>
@@ -2479,7 +2545,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="86">
+      <c r="B13" s="83">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2490,22 +2556,22 @@
         <v>61</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G13" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K13" s="55">
         <v>8</v>
@@ -2517,8 +2583,8 @@
       <c r="M13" s="31">
         <v>100</v>
       </c>
-      <c r="N13" s="77" t="s">
-        <v>228</v>
+      <c r="N13" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O13" s="35">
         <v>1.4E-3</v>
@@ -2532,8 +2598,8 @@
     </row>
     <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="86">
-        <f>ROW(B14) - ROW($B$9)</f>
+      <c r="B14" s="83">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="53" t="s">
@@ -2543,22 +2609,22 @@
         <v>62</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G14" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I14" s="62" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K14" s="56">
         <v>3</v>
@@ -2570,22 +2636,22 @@
       <c r="M14" s="30">
         <v>50</v>
       </c>
-      <c r="N14" s="79" t="s">
-        <v>228</v>
+      <c r="N14" s="77" t="s">
+        <v>224</v>
       </c>
       <c r="O14" s="34">
-        <v>1.7600000000000001E-2</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="P14" s="34">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>0.92499999999999993</v>
       </c>
       <c r="Q14" s="34"/>
       <c r="R14" s="34"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="86">
+      <c r="B15" s="83">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2596,22 +2662,22 @@
         <v>63</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G15" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I15" s="61" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K15" s="55">
         <v>8</v>
@@ -2623,8 +2689,8 @@
       <c r="M15" s="31">
         <v>50</v>
       </c>
-      <c r="N15" s="77" t="s">
-        <v>228</v>
+      <c r="N15" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O15" s="35">
         <v>6.4000000000000003E-3</v>
@@ -2638,8 +2704,8 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="86">
-        <f>ROW(B16) - ROW($B$9)</f>
+      <c r="B16" s="83">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="53" t="s">
@@ -2649,22 +2715,22 @@
         <v>64</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G16" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H16" s="53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I16" s="62" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K16" s="56">
         <v>1</v>
@@ -2676,8 +2742,8 @@
       <c r="M16" s="36">
         <v>10</v>
       </c>
-      <c r="N16" s="79" t="s">
-        <v>228</v>
+      <c r="N16" s="77" t="s">
+        <v>224</v>
       </c>
       <c r="O16" s="37">
         <v>4.8899999999999999E-2</v>
@@ -2691,7 +2757,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="86">
+      <c r="B17" s="83">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2699,25 +2765,25 @@
         <v>18</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I17" s="61" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J17" s="52" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K17" s="55">
         <v>2</v>
@@ -2729,8 +2795,8 @@
       <c r="M17" s="31">
         <v>100</v>
       </c>
-      <c r="N17" s="77" t="s">
-        <v>228</v>
+      <c r="N17" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O17" s="35">
         <v>1.6000000000000001E-3</v>
@@ -2744,8 +2810,8 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="86">
-        <f>ROW(B18) - ROW($B$9)</f>
+      <c r="B18" s="83">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="53" t="s">
@@ -2755,22 +2821,22 @@
         <v>65</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G18" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I18" s="62" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J18" s="53" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K18" s="56">
         <v>1</v>
@@ -2782,22 +2848,22 @@
       <c r="M18" s="30">
         <v>20</v>
       </c>
-      <c r="N18" s="78" t="s">
-        <v>228</v>
+      <c r="N18" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O18" s="34">
-        <v>2.93E-2</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="P18" s="34">
         <f t="shared" si="2"/>
-        <v>0.58599999999999997</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="Q18" s="34"/>
       <c r="R18" s="34"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="86">
+      <c r="B19" s="83">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2808,22 +2874,22 @@
         <v>66</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I19" s="61" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J19" s="58" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K19" s="55">
         <v>1</v>
@@ -2835,23 +2901,23 @@
       <c r="M19" s="31">
         <v>10</v>
       </c>
-      <c r="N19" s="77" t="s">
-        <v>228</v>
+      <c r="N19" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O19" s="35">
-        <v>8.8900000000000007E-2</v>
+        <v>9.2899999999999996E-2</v>
       </c>
       <c r="P19" s="35">
         <f t="shared" si="2"/>
-        <v>0.88900000000000001</v>
+        <v>0.92899999999999994</v>
       </c>
       <c r="Q19" s="35"/>
       <c r="R19" s="35"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="86">
-        <f>ROW(B20) - ROW($B$9)</f>
+      <c r="B20" s="83">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -2861,22 +2927,22 @@
         <v>67</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I20" s="62" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K20" s="56">
         <v>1</v>
@@ -2888,8 +2954,8 @@
       <c r="M20" s="30">
         <v>6</v>
       </c>
-      <c r="N20" s="78" t="s">
-        <v>228</v>
+      <c r="N20" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O20" s="34">
         <v>2.3371</v>
@@ -2903,7 +2969,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="86">
+      <c r="B21" s="83">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2914,22 +2980,22 @@
         <v>68</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G21" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I21" s="61" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J21" s="58" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K21" s="55">
         <v>1</v>
@@ -2941,8 +3007,8 @@
       <c r="M21" s="31">
         <v>20</v>
       </c>
-      <c r="N21" s="77" t="s">
-        <v>228</v>
+      <c r="N21" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O21" s="35">
         <v>4.8399999999999999E-2</v>
@@ -2956,8 +3022,8 @@
     </row>
     <row r="22" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="86">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="83">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="53" t="s">
@@ -2967,22 +3033,22 @@
         <v>69</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G22" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I22" s="62" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K22" s="56">
         <v>1</v>
@@ -2994,8 +3060,8 @@
       <c r="M22" s="30">
         <v>6</v>
       </c>
-      <c r="N22" s="78" t="s">
-        <v>228</v>
+      <c r="N22" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O22" s="34">
         <v>0.18659999999999999</v>
@@ -3009,7 +3075,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="86">
+      <c r="B23" s="83">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -3017,25 +3083,25 @@
         <v>24</v>
       </c>
       <c r="D23" s="52" t="s">
+        <v>282</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>283</v>
+      </c>
+      <c r="G23" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="I23" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="E23" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="58" t="s">
-        <v>288</v>
-      </c>
-      <c r="G23" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>289</v>
-      </c>
-      <c r="I23" s="61" t="s">
-        <v>292</v>
-      </c>
       <c r="J23" s="58" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K23" s="55">
         <v>1</v>
@@ -3047,8 +3113,8 @@
       <c r="M23" s="31">
         <v>10</v>
       </c>
-      <c r="N23" s="88" t="s">
-        <v>228</v>
+      <c r="N23" s="84" t="s">
+        <v>224</v>
       </c>
       <c r="O23" s="35">
         <v>4.3099999999999999E-2</v>
@@ -3062,8 +3128,8 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="86">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="83">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
@@ -3073,22 +3139,22 @@
         <v>70</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H24" s="53" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J24" s="59" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K24" s="56">
         <v>1</v>
@@ -3100,22 +3166,22 @@
       <c r="M24" s="30">
         <v>6</v>
       </c>
-      <c r="N24" s="79" t="s">
-        <v>228</v>
+      <c r="N24" s="77" t="s">
+        <v>224</v>
       </c>
       <c r="O24" s="37">
-        <v>0.1893</v>
+        <v>0.1832</v>
       </c>
       <c r="P24" s="34">
         <f t="shared" si="2"/>
-        <v>1.1357999999999999</v>
+        <v>1.0992</v>
       </c>
       <c r="Q24" s="34"/>
       <c r="R24" s="34"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="86">
+      <c r="B25" s="83">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3123,25 +3189,25 @@
         <v>26</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G25" s="63" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="H25" s="52" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I25" s="61" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J25" s="58" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K25" s="55">
         <v>1</v>
@@ -3153,8 +3219,8 @@
       <c r="M25" s="31">
         <v>20</v>
       </c>
-      <c r="N25" s="88" t="s">
-        <v>228</v>
+      <c r="N25" s="84" t="s">
+        <v>224</v>
       </c>
       <c r="O25" s="35">
         <v>2.29E-2</v>
@@ -3168,62 +3234,62 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="86">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="83">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="D26" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="F26" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" s="66" t="s">
-        <v>281</v>
-      </c>
-      <c r="H26" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="I26" s="66" t="s">
-        <v>281</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="K26" s="56">
+      <c r="E26" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="F26" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="99" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="I26" s="99" t="s">
+        <v>276</v>
+      </c>
+      <c r="J26" s="97" t="s">
+        <v>198</v>
+      </c>
+      <c r="K26" s="100">
         <v>1</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="101">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="101">
         <v>7</v>
       </c>
-      <c r="N26" s="78" t="s">
-        <v>280</v>
-      </c>
-      <c r="O26" s="34">
+      <c r="N26" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="O26" s="103">
         <v>0.25</v>
       </c>
-      <c r="P26" s="34">
+      <c r="P26" s="103">
         <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
-      <c r="Q26" s="72" t="s">
-        <v>286</v>
-      </c>
-      <c r="R26" s="34"/>
+      <c r="Q26" s="104" t="s">
+        <v>281</v>
+      </c>
+      <c r="R26" s="103"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="86">
+      <c r="B27" s="83">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3234,22 +3300,22 @@
         <v>72</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I27" s="61" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J27" s="52" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K27" s="55">
         <v>1</v>
@@ -3261,8 +3327,8 @@
       <c r="M27" s="31">
         <v>7</v>
       </c>
-      <c r="N27" s="77" t="s">
-        <v>228</v>
+      <c r="N27" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O27" s="35">
         <v>0.1575</v>
@@ -3276,8 +3342,8 @@
     </row>
     <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="86">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="83">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="53" t="s">
@@ -3287,22 +3353,22 @@
         <v>73</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G28" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H28" s="53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I28" s="62" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J28" s="53" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K28" s="56">
         <v>1</v>
@@ -3314,22 +3380,22 @@
       <c r="M28" s="36">
         <v>10</v>
       </c>
-      <c r="N28" s="79" t="s">
-        <v>228</v>
+      <c r="N28" s="77" t="s">
+        <v>224</v>
       </c>
       <c r="O28" s="37">
-        <v>4.4400000000000002E-2</v>
+        <v>4.5699999999999998E-2</v>
       </c>
       <c r="P28" s="34">
         <f t="shared" si="2"/>
-        <v>0.44400000000000001</v>
+        <v>0.45699999999999996</v>
       </c>
       <c r="Q28" s="34"/>
       <c r="R28" s="34"/>
     </row>
     <row r="29" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="86">
+      <c r="B29" s="83">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3340,22 +3406,22 @@
         <v>74</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H29" s="52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I29" s="61" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J29" s="52" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K29" s="55">
         <v>1</v>
@@ -3367,8 +3433,8 @@
       <c r="M29" s="31">
         <v>10</v>
       </c>
-      <c r="N29" s="77" t="s">
-        <v>228</v>
+      <c r="N29" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O29" s="35">
         <v>5.7299999999999997E-2</v>
@@ -3382,8 +3448,8 @@
     </row>
     <row r="30" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="86">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="83">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="53" t="s">
@@ -3393,22 +3459,22 @@
         <v>75</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G30" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H30" s="53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I30" s="62" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K30" s="56">
         <v>1</v>
@@ -3420,8 +3486,8 @@
       <c r="M30" s="30">
         <v>10</v>
       </c>
-      <c r="N30" s="78" t="s">
-        <v>228</v>
+      <c r="N30" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O30" s="34">
         <v>6.4600000000000005E-2</v>
@@ -3435,7 +3501,7 @@
     </row>
     <row r="31" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="86">
+      <c r="B31" s="83">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3446,22 +3512,22 @@
         <v>76</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G31" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H31" s="52" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I31" s="61" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J31" s="58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K31" s="55">
         <v>1</v>
@@ -3473,8 +3539,8 @@
       <c r="M31" s="31">
         <v>50</v>
       </c>
-      <c r="N31" s="77" t="s">
-        <v>228</v>
+      <c r="N31" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O31" s="35">
         <v>8.6E-3</v>
@@ -3488,8 +3554,8 @@
     </row>
     <row r="32" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="86">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="83">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="53" t="s">
@@ -3499,20 +3565,20 @@
         <v>77</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" s="62"/>
       <c r="H32" s="53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I32" s="62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K32" s="56">
         <v>1</v>
@@ -3524,8 +3590,8 @@
       <c r="M32" s="36">
         <v>10</v>
       </c>
-      <c r="N32" s="79" t="s">
-        <v>228</v>
+      <c r="N32" s="77" t="s">
+        <v>224</v>
       </c>
       <c r="O32" s="37">
         <v>9.4299999999999995E-2</v>
@@ -3539,7 +3605,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="86">
+      <c r="B33" s="83">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3550,22 +3616,22 @@
         <v>78</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F33" s="68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G33" s="61" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H33" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I33" s="61" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J33" s="58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K33" s="55">
         <v>2</v>
@@ -3577,8 +3643,8 @@
       <c r="M33" s="31">
         <v>50</v>
       </c>
-      <c r="N33" s="77" t="s">
-        <v>228</v>
+      <c r="N33" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O33" s="35">
         <v>1.7500000000000002E-2</v>
@@ -3592,8 +3658,8 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="86">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="83">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="53" t="s">
@@ -3603,22 +3669,22 @@
         <v>79</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G34" s="62" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H34" s="53" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I34" s="62" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K34" s="56">
         <v>1</v>
@@ -3630,8 +3696,8 @@
       <c r="M34" s="30">
         <v>10</v>
       </c>
-      <c r="N34" s="78" t="s">
-        <v>228</v>
+      <c r="N34" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O34" s="34">
         <v>5.2400000000000002E-2</v>
@@ -3643,35 +3709,35 @@
       <c r="Q34" s="34"/>
       <c r="R34" s="34"/>
     </row>
-    <row r="35" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="86">
+      <c r="B35" s="83">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="61" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="H35" s="52" t="s">
-        <v>176</v>
+      <c r="D35" s="85" t="s">
+        <v>289</v>
+      </c>
+      <c r="E35" s="86" t="s">
+        <v>290</v>
+      </c>
+      <c r="F35" s="86" t="s">
+        <v>291</v>
+      </c>
+      <c r="G35" s="87" t="s">
+        <v>215</v>
+      </c>
+      <c r="H35" s="86" t="s">
+        <v>292</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="J35" s="52" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K35" s="55">
         <v>1</v>
@@ -3683,48 +3749,48 @@
       <c r="M35" s="31">
         <v>50</v>
       </c>
-      <c r="N35" s="77" t="s">
-        <v>228</v>
+      <c r="N35" s="84" t="s">
+        <v>224</v>
       </c>
       <c r="O35" s="35">
-        <v>1.4200000000000001E-2</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="P35" s="35">
         <f t="shared" si="2"/>
-        <v>0.71000000000000008</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="Q35" s="35"/>
       <c r="R35" s="35"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="86">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="83">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="53" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F36" s="53" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G36" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H36" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I36" s="62" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J36" s="53" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K36" s="56">
         <v>4</v>
@@ -3736,8 +3802,8 @@
       <c r="M36" s="30">
         <v>100</v>
       </c>
-      <c r="N36" s="78" t="s">
-        <v>228</v>
+      <c r="N36" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O36" s="34">
         <v>5.9999999999999995E-4</v>
@@ -3751,7 +3817,7 @@
     </row>
     <row r="37" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="86">
+      <c r="B37" s="83">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -3759,25 +3825,25 @@
         <v>38</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G37" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I37" s="61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J37" s="52" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K37" s="55">
         <v>10</v>
@@ -3789,8 +3855,8 @@
       <c r="M37" s="31">
         <v>100</v>
       </c>
-      <c r="N37" s="77" t="s">
-        <v>228</v>
+      <c r="N37" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O37" s="35">
         <v>6.9999999999999999E-4</v>
@@ -3804,33 +3870,33 @@
     </row>
     <row r="38" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="86">
-        <f>ROW(B38) - ROW($B$9)</f>
+      <c r="B38" s="83">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="53" t="s">
         <v>39</v>
       </c>
       <c r="D38" s="62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F38" s="53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G38" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H38" s="53" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I38" s="62" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J38" s="53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K38" s="56">
         <v>1</v>
@@ -3842,8 +3908,8 @@
       <c r="M38" s="30">
         <v>100</v>
       </c>
-      <c r="N38" s="78" t="s">
-        <v>228</v>
+      <c r="N38" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O38" s="34">
         <v>5.0000000000000001E-4</v>
@@ -3857,7 +3923,7 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="86">
+      <c r="B39" s="83">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -3865,25 +3931,25 @@
         <v>40</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" s="52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F39" s="68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G39" s="61" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="H39" s="52" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I39" s="61" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J39" s="52" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K39" s="55">
         <v>7</v>
@@ -3895,48 +3961,48 @@
       <c r="M39" s="31">
         <v>100</v>
       </c>
-      <c r="N39" s="77" t="s">
-        <v>228</v>
+      <c r="N39" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O39" s="35">
-        <v>6.9999999999999999E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="P39" s="35">
         <f t="shared" si="2"/>
-        <v>6.9999999999999993E-2</v>
+        <v>0.06</v>
       </c>
       <c r="Q39" s="35"/>
       <c r="R39" s="35"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="86">
-        <f>ROW(B40) - ROW($B$9)</f>
+      <c r="B40" s="83">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="53" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G40" s="62" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="H40" s="53" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I40" s="62" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J40" s="53" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K40" s="56">
         <v>2</v>
@@ -3948,8 +4014,8 @@
       <c r="M40" s="30">
         <v>100</v>
       </c>
-      <c r="N40" s="78" t="s">
-        <v>228</v>
+      <c r="N40" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O40" s="34">
         <v>8.0000000000000004E-4</v>
@@ -3963,7 +4029,7 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="86">
+      <c r="B41" s="83">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -3971,25 +4037,25 @@
         <v>42</v>
       </c>
       <c r="D41" s="61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E41" s="52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F41" s="68" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G41" s="61" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="H41" s="52" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I41" s="61" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J41" s="52" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K41" s="55">
         <v>2</v>
@@ -4001,8 +4067,8 @@
       <c r="M41" s="31">
         <v>100</v>
       </c>
-      <c r="N41" s="77" t="s">
-        <v>228</v>
+      <c r="N41" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O41" s="35">
         <v>3.5999999999999999E-3</v>
@@ -4016,33 +4082,33 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="86">
-        <f>ROW(B42) - ROW($B$9)</f>
+      <c r="B42" s="83">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="53" t="s">
         <v>43</v>
       </c>
       <c r="D42" s="62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F42" s="53" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G42" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H42" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I42" s="62" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J42" s="53" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K42" s="56">
         <v>1</v>
@@ -4054,8 +4120,8 @@
       <c r="M42" s="30">
         <v>50</v>
       </c>
-      <c r="N42" s="78" t="s">
-        <v>228</v>
+      <c r="N42" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O42" s="34">
         <v>6.9999999999999999E-4</v>
@@ -4069,7 +4135,7 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="86">
+      <c r="B43" s="83">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -4077,23 +4143,23 @@
         <v>44</v>
       </c>
       <c r="D43" s="61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F43" s="58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G43" s="63"/>
       <c r="H43" s="58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I43" s="63" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J43" s="58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K43" s="55">
         <v>3</v>
@@ -4103,49 +4169,49 @@
         <v>15</v>
       </c>
       <c r="M43" s="70" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N43" s="70" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O43" s="70" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P43" s="70" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q43" s="70"/>
       <c r="R43" s="70"/>
     </row>
     <row r="44" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="86">
-        <f>ROW(B44) - ROW($B$9)</f>
+      <c r="B44" s="83">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="53" t="s">
         <v>45</v>
       </c>
       <c r="D44" s="62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F44" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G44" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H44" s="53" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I44" s="62" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K44" s="56">
         <v>1</v>
@@ -4157,103 +4223,103 @@
       <c r="M44" s="30">
         <v>10</v>
       </c>
-      <c r="N44" s="78" t="s">
-        <v>228</v>
+      <c r="N44" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O44" s="34">
-        <v>5.91E-2</v>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="P44" s="34">
         <f t="shared" si="2"/>
-        <v>0.59099999999999997</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="Q44" s="34"/>
       <c r="R44" s="34"/>
     </row>
     <row r="45" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="86">
+      <c r="B45" s="83">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="E45" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="G45" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="H45" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="I45" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="J45" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="K45" s="55">
+      <c r="D45" s="98" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="G45" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="H45" s="97" t="s">
+        <v>178</v>
+      </c>
+      <c r="I45" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="J45" s="105" t="s">
+        <v>216</v>
+      </c>
+      <c r="K45" s="100">
         <v>1</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="101">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="101">
         <v>6</v>
       </c>
-      <c r="N45" s="77" t="s">
-        <v>280</v>
-      </c>
-      <c r="O45" s="35">
+      <c r="N45" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="O45" s="103">
         <v>3.2</v>
       </c>
-      <c r="P45" s="35">
+      <c r="P45" s="103">
         <f t="shared" si="2"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="Q45" s="71" t="s">
-        <v>286</v>
-      </c>
-      <c r="R45" s="35"/>
+      <c r="Q45" s="104" t="s">
+        <v>281</v>
+      </c>
+      <c r="R45" s="103"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="86">
-        <f>ROW(B46) - ROW($B$9)</f>
+      <c r="B46" s="83">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="53" t="s">
         <v>47</v>
       </c>
       <c r="D46" s="62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F46" s="53" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G46" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H46" s="53" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I46" s="62" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K46" s="56">
         <v>1</v>
@@ -4265,211 +4331,213 @@
       <c r="M46" s="30">
         <v>6</v>
       </c>
-      <c r="N46" s="78" t="s">
-        <v>228</v>
+      <c r="N46" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O46" s="34">
-        <v>0.47070000000000001</v>
+        <v>0.49409999999999998</v>
       </c>
       <c r="P46" s="34">
         <f t="shared" si="2"/>
-        <v>2.8242000000000003</v>
+        <v>2.9645999999999999</v>
       </c>
       <c r="Q46" s="34"/>
       <c r="R46" s="34"/>
     </row>
     <row r="47" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="86">
+      <c r="B47" s="83">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="E47" s="52" t="s">
-        <v>124</v>
-      </c>
-      <c r="F47" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="G47" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="H47" s="52" t="s">
-        <v>183</v>
-      </c>
-      <c r="I47" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="J47" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="K47" s="55">
+      <c r="D47" s="98" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="H47" s="97" t="s">
+        <v>180</v>
+      </c>
+      <c r="I47" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="J47" s="105" t="s">
+        <v>216</v>
+      </c>
+      <c r="K47" s="100">
         <v>1</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L47" s="101">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M47" s="31">
+      <c r="M47" s="101">
         <v>6</v>
       </c>
-      <c r="N47" s="77" t="s">
-        <v>280</v>
-      </c>
-      <c r="O47" s="35">
+      <c r="N47" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="O47" s="103">
         <v>1.8</v>
       </c>
-      <c r="P47" s="35">
+      <c r="P47" s="103">
         <f t="shared" si="2"/>
         <v>10.8</v>
       </c>
-      <c r="Q47" s="71" t="s">
-        <v>286</v>
-      </c>
-      <c r="R47" s="35"/>
+      <c r="Q47" s="104" t="s">
+        <v>281</v>
+      </c>
+      <c r="R47" s="103"/>
     </row>
     <row r="48" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="86">
-        <f>ROW(B48) - ROW($B$9)</f>
+      <c r="B48" s="83">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="53" t="s">
+      <c r="C48" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="E48" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="F48" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="G48" s="66" t="s">
-        <v>218</v>
-      </c>
-      <c r="H48" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="I48" s="62" t="s">
-        <v>267</v>
-      </c>
-      <c r="J48" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="K48" s="56">
+      <c r="D48" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="88" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="G48" s="90" t="s">
+        <v>215</v>
+      </c>
+      <c r="H48" s="88" t="s">
+        <v>181</v>
+      </c>
+      <c r="I48" s="89" t="s">
+        <v>262</v>
+      </c>
+      <c r="J48" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="K48" s="92">
         <v>1</v>
       </c>
-      <c r="L48" s="30">
+      <c r="L48" s="93">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M48" s="30">
+      <c r="M48" s="93">
         <v>6</v>
       </c>
-      <c r="N48" s="78" t="s">
-        <v>228</v>
-      </c>
-      <c r="O48" s="34">
-        <v>13.1333</v>
-      </c>
-      <c r="P48" s="34">
+      <c r="N48" s="94" t="s">
+        <v>224</v>
+      </c>
+      <c r="O48" s="95">
+        <v>12.0892</v>
+      </c>
+      <c r="P48" s="95">
         <f t="shared" si="2"/>
-        <v>78.799800000000005</v>
-      </c>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="34"/>
+        <v>72.535200000000003</v>
+      </c>
+      <c r="Q48" s="96" t="s">
+        <v>294</v>
+      </c>
+      <c r="R48" s="95"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="86">
+      <c r="B49" s="83">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="D49" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="F49" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="H49" s="52" t="s">
-        <v>185</v>
-      </c>
-      <c r="I49" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="J49" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="K49" s="55">
+      <c r="D49" s="98" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="F49" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="G49" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="H49" s="97" t="s">
+        <v>182</v>
+      </c>
+      <c r="I49" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="J49" s="105" t="s">
+        <v>216</v>
+      </c>
+      <c r="K49" s="100">
         <v>1</v>
       </c>
-      <c r="L49" s="31">
+      <c r="L49" s="101">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M49" s="31">
+      <c r="M49" s="101">
         <v>6</v>
       </c>
-      <c r="N49" s="77" t="s">
-        <v>280</v>
-      </c>
-      <c r="O49" s="35">
+      <c r="N49" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="O49" s="103">
         <v>11.45</v>
       </c>
-      <c r="P49" s="35">
+      <c r="P49" s="103">
         <f t="shared" si="2"/>
         <v>68.699999999999989</v>
       </c>
-      <c r="Q49" s="71" t="s">
-        <v>286</v>
-      </c>
-      <c r="R49" s="35"/>
+      <c r="Q49" s="104" t="s">
+        <v>281</v>
+      </c>
+      <c r="R49" s="103"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="86">
-        <f>ROW(B50) - ROW($B$9)</f>
+      <c r="B50" s="83">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="53" t="s">
         <v>51</v>
       </c>
       <c r="D50" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F50" s="53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G50" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H50" s="53" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I50" s="62" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J50" s="59" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K50" s="56">
         <v>1</v>
@@ -4481,8 +4549,8 @@
       <c r="M50" s="30">
         <v>6</v>
       </c>
-      <c r="N50" s="78" t="s">
-        <v>228</v>
+      <c r="N50" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O50" s="34">
         <v>2.851</v>
@@ -4496,7 +4564,7 @@
     </row>
     <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="86">
+      <c r="B51" s="83">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -4504,25 +4572,25 @@
         <v>52</v>
       </c>
       <c r="D51" s="61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" s="52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H51" s="52" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I51" s="61" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J51" s="58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K51" s="55">
         <v>1</v>
@@ -4534,8 +4602,8 @@
       <c r="M51" s="31">
         <v>6</v>
       </c>
-      <c r="N51" s="77" t="s">
-        <v>228</v>
+      <c r="N51" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O51" s="35">
         <v>4.3278999999999996</v>
@@ -4549,33 +4617,33 @@
     </row>
     <row r="52" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="86">
-        <f>ROW(B52) - ROW($B$9)</f>
+      <c r="B52" s="83">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="53" t="s">
         <v>53</v>
       </c>
       <c r="D52" s="62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F52" s="53" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G52" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H52" s="53" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I52" s="62" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J52" s="59" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K52" s="56">
         <v>1</v>
@@ -4587,8 +4655,8 @@
       <c r="M52" s="30">
         <v>10</v>
       </c>
-      <c r="N52" s="78" t="s">
-        <v>228</v>
+      <c r="N52" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O52" s="34">
         <v>2.0400000000000001E-2</v>
@@ -4602,7 +4670,7 @@
     </row>
     <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="86">
+      <c r="B53" s="83">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -4610,25 +4678,25 @@
         <v>54</v>
       </c>
       <c r="D53" s="61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F53" s="52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G53" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H53" s="52" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I53" s="61" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J53" s="52" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K53" s="55">
         <v>2</v>
@@ -4640,48 +4708,48 @@
       <c r="M53" s="31">
         <v>11</v>
       </c>
-      <c r="N53" s="77" t="s">
-        <v>228</v>
+      <c r="N53" s="75" t="s">
+        <v>224</v>
       </c>
       <c r="O53" s="35">
-        <v>0.27989999999999998</v>
+        <v>0.27650000000000002</v>
       </c>
       <c r="P53" s="35">
         <f t="shared" si="2"/>
-        <v>3.0789</v>
+        <v>3.0415000000000001</v>
       </c>
       <c r="Q53" s="35"/>
       <c r="R53" s="35"/>
     </row>
     <row r="54" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="86">
-        <f>ROW(B54) - ROW($B$9)</f>
+      <c r="B54" s="83">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="53" t="s">
         <v>55</v>
       </c>
       <c r="D54" s="62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F54" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G54" s="66" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H54" s="53" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I54" s="62" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J54" s="53" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K54" s="56">
         <v>1</v>
@@ -4693,48 +4761,48 @@
       <c r="M54" s="30">
         <v>10</v>
       </c>
-      <c r="N54" s="78" t="s">
-        <v>228</v>
+      <c r="N54" s="76" t="s">
+        <v>224</v>
       </c>
       <c r="O54" s="34">
-        <v>9.8500000000000004E-2</v>
+        <v>9.7100000000000006E-2</v>
       </c>
       <c r="P54" s="34">
         <f t="shared" si="2"/>
-        <v>0.9850000000000001</v>
+        <v>0.97100000000000009</v>
       </c>
       <c r="Q54" s="34"/>
       <c r="R54" s="34"/>
     </row>
     <row r="55" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="B55" s="87">
+      <c r="B55" s="83">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="75" t="s">
+      <c r="C55" s="73" t="s">
         <v>56</v>
       </c>
       <c r="D55" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E55" s="75" t="s">
-        <v>217</v>
-      </c>
-      <c r="F55" s="75" t="s">
-        <v>132</v>
+        <v>98</v>
+      </c>
+      <c r="E55" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="F55" s="73" t="s">
+        <v>131</v>
       </c>
       <c r="G55" s="67" t="s">
-        <v>218</v>
-      </c>
-      <c r="H55" s="75" t="s">
-        <v>190</v>
+        <v>215</v>
+      </c>
+      <c r="H55" s="73" t="s">
+        <v>187</v>
       </c>
       <c r="I55" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="J55" s="75" t="s">
-        <v>216</v>
+        <v>268</v>
+      </c>
+      <c r="J55" s="73" t="s">
+        <v>213</v>
       </c>
       <c r="K55" s="57">
         <v>1</v>
@@ -4746,8 +4814,8 @@
       <c r="M55" s="45">
         <v>10</v>
       </c>
-      <c r="N55" s="80" t="s">
-        <v>228</v>
+      <c r="N55" s="78" t="s">
+        <v>224</v>
       </c>
       <c r="O55" s="46">
         <v>0.13439999999999999</v>
@@ -4767,24 +4835,24 @@
       </c>
       <c r="D56" s="49"/>
       <c r="E56" s="50"/>
-      <c r="F56" s="73"/>
-      <c r="G56" s="73"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="73"/>
-      <c r="J56" s="73"/>
-      <c r="K56" s="73"/>
-      <c r="L56" s="73"/>
-      <c r="M56" s="93" t="s">
-        <v>283</v>
-      </c>
-      <c r="N56" s="94"/>
-      <c r="O56" s="94"/>
-      <c r="P56" s="82">
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="71"/>
+      <c r="L56" s="71"/>
+      <c r="M56" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="N56" s="111"/>
+      <c r="O56" s="111"/>
+      <c r="P56" s="80">
         <f>SUM(P10:P55)</f>
-        <v>262.65479999999997</v>
-      </c>
-      <c r="Q56" s="73"/>
-      <c r="R56" s="74"/>
+        <v>256.46360000000004</v>
+      </c>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
     </row>
     <row r="57" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
@@ -4801,14 +4869,14 @@
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
       <c r="L57" s="43"/>
-      <c r="M57" s="93" t="s">
-        <v>284</v>
-      </c>
-      <c r="N57" s="94"/>
-      <c r="O57" s="94"/>
-      <c r="P57" s="81">
+      <c r="M57" s="110" t="s">
+        <v>279</v>
+      </c>
+      <c r="N57" s="111"/>
+      <c r="O57" s="111"/>
+      <c r="P57" s="79">
         <f>P56/5</f>
-        <v>52.530959999999993</v>
+        <v>51.29272000000001</v>
       </c>
       <c r="Q57" s="43"/>
       <c r="R57" s="44"/>
@@ -4844,29 +4912,29 @@
     <hyperlink ref="N31" r:id="rId20" xr:uid="{DAFC4B5E-88AC-4044-8DE5-E6B95F9FA94C}"/>
     <hyperlink ref="N33" r:id="rId21" xr:uid="{FC25DD16-B062-4971-87F3-FBBA153342C7}"/>
     <hyperlink ref="N34" r:id="rId22" xr:uid="{BA75FE37-D1AE-4A06-A7D6-2FC24E19A57B}"/>
-    <hyperlink ref="N35" r:id="rId23" xr:uid="{98223D7D-7BBA-4B3D-BFE2-9CB1E02D92C6}"/>
-    <hyperlink ref="N37" r:id="rId24" xr:uid="{F2FCE814-68EB-42CA-B801-47EACCC9D840}"/>
-    <hyperlink ref="N38" r:id="rId25" xr:uid="{B8B83BF6-E82D-4A6D-9C89-2F85CAB04646}"/>
-    <hyperlink ref="N42" r:id="rId26" xr:uid="{377F7D05-CD56-46CE-86C7-8359A58D6174}"/>
-    <hyperlink ref="N39" r:id="rId27" xr:uid="{5BC7FB0B-A7A9-4A4F-B0AF-D93D90BD0257}"/>
-    <hyperlink ref="N40" r:id="rId28" xr:uid="{42342919-596A-4C59-8816-01D385B759CB}"/>
-    <hyperlink ref="N41" r:id="rId29" xr:uid="{5D8F6C78-4114-4B09-9296-33D8E0033965}"/>
-    <hyperlink ref="N44" r:id="rId30" xr:uid="{30A94DA1-5BD4-4155-A48B-F08C168CF099}"/>
-    <hyperlink ref="N46" r:id="rId31" xr:uid="{C3F3FC15-3DA9-4B1A-84AC-5A582D205C55}"/>
-    <hyperlink ref="N48" r:id="rId32" xr:uid="{3A097DB9-C3B3-436E-8B87-273AE27C3FB3}"/>
-    <hyperlink ref="N50" r:id="rId33" xr:uid="{0763754B-803A-440F-9046-E7656CF9DB82}"/>
-    <hyperlink ref="N51" r:id="rId34" xr:uid="{4C3FCDA1-65D2-4395-9426-3E1F29BD784A}"/>
-    <hyperlink ref="N52" r:id="rId35" xr:uid="{A4B71E3E-7A98-4CCB-A3C2-8B949A858D06}"/>
-    <hyperlink ref="N53" r:id="rId36" xr:uid="{8DCBF280-B1E4-481C-8762-45E69BB689C9}"/>
-    <hyperlink ref="N54" r:id="rId37" xr:uid="{9D7C6330-6521-4E77-B082-7293A2D402F7}"/>
-    <hyperlink ref="N55" r:id="rId38" xr:uid="{60E4F958-BD03-4950-AA1A-E5483E7B8267}"/>
-    <hyperlink ref="N36" r:id="rId39" xr:uid="{019A488B-4FF7-4C4E-B4AC-B360044B8376}"/>
-    <hyperlink ref="N45" r:id="rId40" xr:uid="{422359C3-822C-4FAA-8878-23A1A61D0F74}"/>
-    <hyperlink ref="N47" r:id="rId41" xr:uid="{1814BF9F-58FE-400D-907F-EAC26C6361E4}"/>
-    <hyperlink ref="N49" r:id="rId42" xr:uid="{1CD03380-9BD7-47D9-B053-5A646F2458CF}"/>
-    <hyperlink ref="N26" r:id="rId43" xr:uid="{3DEFF66E-912E-4F2F-97AB-FACD57B0039F}"/>
-    <hyperlink ref="N23" r:id="rId44" xr:uid="{83A2C1C1-8C25-4D67-A480-302431668718}"/>
-    <hyperlink ref="N25" r:id="rId45" xr:uid="{30D22A24-3F30-4E99-967B-FA4F0FA9B8E8}"/>
+    <hyperlink ref="N37" r:id="rId23" xr:uid="{F2FCE814-68EB-42CA-B801-47EACCC9D840}"/>
+    <hyperlink ref="N38" r:id="rId24" xr:uid="{B8B83BF6-E82D-4A6D-9C89-2F85CAB04646}"/>
+    <hyperlink ref="N42" r:id="rId25" xr:uid="{377F7D05-CD56-46CE-86C7-8359A58D6174}"/>
+    <hyperlink ref="N39" r:id="rId26" xr:uid="{5BC7FB0B-A7A9-4A4F-B0AF-D93D90BD0257}"/>
+    <hyperlink ref="N40" r:id="rId27" xr:uid="{42342919-596A-4C59-8816-01D385B759CB}"/>
+    <hyperlink ref="N41" r:id="rId28" xr:uid="{5D8F6C78-4114-4B09-9296-33D8E0033965}"/>
+    <hyperlink ref="N44" r:id="rId29" xr:uid="{30A94DA1-5BD4-4155-A48B-F08C168CF099}"/>
+    <hyperlink ref="N46" r:id="rId30" xr:uid="{C3F3FC15-3DA9-4B1A-84AC-5A582D205C55}"/>
+    <hyperlink ref="N48" r:id="rId31" xr:uid="{3A097DB9-C3B3-436E-8B87-273AE27C3FB3}"/>
+    <hyperlink ref="N50" r:id="rId32" xr:uid="{0763754B-803A-440F-9046-E7656CF9DB82}"/>
+    <hyperlink ref="N51" r:id="rId33" xr:uid="{4C3FCDA1-65D2-4395-9426-3E1F29BD784A}"/>
+    <hyperlink ref="N52" r:id="rId34" xr:uid="{A4B71E3E-7A98-4CCB-A3C2-8B949A858D06}"/>
+    <hyperlink ref="N53" r:id="rId35" xr:uid="{8DCBF280-B1E4-481C-8762-45E69BB689C9}"/>
+    <hyperlink ref="N54" r:id="rId36" xr:uid="{9D7C6330-6521-4E77-B082-7293A2D402F7}"/>
+    <hyperlink ref="N55" r:id="rId37" xr:uid="{60E4F958-BD03-4950-AA1A-E5483E7B8267}"/>
+    <hyperlink ref="N36" r:id="rId38" xr:uid="{019A488B-4FF7-4C4E-B4AC-B360044B8376}"/>
+    <hyperlink ref="N45" r:id="rId39" xr:uid="{422359C3-822C-4FAA-8878-23A1A61D0F74}"/>
+    <hyperlink ref="N47" r:id="rId40" xr:uid="{1814BF9F-58FE-400D-907F-EAC26C6361E4}"/>
+    <hyperlink ref="N49" r:id="rId41" xr:uid="{1CD03380-9BD7-47D9-B053-5A646F2458CF}"/>
+    <hyperlink ref="N26" r:id="rId42" xr:uid="{3DEFF66E-912E-4F2F-97AB-FACD57B0039F}"/>
+    <hyperlink ref="N23" r:id="rId43" xr:uid="{83A2C1C1-8C25-4D67-A480-302431668718}"/>
+    <hyperlink ref="N25" r:id="rId44" xr:uid="{30D22A24-3F30-4E99-967B-FA4F0FA9B8E8}"/>
+    <hyperlink ref="N35" r:id="rId45" xr:uid="{E6D3A492-9D47-4832-8671-ED5B61C9ACB1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId46"/>

--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E92F0D-5710-482F-A02C-BC10C1C0C662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB529AF9-ED5E-4632-946F-077CCFFDF5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="295">
   <si>
     <t>Component list</t>
   </si>
@@ -857,9 +857,6 @@
     <t xml:space="preserve">Reviewer Remarks </t>
   </si>
   <si>
-    <t>Alibaba</t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
@@ -875,9 +872,6 @@
     <t>Total Cost/5 Boards</t>
   </si>
   <si>
-    <t>Custom Supplier Quotation</t>
-  </si>
-  <si>
     <t>CONN HEADER VERT 8POS 2.54MM</t>
   </si>
   <si>
@@ -918,6 +912,9 @@
   </si>
   <si>
     <t>Quantity (5 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Need Fresh Quote From Custom Supplier </t>
   </si>
 </sst>
 </file>
@@ -929,7 +926,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1093,12 +1090,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1144,7 +1135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1466,9 +1457,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1476,6 +1478,21 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1485,7 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1657,21 +1674,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1713,22 +1715,10 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1801,6 +1791,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2171,8 +2203,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="113"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="104"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2188,15 +2220,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="109"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="100"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2220,7 +2252,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="106"/>
+      <c r="R3" s="97"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2244,7 +2276,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="107"/>
+      <c r="R4" s="98"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2268,7 +2300,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="107"/>
+      <c r="R5" s="98"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2288,7 +2320,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="107"/>
+      <c r="R6" s="98"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2308,7 +2340,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="107"/>
+      <c r="R7" s="98"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2328,11 +2360,11 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="107"/>
+      <c r="R8" s="98"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="76" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="32" t="s">
@@ -2344,13 +2376,13 @@
       <c r="E9" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="77" t="s">
         <v>160</v>
       </c>
       <c r="I9" s="33" t="s">
@@ -2359,11 +2391,11 @@
       <c r="J9" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="K9" s="82" t="s">
+      <c r="K9" s="77" t="s">
         <v>220</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M9" s="32" t="s">
         <v>221</v>
@@ -2375,7 +2407,7 @@
         <v>223</v>
       </c>
       <c r="P9" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q9" s="32" t="s">
         <v>273</v>
@@ -2386,7 +2418,7 @@
     </row>
     <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="83">
+      <c r="B10" s="78">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -2399,13 +2431,13 @@
       <c r="E10" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="G10" s="65" t="s">
+      <c r="G10" s="114" t="s">
         <v>215</v>
       </c>
-      <c r="H10" s="51" t="s">
+      <c r="H10" s="106" t="s">
         <v>161</v>
       </c>
       <c r="I10" s="60" t="s">
@@ -2424,7 +2456,7 @@
       <c r="M10" s="41">
         <v>20</v>
       </c>
-      <c r="N10" s="74" t="s">
+      <c r="N10" s="69" t="s">
         <v>224</v>
       </c>
       <c r="O10" s="42">
@@ -2439,7 +2471,7 @@
     </row>
     <row r="11" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="83">
+      <c r="B11" s="78">
         <f t="shared" ref="B11:B55" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
@@ -2452,13 +2484,13 @@
       <c r="E11" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="G11" s="61" t="s">
+      <c r="G11" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="107" t="s">
         <v>161</v>
       </c>
       <c r="I11" s="61" t="s">
@@ -2477,7 +2509,7 @@
       <c r="M11" s="31">
         <v>150</v>
       </c>
-      <c r="N11" s="75" t="s">
+      <c r="N11" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O11" s="35">
@@ -2492,7 +2524,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="83">
+      <c r="B12" s="78">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2505,13 +2537,13 @@
       <c r="E12" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="62" t="s">
         <v>135</v>
       </c>
-      <c r="G12" s="66" t="s">
+      <c r="G12" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="108" t="s">
         <v>162</v>
       </c>
       <c r="I12" s="62" t="s">
@@ -2530,7 +2562,7 @@
       <c r="M12" s="30">
         <v>20</v>
       </c>
-      <c r="N12" s="76" t="s">
+      <c r="N12" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O12" s="34">
@@ -2545,7 +2577,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="83">
+      <c r="B13" s="78">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2558,13 +2590,13 @@
       <c r="E13" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="107" t="s">
         <v>163</v>
       </c>
       <c r="I13" s="61" t="s">
@@ -2583,7 +2615,7 @@
       <c r="M13" s="31">
         <v>100</v>
       </c>
-      <c r="N13" s="75" t="s">
+      <c r="N13" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O13" s="35">
@@ -2598,7 +2630,7 @@
     </row>
     <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="83">
+      <c r="B14" s="78">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2611,13 +2643,13 @@
       <c r="E14" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="G14" s="66" t="s">
+      <c r="G14" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H14" s="53" t="s">
+      <c r="H14" s="108" t="s">
         <v>164</v>
       </c>
       <c r="I14" s="62" t="s">
@@ -2636,7 +2668,7 @@
       <c r="M14" s="30">
         <v>50</v>
       </c>
-      <c r="N14" s="77" t="s">
+      <c r="N14" s="72" t="s">
         <v>224</v>
       </c>
       <c r="O14" s="34">
@@ -2651,7 +2683,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="83">
+      <c r="B15" s="78">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2664,13 +2696,13 @@
       <c r="E15" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="107" t="s">
         <v>163</v>
       </c>
       <c r="I15" s="61" t="s">
@@ -2689,7 +2721,7 @@
       <c r="M15" s="31">
         <v>50</v>
       </c>
-      <c r="N15" s="75" t="s">
+      <c r="N15" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O15" s="35">
@@ -2704,7 +2736,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="83">
+      <c r="B16" s="78">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2717,13 +2749,13 @@
       <c r="E16" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="G16" s="66" t="s">
+      <c r="G16" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="108" t="s">
         <v>161</v>
       </c>
       <c r="I16" s="62" t="s">
@@ -2742,7 +2774,7 @@
       <c r="M16" s="36">
         <v>10</v>
       </c>
-      <c r="N16" s="77" t="s">
+      <c r="N16" s="72" t="s">
         <v>224</v>
       </c>
       <c r="O16" s="37">
@@ -2757,7 +2789,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="83">
+      <c r="B17" s="78">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2770,13 +2802,13 @@
       <c r="E17" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="52" t="s">
+      <c r="F17" s="61" t="s">
         <v>234</v>
       </c>
-      <c r="G17" s="63" t="s">
+      <c r="G17" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="107" t="s">
         <v>163</v>
       </c>
       <c r="I17" s="61" t="s">
@@ -2795,7 +2827,7 @@
       <c r="M17" s="31">
         <v>100</v>
       </c>
-      <c r="N17" s="75" t="s">
+      <c r="N17" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O17" s="35">
@@ -2810,7 +2842,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="83">
+      <c r="B18" s="78">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2823,13 +2855,13 @@
       <c r="E18" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="53" t="s">
+      <c r="F18" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="108" t="s">
         <v>161</v>
       </c>
       <c r="I18" s="62" t="s">
@@ -2848,7 +2880,7 @@
       <c r="M18" s="30">
         <v>20</v>
       </c>
-      <c r="N18" s="76" t="s">
+      <c r="N18" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O18" s="34">
@@ -2863,7 +2895,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="83">
+      <c r="B19" s="78">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2876,13 +2908,13 @@
       <c r="E19" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="63" t="s">
+      <c r="G19" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="107" t="s">
         <v>165</v>
       </c>
       <c r="I19" s="61" t="s">
@@ -2901,7 +2933,7 @@
       <c r="M19" s="31">
         <v>10</v>
       </c>
-      <c r="N19" s="75" t="s">
+      <c r="N19" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O19" s="35">
@@ -2916,7 +2948,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="83">
+      <c r="B20" s="78">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2929,13 +2961,13 @@
       <c r="E20" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H20" s="53" t="s">
+      <c r="H20" s="108" t="s">
         <v>166</v>
       </c>
       <c r="I20" s="62" t="s">
@@ -2954,7 +2986,7 @@
       <c r="M20" s="30">
         <v>6</v>
       </c>
-      <c r="N20" s="76" t="s">
+      <c r="N20" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O20" s="34">
@@ -2969,7 +3001,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="83">
+      <c r="B21" s="78">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2982,13 +3014,13 @@
       <c r="E21" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="F21" s="52" t="s">
+      <c r="F21" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="107" t="s">
         <v>167</v>
       </c>
       <c r="I21" s="61" t="s">
@@ -3007,7 +3039,7 @@
       <c r="M21" s="31">
         <v>20</v>
       </c>
-      <c r="N21" s="75" t="s">
+      <c r="N21" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O21" s="35">
@@ -3022,7 +3054,7 @@
     </row>
     <row r="22" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="83">
+      <c r="B22" s="78">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -3035,13 +3067,13 @@
       <c r="E22" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="66" t="s">
+      <c r="G22" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H22" s="53" t="s">
+      <c r="H22" s="108" t="s">
         <v>168</v>
       </c>
       <c r="I22" s="62" t="s">
@@ -3060,7 +3092,7 @@
       <c r="M22" s="30">
         <v>6</v>
       </c>
-      <c r="N22" s="76" t="s">
+      <c r="N22" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O22" s="34">
@@ -3075,30 +3107,30 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="83">
+      <c r="B23" s="78">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="52" t="s">
-        <v>282</v>
+      <c r="D23" s="105" t="s">
+        <v>280</v>
       </c>
       <c r="E23" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="G23" s="63" t="s">
+      <c r="F23" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="G23" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H23" s="52" t="s">
-        <v>284</v>
+      <c r="H23" s="107" t="s">
+        <v>282</v>
       </c>
       <c r="I23" s="61" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J23" s="58" t="s">
         <v>215</v>
@@ -3113,7 +3145,7 @@
       <c r="M23" s="31">
         <v>10</v>
       </c>
-      <c r="N23" s="84" t="s">
+      <c r="N23" s="79" t="s">
         <v>224</v>
       </c>
       <c r="O23" s="35">
@@ -3128,7 +3160,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="83">
+      <c r="B24" s="78">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3141,13 +3173,13 @@
       <c r="E24" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="G24" s="66" t="s">
-        <v>277</v>
-      </c>
-      <c r="H24" s="53" t="s">
+      <c r="G24" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="108" t="s">
         <v>165</v>
       </c>
       <c r="I24" s="62" t="s">
@@ -3166,7 +3198,7 @@
       <c r="M24" s="30">
         <v>6</v>
       </c>
-      <c r="N24" s="77" t="s">
+      <c r="N24" s="72" t="s">
         <v>224</v>
       </c>
       <c r="O24" s="37">
@@ -3181,7 +3213,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="83">
+      <c r="B25" s="78">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3189,22 +3221,22 @@
         <v>26</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E25" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="H25" s="107" t="s">
+        <v>282</v>
+      </c>
+      <c r="I25" s="61" t="s">
         <v>286</v>
-      </c>
-      <c r="G25" s="63" t="s">
-        <v>276</v>
-      </c>
-      <c r="H25" s="52" t="s">
-        <v>284</v>
-      </c>
-      <c r="I25" s="61" t="s">
-        <v>288</v>
       </c>
       <c r="J25" s="58" t="s">
         <v>215</v>
@@ -3219,7 +3251,7 @@
       <c r="M25" s="31">
         <v>20</v>
       </c>
-      <c r="N25" s="84" t="s">
+      <c r="N25" s="79" t="s">
         <v>224</v>
       </c>
       <c r="O25" s="35">
@@ -3234,62 +3266,58 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="83">
+      <c r="B26" s="78">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="97" t="s">
+      <c r="C26" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="98" t="s">
+      <c r="D26" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="97" t="s">
+      <c r="E26" s="88" t="s">
         <v>214</v>
       </c>
-      <c r="F26" s="97" t="s">
+      <c r="F26" s="89" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="99" t="s">
-        <v>276</v>
-      </c>
-      <c r="H26" s="97" t="s">
+      <c r="G26" s="96" t="s">
+        <v>275</v>
+      </c>
+      <c r="H26" s="109" t="s">
         <v>164</v>
       </c>
-      <c r="I26" s="99" t="s">
-        <v>276</v>
-      </c>
-      <c r="J26" s="97" t="s">
+      <c r="I26" s="90" t="s">
+        <v>275</v>
+      </c>
+      <c r="J26" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="K26" s="100">
+      <c r="K26" s="91">
         <v>1</v>
       </c>
-      <c r="L26" s="101">
+      <c r="L26" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M26" s="101">
+      <c r="M26" s="92">
         <v>7</v>
       </c>
-      <c r="N26" s="102" t="s">
-        <v>275</v>
-      </c>
-      <c r="O26" s="103">
-        <v>0.25</v>
-      </c>
-      <c r="P26" s="103">
+      <c r="N26" s="93"/>
+      <c r="O26" s="94"/>
+      <c r="P26" s="94">
         <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="Q26" s="104" t="s">
-        <v>281</v>
-      </c>
-      <c r="R26" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="95" t="s">
+        <v>294</v>
+      </c>
+      <c r="R26" s="94"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="83">
+      <c r="B27" s="78">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3302,13 +3330,13 @@
       <c r="E27" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="F27" s="52" t="s">
+      <c r="F27" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="63" t="s">
+      <c r="G27" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H27" s="52" t="s">
+      <c r="H27" s="107" t="s">
         <v>169</v>
       </c>
       <c r="I27" s="61" t="s">
@@ -3327,7 +3355,7 @@
       <c r="M27" s="31">
         <v>7</v>
       </c>
-      <c r="N27" s="75" t="s">
+      <c r="N27" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O27" s="35">
@@ -3342,7 +3370,7 @@
     </row>
     <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="83">
+      <c r="B28" s="78">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -3355,13 +3383,13 @@
       <c r="E28" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="53" t="s">
+      <c r="F28" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="G28" s="66" t="s">
+      <c r="G28" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H28" s="53" t="s">
+      <c r="H28" s="108" t="s">
         <v>170</v>
       </c>
       <c r="I28" s="62" t="s">
@@ -3380,7 +3408,7 @@
       <c r="M28" s="36">
         <v>10</v>
       </c>
-      <c r="N28" s="77" t="s">
+      <c r="N28" s="72" t="s">
         <v>224</v>
       </c>
       <c r="O28" s="37">
@@ -3395,7 +3423,7 @@
     </row>
     <row r="29" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="83">
+      <c r="B29" s="78">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3408,13 +3436,13 @@
       <c r="E29" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="F29" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="63" t="s">
+      <c r="G29" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="H29" s="107" t="s">
         <v>171</v>
       </c>
       <c r="I29" s="61" t="s">
@@ -3433,7 +3461,7 @@
       <c r="M29" s="31">
         <v>10</v>
       </c>
-      <c r="N29" s="75" t="s">
+      <c r="N29" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O29" s="35">
@@ -3448,7 +3476,7 @@
     </row>
     <row r="30" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="83">
+      <c r="B30" s="78">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -3461,13 +3489,13 @@
       <c r="E30" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="G30" s="66" t="s">
+      <c r="G30" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H30" s="53" t="s">
+      <c r="H30" s="108" t="s">
         <v>161</v>
       </c>
       <c r="I30" s="62" t="s">
@@ -3486,7 +3514,7 @@
       <c r="M30" s="30">
         <v>10</v>
       </c>
-      <c r="N30" s="76" t="s">
+      <c r="N30" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O30" s="34">
@@ -3501,7 +3529,7 @@
     </row>
     <row r="31" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="83">
+      <c r="B31" s="78">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3514,13 +3542,13 @@
       <c r="E31" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F31" s="52" t="s">
+      <c r="F31" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="63" t="s">
+      <c r="G31" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H31" s="52" t="s">
+      <c r="H31" s="107" t="s">
         <v>161</v>
       </c>
       <c r="I31" s="61" t="s">
@@ -3539,7 +3567,7 @@
       <c r="M31" s="31">
         <v>50</v>
       </c>
-      <c r="N31" s="75" t="s">
+      <c r="N31" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O31" s="35">
@@ -3554,7 +3582,7 @@
     </row>
     <row r="32" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="83">
+      <c r="B32" s="78">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -3567,11 +3595,11 @@
       <c r="E32" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="G32" s="62"/>
-      <c r="H32" s="53" t="s">
+      <c r="G32" s="53"/>
+      <c r="H32" s="108" t="s">
         <v>172</v>
       </c>
       <c r="I32" s="62" t="s">
@@ -3590,7 +3618,7 @@
       <c r="M32" s="36">
         <v>10</v>
       </c>
-      <c r="N32" s="77" t="s">
+      <c r="N32" s="72" t="s">
         <v>224</v>
       </c>
       <c r="O32" s="37">
@@ -3605,7 +3633,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="83">
+      <c r="B33" s="78">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3618,13 +3646,13 @@
       <c r="E33" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="68" t="s">
+      <c r="F33" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="61" t="s">
+      <c r="G33" s="52" t="s">
         <v>247</v>
       </c>
-      <c r="H33" s="52" t="s">
+      <c r="H33" s="107" t="s">
         <v>173</v>
       </c>
       <c r="I33" s="61" t="s">
@@ -3643,7 +3671,7 @@
       <c r="M33" s="31">
         <v>50</v>
       </c>
-      <c r="N33" s="75" t="s">
+      <c r="N33" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O33" s="35">
@@ -3658,7 +3686,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="83">
+      <c r="B34" s="78">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -3671,13 +3699,13 @@
       <c r="E34" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="F34" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="62" t="s">
+      <c r="G34" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="H34" s="53" t="s">
+      <c r="H34" s="108" t="s">
         <v>173</v>
       </c>
       <c r="I34" s="62" t="s">
@@ -3696,7 +3724,7 @@
       <c r="M34" s="30">
         <v>10</v>
       </c>
-      <c r="N34" s="76" t="s">
+      <c r="N34" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O34" s="34">
@@ -3711,30 +3739,30 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="83">
+      <c r="B35" s="78">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="85" t="s">
+      <c r="D35" s="61" t="s">
+        <v>287</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>288</v>
+      </c>
+      <c r="F35" s="61" t="s">
         <v>289</v>
       </c>
-      <c r="E35" s="86" t="s">
+      <c r="G35" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="H35" s="110" t="s">
         <v>290</v>
       </c>
-      <c r="F35" s="86" t="s">
+      <c r="I35" s="61" t="s">
         <v>291</v>
-      </c>
-      <c r="G35" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="H35" s="86" t="s">
-        <v>292</v>
-      </c>
-      <c r="I35" s="61" t="s">
-        <v>293</v>
       </c>
       <c r="J35" s="52" t="s">
         <v>203</v>
@@ -3749,7 +3777,7 @@
       <c r="M35" s="31">
         <v>50</v>
       </c>
-      <c r="N35" s="84" t="s">
+      <c r="N35" s="79" t="s">
         <v>224</v>
       </c>
       <c r="O35" s="35">
@@ -3764,7 +3792,7 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="83">
+      <c r="B36" s="78">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -3777,13 +3805,13 @@
       <c r="E36" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="F36" s="53" t="s">
+      <c r="F36" s="62" t="s">
         <v>270</v>
       </c>
-      <c r="G36" s="66" t="s">
+      <c r="G36" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H36" s="53" t="s">
+      <c r="H36" s="108" t="s">
         <v>163</v>
       </c>
       <c r="I36" s="62" t="s">
@@ -3802,7 +3830,7 @@
       <c r="M36" s="30">
         <v>100</v>
       </c>
-      <c r="N36" s="76" t="s">
+      <c r="N36" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O36" s="34">
@@ -3817,7 +3845,7 @@
     </row>
     <row r="37" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="83">
+      <c r="B37" s="78">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -3830,13 +3858,13 @@
       <c r="E37" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="F37" s="52" t="s">
+      <c r="F37" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="G37" s="63" t="s">
+      <c r="G37" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H37" s="52" t="s">
+      <c r="H37" s="107" t="s">
         <v>163</v>
       </c>
       <c r="I37" s="61" t="s">
@@ -3855,7 +3883,7 @@
       <c r="M37" s="31">
         <v>100</v>
       </c>
-      <c r="N37" s="75" t="s">
+      <c r="N37" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O37" s="35">
@@ -3870,7 +3898,7 @@
     </row>
     <row r="38" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="83">
+      <c r="B38" s="78">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -3883,13 +3911,13 @@
       <c r="E38" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="F38" s="53" t="s">
+      <c r="F38" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="G38" s="66" t="s">
+      <c r="G38" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H38" s="53" t="s">
+      <c r="H38" s="108" t="s">
         <v>174</v>
       </c>
       <c r="I38" s="62" t="s">
@@ -3908,7 +3936,7 @@
       <c r="M38" s="30">
         <v>100</v>
       </c>
-      <c r="N38" s="76" t="s">
+      <c r="N38" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O38" s="34">
@@ -3923,7 +3951,7 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="83">
+      <c r="B39" s="78">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -3936,13 +3964,13 @@
       <c r="E39" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="F39" s="68" t="s">
+      <c r="F39" s="116" t="s">
         <v>148</v>
       </c>
-      <c r="G39" s="61" t="s">
+      <c r="G39" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="H39" s="52" t="s">
+      <c r="H39" s="107" t="s">
         <v>175</v>
       </c>
       <c r="I39" s="61" t="s">
@@ -3961,7 +3989,7 @@
       <c r="M39" s="31">
         <v>100</v>
       </c>
-      <c r="N39" s="75" t="s">
+      <c r="N39" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O39" s="35">
@@ -3976,7 +4004,7 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="83">
+      <c r="B40" s="78">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -3989,13 +4017,13 @@
       <c r="E40" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="F40" s="69" t="s">
+      <c r="F40" s="117" t="s">
         <v>149</v>
       </c>
-      <c r="G40" s="62" t="s">
+      <c r="G40" s="53" t="s">
         <v>256</v>
       </c>
-      <c r="H40" s="53" t="s">
+      <c r="H40" s="108" t="s">
         <v>175</v>
       </c>
       <c r="I40" s="62" t="s">
@@ -4014,7 +4042,7 @@
       <c r="M40" s="30">
         <v>100</v>
       </c>
-      <c r="N40" s="76" t="s">
+      <c r="N40" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O40" s="34">
@@ -4029,7 +4057,7 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="83">
+      <c r="B41" s="78">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -4042,13 +4070,13 @@
       <c r="E41" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="68" t="s">
+      <c r="F41" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="61" t="s">
+      <c r="G41" s="52" t="s">
         <v>258</v>
       </c>
-      <c r="H41" s="52" t="s">
+      <c r="H41" s="107" t="s">
         <v>176</v>
       </c>
       <c r="I41" s="61" t="s">
@@ -4067,7 +4095,7 @@
       <c r="M41" s="31">
         <v>100</v>
       </c>
-      <c r="N41" s="75" t="s">
+      <c r="N41" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O41" s="35">
@@ -4082,7 +4110,7 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="83">
+      <c r="B42" s="78">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -4095,13 +4123,13 @@
       <c r="E42" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="F42" s="53" t="s">
+      <c r="F42" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="G42" s="66" t="s">
+      <c r="G42" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H42" s="53" t="s">
+      <c r="H42" s="108" t="s">
         <v>163</v>
       </c>
       <c r="I42" s="62" t="s">
@@ -4120,7 +4148,7 @@
       <c r="M42" s="30">
         <v>50</v>
       </c>
-      <c r="N42" s="76" t="s">
+      <c r="N42" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O42" s="34">
@@ -4135,7 +4163,7 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="83">
+      <c r="B43" s="78">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -4148,11 +4176,11 @@
       <c r="E43" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="F43" s="58" t="s">
+      <c r="F43" s="63" t="s">
         <v>216</v>
       </c>
-      <c r="G43" s="63"/>
-      <c r="H43" s="58" t="s">
+      <c r="G43" s="58"/>
+      <c r="H43" s="111" t="s">
         <v>216</v>
       </c>
       <c r="I43" s="63" t="s">
@@ -4168,24 +4196,24 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="M43" s="70" t="s">
+      <c r="M43" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="N43" s="70" t="s">
+      <c r="N43" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="O43" s="70" t="s">
+      <c r="O43" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="P43" s="70" t="s">
+      <c r="P43" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="Q43" s="70"/>
-      <c r="R43" s="70"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
     </row>
     <row r="44" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="83">
+      <c r="B44" s="78">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -4198,13 +4226,13 @@
       <c r="E44" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F44" s="53" t="s">
+      <c r="F44" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="G44" s="66" t="s">
+      <c r="G44" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H44" s="53" t="s">
+      <c r="H44" s="108" t="s">
         <v>177</v>
       </c>
       <c r="I44" s="62" t="s">
@@ -4223,7 +4251,7 @@
       <c r="M44" s="30">
         <v>10</v>
       </c>
-      <c r="N44" s="76" t="s">
+      <c r="N44" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O44" s="34">
@@ -4238,62 +4266,58 @@
     </row>
     <row r="45" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="83">
+      <c r="B45" s="78">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="97" t="s">
+      <c r="C45" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="98" t="s">
+      <c r="D45" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="E45" s="97" t="s">
+      <c r="E45" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="F45" s="97" t="s">
+      <c r="F45" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="G45" s="99" t="s">
+      <c r="G45" s="96" t="s">
         <v>272</v>
       </c>
-      <c r="H45" s="97" t="s">
+      <c r="H45" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="I45" s="99" t="s">
+      <c r="I45" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="J45" s="105" t="s">
+      <c r="J45" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="K45" s="100">
+      <c r="K45" s="91">
         <v>1</v>
       </c>
-      <c r="L45" s="101">
+      <c r="L45" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M45" s="101">
+      <c r="M45" s="92">
         <v>6</v>
       </c>
-      <c r="N45" s="102" t="s">
-        <v>275</v>
-      </c>
-      <c r="O45" s="103">
-        <v>3.2</v>
-      </c>
-      <c r="P45" s="103">
+      <c r="N45" s="93"/>
+      <c r="O45" s="94"/>
+      <c r="P45" s="94">
         <f t="shared" si="2"/>
-        <v>19.200000000000003</v>
-      </c>
-      <c r="Q45" s="104" t="s">
-        <v>281</v>
-      </c>
-      <c r="R45" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="95" t="s">
+        <v>294</v>
+      </c>
+      <c r="R45" s="94"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="83">
+      <c r="B46" s="78">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -4306,13 +4330,13 @@
       <c r="E46" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="F46" s="53" t="s">
+      <c r="F46" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="G46" s="66" t="s">
+      <c r="G46" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H46" s="53" t="s">
+      <c r="H46" s="108" t="s">
         <v>179</v>
       </c>
       <c r="I46" s="62" t="s">
@@ -4331,7 +4355,7 @@
       <c r="M46" s="30">
         <v>6</v>
       </c>
-      <c r="N46" s="76" t="s">
+      <c r="N46" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O46" s="34">
@@ -4346,172 +4370,162 @@
     </row>
     <row r="47" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="83">
+      <c r="B47" s="78">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="97" t="s">
+      <c r="C47" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="98" t="s">
+      <c r="D47" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="97" t="s">
+      <c r="E47" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="F47" s="97" t="s">
+      <c r="F47" s="89" t="s">
         <v>154</v>
       </c>
-      <c r="G47" s="99" t="s">
+      <c r="G47" s="96" t="s">
         <v>215</v>
       </c>
-      <c r="H47" s="97" t="s">
+      <c r="H47" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="I47" s="99" t="s">
+      <c r="I47" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="J47" s="105" t="s">
+      <c r="J47" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="K47" s="100">
+      <c r="K47" s="91">
         <v>1</v>
       </c>
-      <c r="L47" s="101">
+      <c r="L47" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M47" s="101">
+      <c r="M47" s="92">
         <v>6</v>
       </c>
-      <c r="N47" s="102" t="s">
-        <v>275</v>
-      </c>
-      <c r="O47" s="103">
-        <v>1.8</v>
-      </c>
-      <c r="P47" s="103">
+      <c r="N47" s="93"/>
+      <c r="O47" s="94"/>
+      <c r="P47" s="94">
         <f t="shared" si="2"/>
-        <v>10.8</v>
-      </c>
-      <c r="Q47" s="104" t="s">
-        <v>281</v>
-      </c>
-      <c r="R47" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="95"/>
+      <c r="R47" s="94"/>
     </row>
     <row r="48" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="83">
+      <c r="B48" s="78">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="88" t="s">
+      <c r="C48" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="89" t="s">
+      <c r="D48" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="E48" s="88" t="s">
+      <c r="E48" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="88" t="s">
+      <c r="F48" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="G48" s="90" t="s">
+      <c r="G48" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="H48" s="88" t="s">
+      <c r="H48" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="I48" s="89" t="s">
+      <c r="I48" s="81" t="s">
         <v>262</v>
       </c>
-      <c r="J48" s="91" t="s">
+      <c r="J48" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="K48" s="92">
+      <c r="K48" s="83">
         <v>1</v>
       </c>
-      <c r="L48" s="93">
+      <c r="L48" s="84">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M48" s="93">
+      <c r="M48" s="84">
         <v>6</v>
       </c>
-      <c r="N48" s="94" t="s">
+      <c r="N48" s="85" t="s">
         <v>224</v>
       </c>
-      <c r="O48" s="95">
+      <c r="O48" s="86">
         <v>12.0892</v>
       </c>
-      <c r="P48" s="95">
+      <c r="P48" s="86">
         <f t="shared" si="2"/>
         <v>72.535200000000003</v>
       </c>
-      <c r="Q48" s="96" t="s">
-        <v>294</v>
-      </c>
-      <c r="R48" s="95"/>
+      <c r="Q48" s="87" t="s">
+        <v>292</v>
+      </c>
+      <c r="R48" s="86"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="83">
+      <c r="B49" s="78">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="97" t="s">
+      <c r="C49" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D49" s="98" t="s">
+      <c r="D49" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="E49" s="97" t="s">
+      <c r="E49" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="F49" s="97" t="s">
+      <c r="F49" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="G49" s="99" t="s">
+      <c r="G49" s="96" t="s">
         <v>215</v>
       </c>
-      <c r="H49" s="97" t="s">
+      <c r="H49" s="109" t="s">
         <v>182</v>
       </c>
-      <c r="I49" s="99" t="s">
+      <c r="I49" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="J49" s="105" t="s">
+      <c r="J49" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="K49" s="100">
+      <c r="K49" s="91">
         <v>1</v>
       </c>
-      <c r="L49" s="101">
+      <c r="L49" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M49" s="101">
+      <c r="M49" s="92">
         <v>6</v>
       </c>
-      <c r="N49" s="102" t="s">
-        <v>275</v>
-      </c>
-      <c r="O49" s="103">
-        <v>11.45</v>
-      </c>
-      <c r="P49" s="103">
+      <c r="N49" s="93"/>
+      <c r="O49" s="94"/>
+      <c r="P49" s="94">
         <f t="shared" si="2"/>
-        <v>68.699999999999989</v>
-      </c>
-      <c r="Q49" s="104" t="s">
-        <v>281</v>
-      </c>
-      <c r="R49" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="95" t="s">
+        <v>294</v>
+      </c>
+      <c r="R49" s="94"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="83">
+      <c r="B50" s="78">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -4524,13 +4538,13 @@
       <c r="E50" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="F50" s="53" t="s">
+      <c r="F50" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="G50" s="66" t="s">
+      <c r="G50" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H50" s="53" t="s">
+      <c r="H50" s="108" t="s">
         <v>183</v>
       </c>
       <c r="I50" s="62" t="s">
@@ -4549,7 +4563,7 @@
       <c r="M50" s="30">
         <v>6</v>
       </c>
-      <c r="N50" s="76" t="s">
+      <c r="N50" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O50" s="34">
@@ -4564,7 +4578,7 @@
     </row>
     <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="83">
+      <c r="B51" s="78">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -4577,13 +4591,13 @@
       <c r="E51" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="G51" s="63" t="s">
+      <c r="G51" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H51" s="52" t="s">
+      <c r="H51" s="107" t="s">
         <v>184</v>
       </c>
       <c r="I51" s="61" t="s">
@@ -4602,7 +4616,7 @@
       <c r="M51" s="31">
         <v>6</v>
       </c>
-      <c r="N51" s="75" t="s">
+      <c r="N51" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O51" s="35">
@@ -4617,7 +4631,7 @@
     </row>
     <row r="52" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="83">
+      <c r="B52" s="78">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -4630,13 +4644,13 @@
       <c r="E52" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="F52" s="53" t="s">
+      <c r="F52" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="G52" s="66" t="s">
+      <c r="G52" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H52" s="53" t="s">
+      <c r="H52" s="108" t="s">
         <v>185</v>
       </c>
       <c r="I52" s="62" t="s">
@@ -4655,7 +4669,7 @@
       <c r="M52" s="30">
         <v>10</v>
       </c>
-      <c r="N52" s="76" t="s">
+      <c r="N52" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O52" s="34">
@@ -4670,7 +4684,7 @@
     </row>
     <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="83">
+      <c r="B53" s="78">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -4683,13 +4697,13 @@
       <c r="E53" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="61" t="s">
         <v>129</v>
       </c>
-      <c r="G53" s="63" t="s">
+      <c r="G53" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="H53" s="52" t="s">
+      <c r="H53" s="107" t="s">
         <v>186</v>
       </c>
       <c r="I53" s="61" t="s">
@@ -4708,7 +4722,7 @@
       <c r="M53" s="31">
         <v>11</v>
       </c>
-      <c r="N53" s="75" t="s">
+      <c r="N53" s="70" t="s">
         <v>224</v>
       </c>
       <c r="O53" s="35">
@@ -4723,7 +4737,7 @@
     </row>
     <row r="54" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="83">
+      <c r="B54" s="78">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -4736,13 +4750,13 @@
       <c r="E54" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="53" t="s">
+      <c r="F54" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="G54" s="66" t="s">
+      <c r="G54" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="H54" s="53" t="s">
+      <c r="H54" s="108" t="s">
         <v>186</v>
       </c>
       <c r="I54" s="62" t="s">
@@ -4761,7 +4775,7 @@
       <c r="M54" s="30">
         <v>10</v>
       </c>
-      <c r="N54" s="76" t="s">
+      <c r="N54" s="71" t="s">
         <v>224</v>
       </c>
       <c r="O54" s="34">
@@ -4776,32 +4790,32 @@
     </row>
     <row r="55" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="B55" s="83">
+      <c r="B55" s="78">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="73" t="s">
+      <c r="C55" s="68" t="s">
         <v>56</v>
       </c>
       <c r="D55" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="E55" s="73" t="s">
+      <c r="E55" s="118" t="s">
         <v>214</v>
       </c>
-      <c r="F55" s="73" t="s">
+      <c r="F55" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="G55" s="67" t="s">
+      <c r="G55" s="115" t="s">
         <v>215</v>
       </c>
-      <c r="H55" s="73" t="s">
+      <c r="H55" s="113" t="s">
         <v>187</v>
       </c>
       <c r="I55" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="J55" s="73" t="s">
+      <c r="J55" s="68" t="s">
         <v>213</v>
       </c>
       <c r="K55" s="57">
@@ -4814,7 +4828,7 @@
       <c r="M55" s="45">
         <v>10</v>
       </c>
-      <c r="N55" s="78" t="s">
+      <c r="N55" s="73" t="s">
         <v>224</v>
       </c>
       <c r="O55" s="46">
@@ -4835,24 +4849,24 @@
       </c>
       <c r="D56" s="49"/>
       <c r="E56" s="50"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="71"/>
-      <c r="K56" s="71"/>
-      <c r="L56" s="71"/>
-      <c r="M56" s="110" t="s">
-        <v>278</v>
-      </c>
-      <c r="N56" s="111"/>
-      <c r="O56" s="111"/>
-      <c r="P56" s="80">
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="66"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="66"/>
+      <c r="M56" s="101" t="s">
+        <v>277</v>
+      </c>
+      <c r="N56" s="102"/>
+      <c r="O56" s="102"/>
+      <c r="P56" s="75">
         <f>SUM(P10:P55)</f>
-        <v>256.46360000000004</v>
-      </c>
-      <c r="Q56" s="71"/>
-      <c r="R56" s="72"/>
+        <v>156.01360000000003</v>
+      </c>
+      <c r="Q56" s="66"/>
+      <c r="R56" s="67"/>
     </row>
     <row r="57" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
@@ -4869,14 +4883,14 @@
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
       <c r="L57" s="43"/>
-      <c r="M57" s="110" t="s">
-        <v>279</v>
-      </c>
-      <c r="N57" s="111"/>
-      <c r="O57" s="111"/>
-      <c r="P57" s="79">
+      <c r="M57" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="N57" s="102"/>
+      <c r="O57" s="102"/>
+      <c r="P57" s="74">
         <f>P56/5</f>
-        <v>51.29272000000001</v>
+        <v>31.202720000000006</v>
       </c>
       <c r="Q57" s="43"/>
       <c r="R57" s="44"/>
@@ -4928,16 +4942,12 @@
     <hyperlink ref="N54" r:id="rId36" xr:uid="{9D7C6330-6521-4E77-B082-7293A2D402F7}"/>
     <hyperlink ref="N55" r:id="rId37" xr:uid="{60E4F958-BD03-4950-AA1A-E5483E7B8267}"/>
     <hyperlink ref="N36" r:id="rId38" xr:uid="{019A488B-4FF7-4C4E-B4AC-B360044B8376}"/>
-    <hyperlink ref="N45" r:id="rId39" xr:uid="{422359C3-822C-4FAA-8878-23A1A61D0F74}"/>
-    <hyperlink ref="N47" r:id="rId40" xr:uid="{1814BF9F-58FE-400D-907F-EAC26C6361E4}"/>
-    <hyperlink ref="N49" r:id="rId41" xr:uid="{1CD03380-9BD7-47D9-B053-5A646F2458CF}"/>
-    <hyperlink ref="N26" r:id="rId42" xr:uid="{3DEFF66E-912E-4F2F-97AB-FACD57B0039F}"/>
-    <hyperlink ref="N23" r:id="rId43" xr:uid="{83A2C1C1-8C25-4D67-A480-302431668718}"/>
-    <hyperlink ref="N25" r:id="rId44" xr:uid="{30D22A24-3F30-4E99-967B-FA4F0FA9B8E8}"/>
-    <hyperlink ref="N35" r:id="rId45" xr:uid="{E6D3A492-9D47-4832-8671-ED5B61C9ACB1}"/>
+    <hyperlink ref="N23" r:id="rId39" xr:uid="{83A2C1C1-8C25-4D67-A480-302431668718}"/>
+    <hyperlink ref="N25" r:id="rId40" xr:uid="{30D22A24-3F30-4E99-967B-FA4F0FA9B8E8}"/>
+    <hyperlink ref="N35" r:id="rId41" xr:uid="{E6D3A492-9D47-4832-8671-ED5B61C9ACB1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId46"/>
-  <drawing r:id="rId47"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
+  <drawing r:id="rId43"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB529AF9-ED5E-4632-946F-077CCFFDF5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="289">
   <si>
     <t>Component list</t>
   </si>
@@ -68,27 +67,15 @@
     <t>C1, C2, C7</t>
   </si>
   <si>
-    <t>C3, C4, C6, C10, C11, C12, C13, C14, C15, C18, C19, C20, C21, C22, C24, C31, C34, C35, C36, C37, C41, C42, C47, C49</t>
-  </si>
-  <si>
     <t>C5</t>
   </si>
   <si>
     <t>C8, C25, C26, C27, C28, C39, C40, C50</t>
   </si>
   <si>
-    <t>C9, C23, C33</t>
-  </si>
-  <si>
-    <t>C16, C30, C32, C43, C45, C46, C48, C51</t>
-  </si>
-  <si>
     <t>C17</t>
   </si>
   <si>
-    <t>C29, C44</t>
-  </si>
-  <si>
     <t>C38</t>
   </si>
   <si>
@@ -116,9 +103,6 @@
     <t>L1</t>
   </si>
   <si>
-    <t>L2</t>
-  </si>
-  <si>
     <t>L3</t>
   </si>
   <si>
@@ -149,12 +133,6 @@
     <t>R4, R5, R6, R12, R18, R19, R22, R23, R25, R27</t>
   </si>
   <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>R8, R13, R14, R15, R16, R17, R26</t>
-  </si>
-  <si>
     <t>R10, R11</t>
   </si>
   <si>
@@ -167,9 +145,6 @@
     <t>SB1, SB2, SB3</t>
   </si>
   <si>
-    <t>SW1</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -248,9 +223,6 @@
     <t>FIXED IND 2.2UH 1.5A 160MOHM SMD</t>
   </si>
   <si>
-    <t>FIXED IND 10UH 360MA 1.32OHM SMD</t>
-  </si>
-  <si>
     <t>500mA 10uH ±20% 320mΩ 0805 Inductors (SMD) ROHS</t>
   </si>
   <si>
@@ -275,9 +247,6 @@
     <t>RES SMD 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>62.5mW Thick Film Resistors 50V ±5% ±200ppm/℃ 1Ω -55℃~+155℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
     <t>RES SMD 100K OHM 1% 1/5W 0402</t>
   </si>
   <si>
@@ -365,9 +334,6 @@
     <t>MAKK2016T2R2M</t>
   </si>
   <si>
-    <t>NLCV25T-100K-EFRD</t>
-  </si>
-  <si>
     <t>Ind0805</t>
   </si>
   <si>
@@ -473,9 +439,6 @@
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
-    <t>FRC0402J1R0 TS</t>
-  </si>
-  <si>
     <t>ERJ-PA2F1003X</t>
   </si>
   <si>
@@ -539,9 +502,6 @@
     <t>XFCN</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>microgate</t>
   </si>
   <si>
@@ -554,9 +514,6 @@
     <t>SunLED</t>
   </si>
   <si>
-    <t>FOJAN</t>
-  </si>
-  <si>
     <t>Panasonic</t>
   </si>
   <si>
@@ -650,9 +607,6 @@
     <t>10K</t>
   </si>
   <si>
-    <t>1R</t>
-  </si>
-  <si>
     <t>100K</t>
   </si>
   <si>
@@ -755,9 +709,6 @@
     <t>C424659</t>
   </si>
   <si>
-    <t>C295388</t>
-  </si>
-  <si>
     <t>C281113</t>
   </si>
   <si>
@@ -788,9 +739,6 @@
     <t>C60490</t>
   </si>
   <si>
-    <t>C2906901</t>
-  </si>
-  <si>
     <t>C226678</t>
   </si>
   <si>
@@ -915,12 +863,45 @@
   </si>
   <si>
     <t xml:space="preserve">Need Fresh Quote From Custom Supplier </t>
+  </si>
+  <si>
+    <t>C3, C4, C6, C10, C11, C12, C13, C14, C15, C18, C19, C20, C21, C22, C23, C24, C31, C34, C35, C36, C41, C42, C47, C49</t>
+  </si>
+  <si>
+    <t>C9, C33</t>
+  </si>
+  <si>
+    <t>C16, C32, C43, C45, C46, C48, C51</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>CAP CER 100pF 50V C0G 0402</t>
+  </si>
+  <si>
+    <t>Cap 0403</t>
+  </si>
+  <si>
+    <t>GCM1555C1H101JA16D</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>R7, R8, R13, R14, R15, R16, R17, R26</t>
+  </si>
+  <si>
+    <t>SW1, SW2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1135,7 +1116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1497,12 +1478,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1766,6 +1762,48 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1792,46 +1830,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2169,9 +2174,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2203,8 +2208,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="104"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="118"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2220,15 +2225,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="100"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="114"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2252,7 +2257,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="97"/>
+      <c r="R3" s="111"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2276,7 +2281,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="98"/>
+      <c r="R4" s="112"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2300,7 +2305,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="98"/>
+      <c r="R5" s="112"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2320,7 +2325,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="98"/>
+      <c r="R6" s="112"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2340,7 +2345,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="98"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2360,7 +2365,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="98"/>
+      <c r="R8" s="112"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2371,49 +2376,49 @@
         <v>10</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="H9" s="77" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="K9" s="77" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="M9" s="32" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="O9" s="32" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="P9" s="32" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="Q9" s="32" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
@@ -2426,25 +2431,25 @@
         <v>11</v>
       </c>
       <c r="D10" s="60" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" s="114" t="s">
-        <v>215</v>
-      </c>
-      <c r="H10" s="106" t="s">
-        <v>161</v>
+        <v>122</v>
+      </c>
+      <c r="G10" s="106" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" s="98" t="s">
+        <v>149</v>
       </c>
       <c r="I10" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="J10" s="51" t="s">
-        <v>189</v>
+        <v>204</v>
+      </c>
+      <c r="J10" s="121" t="s">
+        <v>175</v>
       </c>
       <c r="K10" s="54">
         <v>3</v>
@@ -2457,7 +2462,7 @@
         <v>20</v>
       </c>
       <c r="N10" s="69" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O10" s="42">
         <v>7.2800000000000004E-2</v>
@@ -2472,51 +2477,51 @@
     <row r="11" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="78">
-        <f t="shared" ref="B11:B55" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>12</v>
+        <v>278</v>
       </c>
       <c r="D11" s="61" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="F11" s="116" t="s">
-        <v>134</v>
+        <v>91</v>
+      </c>
+      <c r="F11" s="108" t="s">
+        <v>123</v>
       </c>
       <c r="G11" s="52" t="s">
-        <v>225</v>
-      </c>
-      <c r="H11" s="107" t="s">
-        <v>161</v>
+        <v>210</v>
+      </c>
+      <c r="H11" s="99" t="s">
+        <v>149</v>
       </c>
       <c r="I11" s="61" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="K11" s="55">
         <v>24</v>
       </c>
       <c r="L11" s="31">
-        <f t="shared" ref="L11:L55" si="1">K11*5</f>
+        <f t="shared" ref="L11:L54" si="1">K11*5</f>
         <v>120</v>
       </c>
       <c r="M11" s="31">
         <v>150</v>
       </c>
       <c r="N11" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O11" s="35">
         <v>7.3000000000000001E-3</v>
       </c>
       <c r="P11" s="35">
-        <f t="shared" ref="P11:P55" si="2">O11*M11</f>
+        <f t="shared" ref="P11:P54" si="2">O11*M11</f>
         <v>1.095</v>
       </c>
       <c r="Q11" s="35"/>
@@ -2529,28 +2534,28 @@
         <v>3</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F12" s="62" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" s="108" t="s">
-        <v>162</v>
+        <v>200</v>
+      </c>
+      <c r="H12" s="100" t="s">
+        <v>150</v>
       </c>
       <c r="I12" s="62" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="K12" s="56">
         <v>1</v>
@@ -2563,7 +2568,7 @@
         <v>20</v>
       </c>
       <c r="N12" s="71" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O12" s="34">
         <v>1.3599999999999999E-2</v>
@@ -2582,28 +2587,28 @@
         <v>4</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="61" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H13" s="107" t="s">
-        <v>163</v>
+        <v>200</v>
+      </c>
+      <c r="H13" s="99" t="s">
+        <v>151</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="K13" s="55">
         <v>8</v>
@@ -2616,7 +2621,7 @@
         <v>100</v>
       </c>
       <c r="N13" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O13" s="35">
         <v>1.4E-3</v>
@@ -2635,41 +2640,41 @@
         <v>5</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>15</v>
+        <v>279</v>
       </c>
       <c r="D14" s="62" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F14" s="62" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H14" s="108" t="s">
-        <v>164</v>
+        <v>200</v>
+      </c>
+      <c r="H14" s="100" t="s">
+        <v>152</v>
       </c>
       <c r="I14" s="62" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="K14" s="56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="30">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M14" s="30">
         <v>50</v>
       </c>
       <c r="N14" s="72" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O14" s="34">
         <v>1.8499999999999999E-2</v>
@@ -2688,41 +2693,41 @@
         <v>6</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>16</v>
+        <v>280</v>
       </c>
       <c r="D15" s="61" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F15" s="61" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G15" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="99" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="H15" s="107" t="s">
-        <v>163</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>230</v>
-      </c>
       <c r="J15" s="52" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="K15" s="55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L15" s="31">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M15" s="31">
         <v>50</v>
       </c>
       <c r="N15" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O15" s="35">
         <v>6.4000000000000003E-3</v>
@@ -2741,28 +2746,28 @@
         <v>7</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F16" s="62" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H16" s="108" t="s">
-        <v>161</v>
+        <v>200</v>
+      </c>
+      <c r="H16" s="100" t="s">
+        <v>149</v>
       </c>
       <c r="I16" s="62" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="K16" s="56">
         <v>1</v>
@@ -2775,7 +2780,7 @@
         <v>10</v>
       </c>
       <c r="N16" s="72" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O16" s="37">
         <v>4.8899999999999999E-2</v>
@@ -2789,56 +2794,52 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="78">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>233</v>
-      </c>
-      <c r="E17" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="G17" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H17" s="107" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="61" t="s">
-        <v>232</v>
-      </c>
-      <c r="J17" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="K17" s="55">
-        <v>2</v>
-      </c>
-      <c r="L17" s="31">
+      <c r="B17" s="78"/>
+      <c r="C17" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="D17" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="G17" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="I17" s="119">
+        <v>1</v>
+      </c>
+      <c r="J17" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="K17" s="56">
+        <v>1</v>
+      </c>
+      <c r="L17" s="30">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M17" s="31">
-        <v>100</v>
-      </c>
-      <c r="N17" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O17" s="35">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="P17" s="35">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
+        <v>5</v>
+      </c>
+      <c r="M17" s="36">
+        <v>50</v>
+      </c>
+      <c r="N17" s="120" t="s">
+        <v>209</v>
+      </c>
+      <c r="O17" s="37">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="P17" s="34">
+        <v>0.48</v>
+      </c>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -2846,52 +2847,52 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="62" t="s">
-        <v>140</v>
-      </c>
-      <c r="G18" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H18" s="108" t="s">
-        <v>161</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="J18" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="K18" s="56">
+      <c r="C18" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H18" s="99" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="J18" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="K18" s="55">
         <v>1</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="31">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M18" s="30">
-        <v>20</v>
-      </c>
-      <c r="N18" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O18" s="34">
-        <v>3.0300000000000001E-2</v>
-      </c>
-      <c r="P18" s="34">
+      <c r="M18" s="31">
+        <v>100</v>
+      </c>
+      <c r="N18" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O18" s="35">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="P18" s="35">
         <f t="shared" si="2"/>
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
+        <v>0.16</v>
+      </c>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -2899,52 +2900,52 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="F19" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H19" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="I19" s="61" t="s">
-        <v>236</v>
-      </c>
-      <c r="J19" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="K19" s="55">
+      <c r="C19" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H19" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="J19" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="K19" s="56">
         <v>1</v>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M19" s="31">
-        <v>10</v>
-      </c>
-      <c r="N19" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O19" s="35">
-        <v>9.2899999999999996E-2</v>
-      </c>
-      <c r="P19" s="35">
+      <c r="M19" s="30">
+        <v>20</v>
+      </c>
+      <c r="N19" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O19" s="34">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P19" s="34">
         <f t="shared" si="2"/>
-        <v>0.92899999999999994</v>
-      </c>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2952,52 +2953,52 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="F20" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H20" s="108" t="s">
-        <v>166</v>
-      </c>
-      <c r="I20" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="J20" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="K20" s="56">
+      <c r="C20" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="F20" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="99" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>221</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="K20" s="55">
         <v>1</v>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="31">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M20" s="30">
-        <v>6</v>
-      </c>
-      <c r="N20" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O20" s="34">
-        <v>2.3371</v>
-      </c>
-      <c r="P20" s="34">
+      <c r="M20" s="31">
+        <v>10</v>
+      </c>
+      <c r="N20" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O20" s="35">
+        <v>9.2899999999999996E-2</v>
+      </c>
+      <c r="P20" s="35">
         <f t="shared" si="2"/>
-        <v>14.022600000000001</v>
-      </c>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
+        <v>0.92899999999999994</v>
+      </c>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -3005,158 +3006,158 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="F21" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H21" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="I21" s="61" t="s">
-        <v>238</v>
-      </c>
-      <c r="J21" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="K21" s="55">
+      <c r="C21" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H21" s="100" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="62" t="s">
+        <v>222</v>
+      </c>
+      <c r="J21" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="K21" s="56">
         <v>1</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M21" s="31">
-        <v>20</v>
-      </c>
-      <c r="N21" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O21" s="35">
-        <v>4.8399999999999999E-2</v>
-      </c>
-      <c r="P21" s="35">
+      <c r="M21" s="30">
+        <v>6</v>
+      </c>
+      <c r="N21" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O21" s="34">
+        <v>2.3371</v>
+      </c>
+      <c r="P21" s="34">
         <f t="shared" si="2"/>
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-    </row>
-    <row r="22" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+        <v>14.022600000000001</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="78">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="F22" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H22" s="108" t="s">
-        <v>168</v>
-      </c>
-      <c r="I22" s="62" t="s">
-        <v>239</v>
-      </c>
-      <c r="J22" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="K22" s="56">
+      <c r="C22" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="99" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="K22" s="55">
         <v>1</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M22" s="30">
-        <v>6</v>
-      </c>
-      <c r="N22" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O22" s="34">
-        <v>0.18659999999999999</v>
-      </c>
-      <c r="P22" s="34">
+      <c r="M22" s="31">
+        <v>20</v>
+      </c>
+      <c r="N22" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O22" s="35">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="P22" s="35">
         <f t="shared" si="2"/>
-        <v>1.1195999999999999</v>
-      </c>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+    </row>
+    <row r="23" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="78">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="105" t="s">
-        <v>280</v>
-      </c>
-      <c r="E23" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="63" t="s">
-        <v>281</v>
-      </c>
-      <c r="G23" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H23" s="107" t="s">
-        <v>282</v>
-      </c>
-      <c r="I23" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="J23" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="K23" s="55">
+      <c r="C23" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H23" s="100" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="62" t="s">
+        <v>224</v>
+      </c>
+      <c r="J23" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="K23" s="56">
         <v>1</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M23" s="31">
-        <v>10</v>
-      </c>
-      <c r="N23" s="79" t="s">
-        <v>224</v>
-      </c>
-      <c r="O23" s="35">
-        <v>4.3099999999999999E-2</v>
-      </c>
-      <c r="P23" s="35">
+      <c r="M23" s="30">
+        <v>6</v>
+      </c>
+      <c r="N23" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O23" s="34">
+        <v>0.18659999999999999</v>
+      </c>
+      <c r="P23" s="34">
         <f t="shared" si="2"/>
-        <v>0.43099999999999999</v>
-      </c>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
+        <v>1.1195999999999999</v>
+      </c>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -3164,52 +3165,52 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="62" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="F24" s="62" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="59" t="s">
-        <v>276</v>
-      </c>
-      <c r="H24" s="108" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="J24" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="K24" s="56">
+      <c r="C24" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="97" t="s">
+        <v>263</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="G24" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H24" s="99" t="s">
+        <v>265</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="J24" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="K24" s="55">
         <v>1</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M24" s="30">
-        <v>6</v>
-      </c>
-      <c r="N24" s="72" t="s">
-        <v>224</v>
-      </c>
-      <c r="O24" s="37">
-        <v>0.1832</v>
-      </c>
-      <c r="P24" s="34">
+      <c r="M24" s="31">
+        <v>10</v>
+      </c>
+      <c r="N24" s="79" t="s">
+        <v>209</v>
+      </c>
+      <c r="O24" s="35">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="P24" s="35">
         <f t="shared" si="2"/>
-        <v>1.0992</v>
-      </c>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -3217,52 +3218,52 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="F25" s="63" t="s">
-        <v>284</v>
-      </c>
-      <c r="G25" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="H25" s="107" t="s">
-        <v>282</v>
-      </c>
-      <c r="I25" s="61" t="s">
-        <v>286</v>
-      </c>
-      <c r="J25" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" s="55">
+      <c r="C25" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="H25" s="100" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="62" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="K25" s="56">
         <v>1</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M25" s="31">
-        <v>20</v>
-      </c>
-      <c r="N25" s="79" t="s">
-        <v>224</v>
-      </c>
-      <c r="O25" s="35">
-        <v>2.29E-2</v>
-      </c>
-      <c r="P25" s="35">
+      <c r="M25" s="30">
+        <v>6</v>
+      </c>
+      <c r="N25" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="O25" s="37">
+        <v>0.1832</v>
+      </c>
+      <c r="P25" s="34">
         <f t="shared" si="2"/>
-        <v>0.45800000000000002</v>
-      </c>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
+        <v>1.0992</v>
+      </c>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
@@ -3270,50 +3271,52 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="89" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="88" t="s">
-        <v>214</v>
-      </c>
-      <c r="F26" s="89" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="96" t="s">
-        <v>275</v>
-      </c>
-      <c r="H26" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="I26" s="90" t="s">
-        <v>275</v>
-      </c>
-      <c r="J26" s="88" t="s">
-        <v>198</v>
-      </c>
-      <c r="K26" s="91">
+      <c r="C26" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>258</v>
+      </c>
+      <c r="H26" s="99" t="s">
+        <v>265</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="K26" s="55">
         <v>1</v>
       </c>
-      <c r="L26" s="92">
+      <c r="L26" s="31">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M26" s="92">
-        <v>7</v>
-      </c>
-      <c r="N26" s="93"/>
-      <c r="O26" s="94"/>
-      <c r="P26" s="94">
+      <c r="M26" s="31">
+        <v>20</v>
+      </c>
+      <c r="N26" s="79" t="s">
+        <v>209</v>
+      </c>
+      <c r="O26" s="35">
+        <v>2.29E-2</v>
+      </c>
+      <c r="P26" s="35">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="95" t="s">
-        <v>294</v>
-      </c>
-      <c r="R26" s="94"/>
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
@@ -3321,52 +3324,50 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="F27" s="61" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H27" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="I27" s="61" t="s">
-        <v>241</v>
-      </c>
-      <c r="J27" s="52" t="s">
+      <c r="C27" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="88" t="s">
         <v>199</v>
       </c>
-      <c r="K27" s="55">
+      <c r="F27" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="96" t="s">
+        <v>258</v>
+      </c>
+      <c r="H27" s="101" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" s="90" t="s">
+        <v>258</v>
+      </c>
+      <c r="J27" s="88" t="s">
+        <v>184</v>
+      </c>
+      <c r="K27" s="91">
         <v>1</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="92">
         <v>7</v>
       </c>
-      <c r="N27" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O27" s="35">
-        <v>0.1575</v>
-      </c>
-      <c r="P27" s="35">
+      <c r="N27" s="93"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94">
         <f t="shared" si="2"/>
-        <v>1.1025</v>
-      </c>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="95" t="s">
+        <v>277</v>
+      </c>
+      <c r="R27" s="94"/>
     </row>
     <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -3375,28 +3376,28 @@
         <v>19</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F28" s="62" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H28" s="108" t="s">
-        <v>170</v>
+        <v>200</v>
+      </c>
+      <c r="H28" s="100" t="s">
+        <v>157</v>
       </c>
       <c r="I28" s="62" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="J28" s="53" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="K28" s="56">
         <v>1</v>
@@ -3409,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="N28" s="72" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O28" s="37">
         <v>4.5699999999999998E-2</v>
@@ -3428,28 +3429,28 @@
         <v>20</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D29" s="61" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F29" s="61" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G29" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H29" s="107" t="s">
-        <v>171</v>
+        <v>200</v>
+      </c>
+      <c r="H29" s="99" t="s">
+        <v>158</v>
       </c>
       <c r="I29" s="61" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="J29" s="52" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="K29" s="55">
         <v>1</v>
@@ -3462,7 +3463,7 @@
         <v>10</v>
       </c>
       <c r="N29" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O29" s="35">
         <v>5.7299999999999997E-2</v>
@@ -3481,28 +3482,28 @@
         <v>21</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D30" s="62" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F30" s="62" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G30" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H30" s="108" t="s">
-        <v>161</v>
+        <v>200</v>
+      </c>
+      <c r="H30" s="100" t="s">
+        <v>149</v>
       </c>
       <c r="I30" s="62" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="K30" s="56">
         <v>1</v>
@@ -3515,7 +3516,7 @@
         <v>10</v>
       </c>
       <c r="N30" s="71" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O30" s="34">
         <v>6.4600000000000005E-2</v>
@@ -3534,28 +3535,28 @@
         <v>22</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F31" s="61" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="G31" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H31" s="107" t="s">
-        <v>161</v>
+        <v>200</v>
+      </c>
+      <c r="H31" s="99" t="s">
+        <v>149</v>
       </c>
       <c r="I31" s="61" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="J31" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="K31" s="55">
         <v>1</v>
@@ -3568,7 +3569,7 @@
         <v>50</v>
       </c>
       <c r="N31" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O31" s="35">
         <v>8.6E-3</v>
@@ -3587,26 +3588,26 @@
         <v>23</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D32" s="62" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F32" s="62" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G32" s="53"/>
-      <c r="H32" s="108" t="s">
-        <v>172</v>
+      <c r="H32" s="100" t="s">
+        <v>159</v>
       </c>
       <c r="I32" s="62" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="K32" s="56">
         <v>1</v>
@@ -3619,7 +3620,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="72" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O32" s="37">
         <v>9.4299999999999995E-2</v>
@@ -3638,28 +3639,28 @@
         <v>24</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="116" t="s">
-        <v>144</v>
+        <v>105</v>
+      </c>
+      <c r="F33" s="108" t="s">
+        <v>133</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="H33" s="107" t="s">
-        <v>173</v>
+        <v>231</v>
+      </c>
+      <c r="H33" s="99" t="s">
+        <v>160</v>
       </c>
       <c r="I33" s="61" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="J33" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="K33" s="55">
         <v>2</v>
@@ -3672,7 +3673,7 @@
         <v>50</v>
       </c>
       <c r="N33" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O33" s="35">
         <v>1.7500000000000002E-2</v>
@@ -3691,28 +3692,28 @@
         <v>25</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="F34" s="117" t="s">
-        <v>145</v>
+        <v>105</v>
+      </c>
+      <c r="F34" s="109" t="s">
+        <v>134</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="H34" s="108" t="s">
-        <v>173</v>
+        <v>233</v>
+      </c>
+      <c r="H34" s="100" t="s">
+        <v>160</v>
       </c>
       <c r="I34" s="62" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="K34" s="56">
         <v>1</v>
@@ -3725,7 +3726,7 @@
         <v>10</v>
       </c>
       <c r="N34" s="71" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O34" s="34">
         <v>5.2400000000000002E-2</v>
@@ -3744,28 +3745,28 @@
         <v>26</v>
       </c>
       <c r="C35" s="52" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="E35" s="52" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="F35" s="61" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="G35" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H35" s="110" t="s">
-        <v>290</v>
+        <v>200</v>
+      </c>
+      <c r="H35" s="102" t="s">
+        <v>273</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="J35" s="52" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="K35" s="55">
         <v>1</v>
@@ -3778,7 +3779,7 @@
         <v>50</v>
       </c>
       <c r="N35" s="79" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O35" s="35">
         <v>1.0500000000000001E-2</v>
@@ -3797,28 +3798,28 @@
         <v>27</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F36" s="62" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="G36" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H36" s="108" t="s">
-        <v>163</v>
+        <v>200</v>
+      </c>
+      <c r="H36" s="100" t="s">
+        <v>151</v>
       </c>
       <c r="I36" s="62" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="J36" s="53" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="K36" s="56">
         <v>4</v>
@@ -3831,7 +3832,7 @@
         <v>100</v>
       </c>
       <c r="N36" s="71" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O36" s="34">
         <v>5.9999999999999995E-4</v>
@@ -3850,28 +3851,28 @@
         <v>28</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F37" s="61" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="G37" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H37" s="107" t="s">
-        <v>163</v>
+        <v>200</v>
+      </c>
+      <c r="H37" s="99" t="s">
+        <v>151</v>
       </c>
       <c r="I37" s="61" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="J37" s="52" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="K37" s="55">
         <v>10</v>
@@ -3884,7 +3885,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="70" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O37" s="35">
         <v>6.9999999999999999E-4</v>
@@ -3896,58 +3897,58 @@
       <c r="Q37" s="35"/>
       <c r="R37" s="35"/>
     </row>
-    <row r="38" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="78">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="62" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="G38" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H38" s="108" t="s">
-        <v>174</v>
-      </c>
-      <c r="I38" s="62" t="s">
-        <v>252</v>
-      </c>
-      <c r="J38" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="K38" s="56">
-        <v>1</v>
-      </c>
-      <c r="L38" s="30">
+      <c r="C38" s="52" t="s">
+        <v>287</v>
+      </c>
+      <c r="D38" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="108" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="H38" s="99" t="s">
+        <v>161</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="J38" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="K38" s="55">
+        <v>8</v>
+      </c>
+      <c r="L38" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M38" s="30">
+        <v>40</v>
+      </c>
+      <c r="M38" s="31">
         <v>100</v>
       </c>
-      <c r="N38" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O38" s="34">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P38" s="34">
+      <c r="N38" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O38" s="35">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="P38" s="35">
         <f t="shared" si="2"/>
-        <v>0.05</v>
-      </c>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
+        <v>0.06</v>
+      </c>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -3955,52 +3956,52 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="61" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="F39" s="116" t="s">
-        <v>148</v>
-      </c>
-      <c r="G39" s="52" t="s">
-        <v>254</v>
-      </c>
-      <c r="H39" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="I39" s="61" t="s">
-        <v>255</v>
-      </c>
-      <c r="J39" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="K39" s="55">
-        <v>7</v>
-      </c>
-      <c r="L39" s="31">
+      <c r="C39" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="H39" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" s="62" t="s">
+        <v>240</v>
+      </c>
+      <c r="J39" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="K39" s="56">
+        <v>2</v>
+      </c>
+      <c r="L39" s="30">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="M39" s="31">
+        <v>10</v>
+      </c>
+      <c r="M39" s="30">
         <v>100</v>
       </c>
-      <c r="N39" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O39" s="35">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="P39" s="35">
+      <c r="N39" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O39" s="34">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="P39" s="34">
         <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
+        <v>0.08</v>
+      </c>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="34"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
@@ -4008,52 +4009,52 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="F40" s="117" t="s">
-        <v>149</v>
-      </c>
-      <c r="G40" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="H40" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="I40" s="62" t="s">
-        <v>257</v>
-      </c>
-      <c r="J40" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="K40" s="56">
+      <c r="C40" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="H40" s="99" t="s">
+        <v>162</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="J40" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="K40" s="55">
         <v>2</v>
       </c>
-      <c r="L40" s="30">
+      <c r="L40" s="31">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M40" s="30">
+      <c r="M40" s="31">
         <v>100</v>
       </c>
-      <c r="N40" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O40" s="34">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="P40" s="34">
+      <c r="N40" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O40" s="35">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="P40" s="35">
         <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
+        <v>0.36</v>
+      </c>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="35"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
@@ -4061,52 +4062,52 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="116" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" s="52" t="s">
-        <v>258</v>
-      </c>
-      <c r="H41" s="107" t="s">
-        <v>176</v>
-      </c>
-      <c r="I41" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="J41" s="52" t="s">
+      <c r="C41" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" s="100" t="s">
+        <v>151</v>
+      </c>
+      <c r="I41" s="62" t="s">
+        <v>236</v>
+      </c>
+      <c r="J41" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="K41" s="56">
+        <v>1</v>
+      </c>
+      <c r="L41" s="30">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M41" s="30">
+        <v>50</v>
+      </c>
+      <c r="N41" s="71" t="s">
         <v>209</v>
       </c>
-      <c r="K41" s="55">
-        <v>2</v>
-      </c>
-      <c r="L41" s="31">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M41" s="31">
-        <v>100</v>
-      </c>
-      <c r="N41" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O41" s="35">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="P41" s="35">
+      <c r="O41" s="34">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="P41" s="34">
         <f t="shared" si="2"/>
-        <v>0.36</v>
-      </c>
-      <c r="Q41" s="35"/>
-      <c r="R41" s="35"/>
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="Q41" s="34"/>
+      <c r="R41" s="34"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
@@ -4114,102 +4115,102 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="E42" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H42" s="108" t="s">
-        <v>163</v>
-      </c>
-      <c r="I42" s="62" t="s">
-        <v>253</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="K42" s="56">
-        <v>1</v>
-      </c>
-      <c r="L42" s="30">
+      <c r="C42" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="58"/>
+      <c r="H42" s="103" t="s">
+        <v>201</v>
+      </c>
+      <c r="I42" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="J42" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="K42" s="55">
+        <v>3</v>
+      </c>
+      <c r="L42" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M42" s="30">
-        <v>50</v>
-      </c>
-      <c r="N42" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O42" s="34">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="P42" s="34">
-        <f t="shared" si="2"/>
-        <v>3.4999999999999996E-2</v>
-      </c>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="M42" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="N42" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="O42" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="P42" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+    </row>
+    <row r="43" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="78">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="61" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="G43" s="58"/>
-      <c r="H43" s="111" t="s">
-        <v>216</v>
-      </c>
-      <c r="I43" s="63" t="s">
-        <v>272</v>
-      </c>
-      <c r="J43" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K43" s="55">
-        <v>3</v>
-      </c>
-      <c r="L43" s="31">
+      <c r="C43" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="D43" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="G43" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H43" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="I43" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="J43" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="K43" s="56">
+        <v>2</v>
+      </c>
+      <c r="L43" s="30">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="M43" s="65" t="s">
-        <v>215</v>
-      </c>
-      <c r="N43" s="65" t="s">
-        <v>216</v>
-      </c>
-      <c r="O43" s="65" t="s">
-        <v>215</v>
-      </c>
-      <c r="P43" s="65" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
+        <v>10</v>
+      </c>
+      <c r="M43" s="30">
+        <v>10</v>
+      </c>
+      <c r="N43" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O43" s="34">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="P43" s="34">
+        <f t="shared" si="2"/>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
     </row>
     <row r="44" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
@@ -4217,156 +4218,152 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="E44" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="F44" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="G44" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H44" s="108" t="s">
-        <v>177</v>
-      </c>
-      <c r="I44" s="62" t="s">
-        <v>260</v>
-      </c>
-      <c r="J44" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="K44" s="56">
+      <c r="C44" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="88" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" s="96" t="s">
+        <v>255</v>
+      </c>
+      <c r="H44" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="I44" s="90" t="s">
+        <v>255</v>
+      </c>
+      <c r="J44" s="96" t="s">
+        <v>201</v>
+      </c>
+      <c r="K44" s="91">
         <v>1</v>
       </c>
-      <c r="L44" s="30">
+      <c r="L44" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M44" s="30">
-        <v>10</v>
-      </c>
-      <c r="N44" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O44" s="34">
-        <v>5.9900000000000002E-2</v>
-      </c>
-      <c r="P44" s="34">
+      <c r="M44" s="92">
+        <v>6</v>
+      </c>
+      <c r="N44" s="93"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94">
         <f t="shared" si="2"/>
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-    </row>
-    <row r="45" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="95" t="s">
+        <v>277</v>
+      </c>
+      <c r="R44" s="94"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="78">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="88" t="s">
-        <v>121</v>
-      </c>
-      <c r="F45" s="89" t="s">
-        <v>152</v>
-      </c>
-      <c r="G45" s="96" t="s">
-        <v>272</v>
-      </c>
-      <c r="H45" s="109" t="s">
-        <v>178</v>
-      </c>
-      <c r="I45" s="90" t="s">
-        <v>272</v>
-      </c>
-      <c r="J45" s="96" t="s">
-        <v>216</v>
-      </c>
-      <c r="K45" s="91">
+      <c r="C45" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="G45" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H45" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="I45" s="62" t="s">
+        <v>244</v>
+      </c>
+      <c r="J45" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="K45" s="56">
         <v>1</v>
       </c>
-      <c r="L45" s="92">
+      <c r="L45" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M45" s="92">
+      <c r="M45" s="30">
         <v>6</v>
       </c>
-      <c r="N45" s="93"/>
-      <c r="O45" s="94"/>
-      <c r="P45" s="94">
+      <c r="N45" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O45" s="34">
+        <v>0.49409999999999998</v>
+      </c>
+      <c r="P45" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="95" t="s">
-        <v>294</v>
-      </c>
-      <c r="R45" s="94"/>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.9645999999999999</v>
+      </c>
+      <c r="Q45" s="34"/>
+      <c r="R45" s="34"/>
+    </row>
+    <row r="46" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="78">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="G46" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H46" s="108" t="s">
-        <v>179</v>
-      </c>
-      <c r="I46" s="62" t="s">
-        <v>261</v>
-      </c>
-      <c r="J46" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="K46" s="56">
+      <c r="C46" s="88" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="89" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="88" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="G46" s="96" t="s">
+        <v>200</v>
+      </c>
+      <c r="H46" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="I46" s="90" t="s">
+        <v>255</v>
+      </c>
+      <c r="J46" s="96" t="s">
+        <v>201</v>
+      </c>
+      <c r="K46" s="91">
         <v>1</v>
       </c>
-      <c r="L46" s="30">
+      <c r="L46" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M46" s="30">
+      <c r="M46" s="92">
         <v>6</v>
       </c>
-      <c r="N46" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O46" s="34">
-        <v>0.49409999999999998</v>
-      </c>
-      <c r="P46" s="34">
+      <c r="N46" s="93"/>
+      <c r="O46" s="94"/>
+      <c r="P46" s="94">
         <f t="shared" si="2"/>
-        <v>2.9645999999999999</v>
-      </c>
-      <c r="Q46" s="34"/>
-      <c r="R46" s="34"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="95"/>
+      <c r="R46" s="94"/>
     </row>
     <row r="47" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
@@ -4374,103 +4371,105 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="88" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="89" t="s">
-        <v>90</v>
-      </c>
-      <c r="E47" s="88" t="s">
-        <v>123</v>
-      </c>
-      <c r="F47" s="89" t="s">
-        <v>154</v>
-      </c>
-      <c r="G47" s="96" t="s">
-        <v>215</v>
-      </c>
-      <c r="H47" s="109" t="s">
-        <v>180</v>
-      </c>
-      <c r="I47" s="90" t="s">
-        <v>272</v>
-      </c>
-      <c r="J47" s="96" t="s">
-        <v>216</v>
-      </c>
-      <c r="K47" s="91">
+      <c r="C47" s="80" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="81" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="80" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="G47" s="82" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" s="104" t="s">
+        <v>167</v>
+      </c>
+      <c r="I47" s="81" t="s">
+        <v>245</v>
+      </c>
+      <c r="J47" s="82" t="s">
+        <v>201</v>
+      </c>
+      <c r="K47" s="83">
         <v>1</v>
       </c>
-      <c r="L47" s="92">
+      <c r="L47" s="84">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M47" s="92">
+      <c r="M47" s="84">
         <v>6</v>
       </c>
-      <c r="N47" s="93"/>
-      <c r="O47" s="94"/>
-      <c r="P47" s="94">
+      <c r="N47" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="O47" s="86">
+        <v>12.0892</v>
+      </c>
+      <c r="P47" s="86">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="95"/>
-      <c r="R47" s="94"/>
-    </row>
-    <row r="48" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+        <v>72.535200000000003</v>
+      </c>
+      <c r="Q47" s="87" t="s">
+        <v>275</v>
+      </c>
+      <c r="R47" s="86"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="78">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="81" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="81" t="s">
-        <v>155</v>
-      </c>
-      <c r="G48" s="82" t="s">
-        <v>215</v>
-      </c>
-      <c r="H48" s="112" t="s">
-        <v>181</v>
-      </c>
-      <c r="I48" s="81" t="s">
-        <v>262</v>
-      </c>
-      <c r="J48" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="K48" s="83">
+      <c r="C48" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="89" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="88" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48" s="89" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="96" t="s">
+        <v>200</v>
+      </c>
+      <c r="H48" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="I48" s="90" t="s">
+        <v>200</v>
+      </c>
+      <c r="J48" s="96" t="s">
+        <v>201</v>
+      </c>
+      <c r="K48" s="91">
         <v>1</v>
       </c>
-      <c r="L48" s="84">
+      <c r="L48" s="92">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M48" s="84">
+      <c r="M48" s="92">
         <v>6</v>
       </c>
-      <c r="N48" s="85" t="s">
-        <v>224</v>
-      </c>
-      <c r="O48" s="86">
-        <v>12.0892</v>
-      </c>
-      <c r="P48" s="86">
+      <c r="N48" s="93"/>
+      <c r="O48" s="94"/>
+      <c r="P48" s="94">
         <f t="shared" si="2"/>
-        <v>72.535200000000003</v>
-      </c>
-      <c r="Q48" s="87" t="s">
-        <v>292</v>
-      </c>
-      <c r="R48" s="86"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="95" t="s">
+        <v>277</v>
+      </c>
+      <c r="R48" s="94"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
@@ -4478,103 +4477,105 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="88" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="E49" s="88" t="s">
-        <v>125</v>
-      </c>
-      <c r="F49" s="89" t="s">
-        <v>156</v>
-      </c>
-      <c r="G49" s="96" t="s">
-        <v>215</v>
-      </c>
-      <c r="H49" s="109" t="s">
-        <v>182</v>
-      </c>
-      <c r="I49" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J49" s="96" t="s">
-        <v>216</v>
-      </c>
-      <c r="K49" s="91">
+      <c r="C49" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="F49" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H49" s="100" t="s">
+        <v>169</v>
+      </c>
+      <c r="I49" s="62" t="s">
+        <v>246</v>
+      </c>
+      <c r="J49" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="K49" s="56">
         <v>1</v>
       </c>
-      <c r="L49" s="92">
+      <c r="L49" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M49" s="92">
+      <c r="M49" s="30">
         <v>6</v>
       </c>
-      <c r="N49" s="93"/>
-      <c r="O49" s="94"/>
-      <c r="P49" s="94">
+      <c r="N49" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O49" s="34">
+        <v>2.851</v>
+      </c>
+      <c r="P49" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="95" t="s">
-        <v>294</v>
-      </c>
-      <c r="R49" s="94"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+        <v>17.106000000000002</v>
+      </c>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="34"/>
+    </row>
+    <row r="50" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="78">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="62" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="F50" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="G50" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H50" s="108" t="s">
-        <v>183</v>
-      </c>
-      <c r="I50" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="J50" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="K50" s="56">
+      <c r="C50" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="G50" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H50" s="99" t="s">
+        <v>170</v>
+      </c>
+      <c r="I50" s="61" t="s">
+        <v>247</v>
+      </c>
+      <c r="J50" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="K50" s="55">
         <v>1</v>
       </c>
-      <c r="L50" s="30">
+      <c r="L50" s="31">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M50" s="30">
+      <c r="M50" s="31">
         <v>6</v>
       </c>
-      <c r="N50" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O50" s="34">
-        <v>2.851</v>
-      </c>
-      <c r="P50" s="34">
+      <c r="N50" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O50" s="35">
+        <v>4.3278999999999996</v>
+      </c>
+      <c r="P50" s="35">
         <f t="shared" si="2"/>
-        <v>17.106000000000002</v>
-      </c>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
+        <v>25.967399999999998</v>
+      </c>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
     </row>
     <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
@@ -4582,52 +4583,52 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="E51" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F51" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="G51" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H51" s="107" t="s">
-        <v>184</v>
-      </c>
-      <c r="I51" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="J51" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K51" s="55">
+      <c r="C51" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H51" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="I51" s="62" t="s">
+        <v>248</v>
+      </c>
+      <c r="J51" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="K51" s="56">
         <v>1</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M51" s="31">
-        <v>6</v>
-      </c>
-      <c r="N51" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O51" s="35">
-        <v>4.3278999999999996</v>
-      </c>
-      <c r="P51" s="35">
+      <c r="M51" s="30">
+        <v>10</v>
+      </c>
+      <c r="N51" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O51" s="34">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="P51" s="34">
         <f t="shared" si="2"/>
-        <v>25.967399999999998</v>
-      </c>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="35"/>
+        <v>0.20400000000000001</v>
+      </c>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="34"/>
     </row>
     <row r="52" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
@@ -4635,52 +4636,52 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="E52" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="62" t="s">
-        <v>159</v>
-      </c>
-      <c r="G52" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H52" s="108" t="s">
-        <v>185</v>
-      </c>
-      <c r="I52" s="62" t="s">
-        <v>265</v>
-      </c>
-      <c r="J52" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="K52" s="56">
-        <v>1</v>
-      </c>
-      <c r="L52" s="30">
+      <c r="C52" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="F52" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="G52" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H52" s="99" t="s">
+        <v>172</v>
+      </c>
+      <c r="I52" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="J52" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K52" s="55">
+        <v>2</v>
+      </c>
+      <c r="L52" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M52" s="30">
         <v>10</v>
       </c>
-      <c r="N52" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O52" s="34">
-        <v>2.0400000000000001E-2</v>
-      </c>
-      <c r="P52" s="34">
+      <c r="M52" s="31">
+        <v>11</v>
+      </c>
+      <c r="N52" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O52" s="35">
+        <v>0.27650000000000002</v>
+      </c>
+      <c r="P52" s="35">
         <f t="shared" si="2"/>
-        <v>0.20400000000000001</v>
-      </c>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
+        <v>3.0415000000000001</v>
+      </c>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
     </row>
     <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
@@ -4688,266 +4689,212 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="D53" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="E53" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="F53" s="61" t="s">
-        <v>129</v>
-      </c>
-      <c r="G53" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="H53" s="107" t="s">
-        <v>186</v>
-      </c>
-      <c r="I53" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="J53" s="52" t="s">
-        <v>211</v>
-      </c>
-      <c r="K53" s="55">
-        <v>2</v>
-      </c>
-      <c r="L53" s="31">
+      <c r="C53" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="H53" s="100" t="s">
+        <v>172</v>
+      </c>
+      <c r="I53" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="J53" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="K53" s="56">
+        <v>1</v>
+      </c>
+      <c r="L53" s="30">
         <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M53" s="30">
         <v>10</v>
       </c>
-      <c r="M53" s="31">
-        <v>11</v>
-      </c>
-      <c r="N53" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O53" s="35">
-        <v>0.27650000000000002</v>
-      </c>
-      <c r="P53" s="35">
+      <c r="N53" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="O53" s="34">
+        <v>9.7100000000000006E-2</v>
+      </c>
+      <c r="P53" s="34">
         <f t="shared" si="2"/>
-        <v>3.0415000000000001</v>
-      </c>
-      <c r="Q53" s="35"/>
-      <c r="R53" s="35"/>
-    </row>
-    <row r="54" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+        <v>0.97100000000000009</v>
+      </c>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+    </row>
+    <row r="54" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="78">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="D54" s="62" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="F54" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="G54" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H54" s="108" t="s">
-        <v>186</v>
-      </c>
-      <c r="I54" s="62" t="s">
-        <v>267</v>
-      </c>
-      <c r="J54" s="53" t="s">
-        <v>212</v>
-      </c>
-      <c r="K54" s="56">
+      <c r="C54" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="110" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54" s="107" t="s">
+        <v>200</v>
+      </c>
+      <c r="H54" s="105" t="s">
+        <v>173</v>
+      </c>
+      <c r="I54" s="64" t="s">
+        <v>251</v>
+      </c>
+      <c r="J54" s="110" t="s">
+        <v>198</v>
+      </c>
+      <c r="K54" s="57">
         <v>1</v>
       </c>
-      <c r="L54" s="30">
+      <c r="L54" s="45">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M54" s="30">
+      <c r="M54" s="45">
         <v>10</v>
       </c>
-      <c r="N54" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="O54" s="34">
-        <v>9.7100000000000006E-2</v>
-      </c>
-      <c r="P54" s="34">
-        <f t="shared" si="2"/>
-        <v>0.97100000000000009</v>
-      </c>
-      <c r="Q54" s="34"/>
-      <c r="R54" s="34"/>
-    </row>
-    <row r="55" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="78">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="C55" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="64" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55" s="118" t="s">
-        <v>214</v>
-      </c>
-      <c r="F55" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="G55" s="115" t="s">
-        <v>215</v>
-      </c>
-      <c r="H55" s="113" t="s">
-        <v>187</v>
-      </c>
-      <c r="I55" s="64" t="s">
-        <v>268</v>
-      </c>
-      <c r="J55" s="68" t="s">
-        <v>213</v>
-      </c>
-      <c r="K55" s="57">
-        <v>1</v>
-      </c>
-      <c r="L55" s="45">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M55" s="45">
-        <v>10</v>
-      </c>
-      <c r="N55" s="73" t="s">
-        <v>224</v>
-      </c>
-      <c r="O55" s="46">
+      <c r="N54" s="73" t="s">
+        <v>209</v>
+      </c>
+      <c r="O54" s="46">
         <v>0.13439999999999999</v>
       </c>
-      <c r="P55" s="46">
+      <c r="P54" s="46">
         <f t="shared" si="2"/>
         <v>1.3439999999999999</v>
       </c>
-      <c r="Q55" s="46"/>
-      <c r="R55" s="46"/>
+      <c r="Q54" s="46"/>
+      <c r="R54" s="46"/>
+    </row>
+    <row r="55" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="66"/>
+      <c r="I55" s="66"/>
+      <c r="J55" s="66"/>
+      <c r="K55" s="66"/>
+      <c r="L55" s="66"/>
+      <c r="M55" s="115" t="s">
+        <v>260</v>
+      </c>
+      <c r="N55" s="116"/>
+      <c r="O55" s="116"/>
+      <c r="P55" s="75">
+        <f>SUM(P10:P54)</f>
+        <v>155.34110000000001</v>
+      </c>
+      <c r="Q55" s="66"/>
+      <c r="R55" s="67"/>
     </row>
     <row r="56" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="49"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
-      <c r="J56" s="66"/>
-      <c r="K56" s="66"/>
-      <c r="L56" s="66"/>
-      <c r="M56" s="101" t="s">
-        <v>277</v>
-      </c>
-      <c r="N56" s="102"/>
-      <c r="O56" s="102"/>
-      <c r="P56" s="75">
-        <f>SUM(P10:P55)</f>
-        <v>156.01360000000003</v>
-      </c>
-      <c r="Q56" s="66"/>
-      <c r="R56" s="67"/>
-    </row>
-    <row r="57" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="8" t="s">
+      <c r="B56" s="24"/>
+      <c r="C56" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
-      <c r="J57" s="43"/>
-      <c r="K57" s="43"/>
-      <c r="L57" s="43"/>
-      <c r="M57" s="101" t="s">
-        <v>278</v>
-      </c>
-      <c r="N57" s="102"/>
-      <c r="O57" s="102"/>
-      <c r="P57" s="74">
-        <f>P56/5</f>
-        <v>31.202720000000006</v>
-      </c>
-      <c r="Q57" s="43"/>
-      <c r="R57" s="44"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+      <c r="L56" s="43"/>
+      <c r="M56" s="115" t="s">
+        <v>261</v>
+      </c>
+      <c r="N56" s="116"/>
+      <c r="O56" s="116"/>
+      <c r="P56" s="74">
+        <f>P55/5</f>
+        <v>31.068220000000004</v>
+      </c>
+      <c r="Q56" s="43"/>
+      <c r="R56" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="R3:R8"/>
     <mergeCell ref="J2:R2"/>
+    <mergeCell ref="M55:O55"/>
     <mergeCell ref="M56:O56"/>
-    <mergeCell ref="M57:O57"/>
     <mergeCell ref="J1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N10" r:id="rId1" xr:uid="{89FE49F2-489B-4F8E-8442-F4F08D2A71B9}"/>
-    <hyperlink ref="N11" r:id="rId2" xr:uid="{B2C94EB8-361E-4059-912A-7E08189FF588}"/>
-    <hyperlink ref="N12" r:id="rId3" xr:uid="{C19BE0B1-F1F1-4F20-B4BD-E9C636ECF5F4}"/>
-    <hyperlink ref="N14" r:id="rId4" xr:uid="{7F307109-CE66-4E56-B927-F44D4A7D1544}"/>
-    <hyperlink ref="N13" r:id="rId5" xr:uid="{452140BD-B707-4DD6-97FD-06A0408D0F5E}"/>
-    <hyperlink ref="N15" r:id="rId6" xr:uid="{567837A6-FAC1-4EE4-8093-25DE77AB4C76}"/>
-    <hyperlink ref="N16" r:id="rId7" xr:uid="{84DDAAD3-0D88-427C-B37F-EF4F7D64C3F9}"/>
-    <hyperlink ref="N17" r:id="rId8" xr:uid="{0F02C980-61A3-4E84-B81B-D6711E4DA791}"/>
-    <hyperlink ref="N18" r:id="rId9" xr:uid="{1F51A281-7903-4DE5-9D43-C8D611F3E5B3}"/>
-    <hyperlink ref="N19" r:id="rId10" xr:uid="{F9BCC43B-5974-4F21-BB56-696E568D40F2}"/>
-    <hyperlink ref="N20" r:id="rId11" xr:uid="{71BDBDEC-A643-4EE2-AB8B-77BCE9EFCD5F}"/>
-    <hyperlink ref="N21" r:id="rId12" xr:uid="{66E014D8-15DF-496D-B3EF-4C478897BEE9}"/>
-    <hyperlink ref="N22" r:id="rId13" xr:uid="{977C37EA-9C73-4C4C-B8BA-458124D4F10B}"/>
-    <hyperlink ref="N24" r:id="rId14" xr:uid="{FEE6FFE2-6B3E-4EE5-9854-876785A32929}"/>
-    <hyperlink ref="N27" r:id="rId15" xr:uid="{7524F555-50E1-47E0-AF8E-5BC45B838FFE}"/>
-    <hyperlink ref="N28" r:id="rId16" xr:uid="{E0EBA58F-E359-4BCB-A2C9-9C49D150A629}"/>
-    <hyperlink ref="N29" r:id="rId17" xr:uid="{30630BC0-7DB5-4073-8F22-E28F5B42FCE1}"/>
-    <hyperlink ref="N32" r:id="rId18" xr:uid="{D7F6D37C-1F7B-418B-9244-5EC422B2C736}"/>
-    <hyperlink ref="N30" r:id="rId19" xr:uid="{7EC7E3F1-93CD-45A5-BAEC-2E96006DD4BC}"/>
-    <hyperlink ref="N31" r:id="rId20" xr:uid="{DAFC4B5E-88AC-4044-8DE5-E6B95F9FA94C}"/>
-    <hyperlink ref="N33" r:id="rId21" xr:uid="{FC25DD16-B062-4971-87F3-FBBA153342C7}"/>
-    <hyperlink ref="N34" r:id="rId22" xr:uid="{BA75FE37-D1AE-4A06-A7D6-2FC24E19A57B}"/>
-    <hyperlink ref="N37" r:id="rId23" xr:uid="{F2FCE814-68EB-42CA-B801-47EACCC9D840}"/>
-    <hyperlink ref="N38" r:id="rId24" xr:uid="{B8B83BF6-E82D-4A6D-9C89-2F85CAB04646}"/>
-    <hyperlink ref="N42" r:id="rId25" xr:uid="{377F7D05-CD56-46CE-86C7-8359A58D6174}"/>
-    <hyperlink ref="N39" r:id="rId26" xr:uid="{5BC7FB0B-A7A9-4A4F-B0AF-D93D90BD0257}"/>
-    <hyperlink ref="N40" r:id="rId27" xr:uid="{42342919-596A-4C59-8816-01D385B759CB}"/>
-    <hyperlink ref="N41" r:id="rId28" xr:uid="{5D8F6C78-4114-4B09-9296-33D8E0033965}"/>
-    <hyperlink ref="N44" r:id="rId29" xr:uid="{30A94DA1-5BD4-4155-A48B-F08C168CF099}"/>
-    <hyperlink ref="N46" r:id="rId30" xr:uid="{C3F3FC15-3DA9-4B1A-84AC-5A582D205C55}"/>
-    <hyperlink ref="N48" r:id="rId31" xr:uid="{3A097DB9-C3B3-436E-8B87-273AE27C3FB3}"/>
-    <hyperlink ref="N50" r:id="rId32" xr:uid="{0763754B-803A-440F-9046-E7656CF9DB82}"/>
-    <hyperlink ref="N51" r:id="rId33" xr:uid="{4C3FCDA1-65D2-4395-9426-3E1F29BD784A}"/>
-    <hyperlink ref="N52" r:id="rId34" xr:uid="{A4B71E3E-7A98-4CCB-A3C2-8B949A858D06}"/>
-    <hyperlink ref="N53" r:id="rId35" xr:uid="{8DCBF280-B1E4-481C-8762-45E69BB689C9}"/>
-    <hyperlink ref="N54" r:id="rId36" xr:uid="{9D7C6330-6521-4E77-B082-7293A2D402F7}"/>
-    <hyperlink ref="N55" r:id="rId37" xr:uid="{60E4F958-BD03-4950-AA1A-E5483E7B8267}"/>
-    <hyperlink ref="N36" r:id="rId38" xr:uid="{019A488B-4FF7-4C4E-B4AC-B360044B8376}"/>
-    <hyperlink ref="N23" r:id="rId39" xr:uid="{83A2C1C1-8C25-4D67-A480-302431668718}"/>
-    <hyperlink ref="N25" r:id="rId40" xr:uid="{30D22A24-3F30-4E99-967B-FA4F0FA9B8E8}"/>
-    <hyperlink ref="N35" r:id="rId41" xr:uid="{E6D3A492-9D47-4832-8671-ED5B61C9ACB1}"/>
+    <hyperlink ref="N10" r:id="rId1"/>
+    <hyperlink ref="N11" r:id="rId2"/>
+    <hyperlink ref="N12" r:id="rId3"/>
+    <hyperlink ref="N14" r:id="rId4"/>
+    <hyperlink ref="N13" r:id="rId5"/>
+    <hyperlink ref="N15" r:id="rId6"/>
+    <hyperlink ref="N16" r:id="rId7"/>
+    <hyperlink ref="N18" r:id="rId8"/>
+    <hyperlink ref="N19" r:id="rId9"/>
+    <hyperlink ref="N20" r:id="rId10"/>
+    <hyperlink ref="N21" r:id="rId11"/>
+    <hyperlink ref="N22" r:id="rId12"/>
+    <hyperlink ref="N23" r:id="rId13"/>
+    <hyperlink ref="N25" r:id="rId14"/>
+    <hyperlink ref="N28" r:id="rId15"/>
+    <hyperlink ref="N29" r:id="rId16"/>
+    <hyperlink ref="N32" r:id="rId17"/>
+    <hyperlink ref="N30" r:id="rId18"/>
+    <hyperlink ref="N31" r:id="rId19"/>
+    <hyperlink ref="N33" r:id="rId20"/>
+    <hyperlink ref="N34" r:id="rId21"/>
+    <hyperlink ref="N37" r:id="rId22"/>
+    <hyperlink ref="N41" r:id="rId23"/>
+    <hyperlink ref="N38" r:id="rId24"/>
+    <hyperlink ref="N39" r:id="rId25"/>
+    <hyperlink ref="N40" r:id="rId26"/>
+    <hyperlink ref="N43" r:id="rId27"/>
+    <hyperlink ref="N45" r:id="rId28"/>
+    <hyperlink ref="N47" r:id="rId29"/>
+    <hyperlink ref="N49" r:id="rId30"/>
+    <hyperlink ref="N50" r:id="rId31"/>
+    <hyperlink ref="N51" r:id="rId32"/>
+    <hyperlink ref="N52" r:id="rId33"/>
+    <hyperlink ref="N53" r:id="rId34"/>
+    <hyperlink ref="N54" r:id="rId35"/>
+    <hyperlink ref="N36" r:id="rId36"/>
+    <hyperlink ref="N24" r:id="rId37"/>
+    <hyperlink ref="N26" r:id="rId38"/>
+    <hyperlink ref="N35" r:id="rId39"/>
+    <hyperlink ref="N17" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
-  <drawing r:id="rId43"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
+  <drawing r:id="rId42"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68604370-23AC-4D9E-83B7-34A41F64DBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-5550" yWindow="2655" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="290">
   <si>
     <t>Component list</t>
   </si>
@@ -896,12 +897,15 @@
   </si>
   <si>
     <t>SW1, SW2</t>
+  </si>
+  <si>
+    <t>C126492</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1498,7 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1804,6 +1808,18 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1829,15 +1845,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2174,7 +2181,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2185,7 +2192,7 @@
     <col min="5" max="5" width="26.28515625" customWidth="1"/>
     <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" customWidth="1"/>
     <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -2208,8 +2215,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="118"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="122"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2225,15 +2232,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="114"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="118"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2257,7 +2264,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="111"/>
+      <c r="R3" s="115"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2281,7 +2288,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="112"/>
+      <c r="R4" s="116"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2305,7 +2312,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="112"/>
+      <c r="R5" s="116"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2325,7 +2332,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="112"/>
+      <c r="R6" s="116"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2345,7 +2352,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="112"/>
+      <c r="R7" s="116"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2365,7 +2372,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="112"/>
+      <c r="R8" s="116"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2448,7 +2455,7 @@
       <c r="I10" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="J10" s="121" t="s">
+      <c r="J10" s="113" t="s">
         <v>175</v>
       </c>
       <c r="K10" s="54">
@@ -2465,11 +2472,11 @@
         <v>209</v>
       </c>
       <c r="O10" s="42">
-        <v>7.2800000000000004E-2</v>
+        <v>6.9400000000000003E-2</v>
       </c>
       <c r="P10" s="42">
         <f>O10*M10</f>
-        <v>1.456</v>
+        <v>1.3880000000000001</v>
       </c>
       <c r="Q10" s="42"/>
       <c r="R10" s="42"/>
@@ -2518,11 +2525,11 @@
         <v>209</v>
       </c>
       <c r="O11" s="35">
-        <v>7.3000000000000001E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="P11" s="35">
         <f t="shared" ref="P11:P54" si="2">O11*M11</f>
-        <v>1.095</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
@@ -2730,11 +2737,11 @@
         <v>209</v>
       </c>
       <c r="O15" s="35">
-        <v>6.4000000000000003E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="P15" s="35">
         <f t="shared" si="2"/>
-        <v>0.32</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="Q15" s="35"/>
       <c r="R15" s="35"/>
@@ -2794,7 +2801,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="78"/>
+      <c r="B17" s="78">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="C17" s="53" t="s">
         <v>281</v>
       </c>
@@ -2813,8 +2823,8 @@
       <c r="H17" s="62" t="s">
         <v>285</v>
       </c>
-      <c r="I17" s="119">
-        <v>1</v>
+      <c r="I17" s="111" t="s">
+        <v>289</v>
       </c>
       <c r="J17" s="53" t="s">
         <v>285</v>
@@ -2829,7 +2839,7 @@
       <c r="M17" s="36">
         <v>50</v>
       </c>
-      <c r="N17" s="120" t="s">
+      <c r="N17" s="112" t="s">
         <v>209</v>
       </c>
       <c r="O17" s="37">
@@ -2991,11 +3001,11 @@
         <v>209</v>
       </c>
       <c r="O20" s="35">
-        <v>9.2899999999999996E-2</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="P20" s="35">
         <f t="shared" si="2"/>
-        <v>0.92899999999999994</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="Q20" s="35"/>
       <c r="R20" s="35"/>
@@ -3007,7 +3017,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="62" t="s">
         <v>59</v>
@@ -3044,11 +3054,11 @@
         <v>209</v>
       </c>
       <c r="O21" s="34">
-        <v>2.3371</v>
+        <v>2.3786</v>
       </c>
       <c r="P21" s="34">
         <f t="shared" si="2"/>
-        <v>14.022600000000001</v>
+        <v>14.271599999999999</v>
       </c>
       <c r="Q21" s="34"/>
       <c r="R21" s="34"/>
@@ -3113,7 +3123,7 @@
         <v>14</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D23" s="62" t="s">
         <v>61</v>
@@ -3413,11 +3423,11 @@
         <v>209</v>
       </c>
       <c r="O28" s="37">
-        <v>4.5699999999999998E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="P28" s="34">
         <f t="shared" si="2"/>
-        <v>0.45699999999999996</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="Q28" s="34"/>
       <c r="R28" s="34"/>
@@ -3888,11 +3898,11 @@
         <v>209</v>
       </c>
       <c r="O37" s="35">
-        <v>6.9999999999999999E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="P37" s="35">
         <f t="shared" si="2"/>
-        <v>6.9999999999999993E-2</v>
+        <v>0.06</v>
       </c>
       <c r="Q37" s="35"/>
       <c r="R37" s="35"/>
@@ -4203,16 +4213,16 @@
         <v>209</v>
       </c>
       <c r="O43" s="34">
-        <v>5.9900000000000002E-2</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="P43" s="34">
         <f t="shared" si="2"/>
-        <v>0.59899999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="Q43" s="34"/>
       <c r="R43" s="34"/>
     </row>
-    <row r="44" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="78">
         <f t="shared" si="0"/>
@@ -4316,7 +4326,7 @@
       <c r="Q45" s="34"/>
       <c r="R45" s="34"/>
     </row>
-    <row r="46" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="78">
         <f t="shared" si="0"/>
@@ -4409,11 +4419,11 @@
         <v>209</v>
       </c>
       <c r="O47" s="86">
-        <v>12.0892</v>
+        <v>12.0063</v>
       </c>
       <c r="P47" s="86">
         <f t="shared" si="2"/>
-        <v>72.535200000000003</v>
+        <v>72.037800000000004</v>
       </c>
       <c r="Q47" s="87" t="s">
         <v>275</v>
@@ -4492,7 +4502,7 @@
       <c r="G49" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="H49" s="100" t="s">
+      <c r="H49" s="114" t="s">
         <v>169</v>
       </c>
       <c r="I49" s="62" t="s">
@@ -4674,11 +4684,11 @@
         <v>209</v>
       </c>
       <c r="O52" s="35">
-        <v>0.27650000000000002</v>
+        <v>0.33639999999999998</v>
       </c>
       <c r="P52" s="35">
         <f t="shared" si="2"/>
-        <v>3.0415000000000001</v>
+        <v>3.7003999999999997</v>
       </c>
       <c r="Q52" s="35"/>
       <c r="R52" s="35"/>
@@ -4804,14 +4814,14 @@
       <c r="J55" s="66"/>
       <c r="K55" s="66"/>
       <c r="L55" s="66"/>
-      <c r="M55" s="115" t="s">
+      <c r="M55" s="119" t="s">
         <v>260</v>
       </c>
-      <c r="N55" s="116"/>
-      <c r="O55" s="116"/>
+      <c r="N55" s="120"/>
+      <c r="O55" s="120"/>
       <c r="P55" s="75">
         <f>SUM(P10:P54)</f>
-        <v>155.34110000000001</v>
+        <v>155.6626</v>
       </c>
       <c r="Q55" s="66"/>
       <c r="R55" s="67"/>
@@ -4831,14 +4841,14 @@
       <c r="J56" s="43"/>
       <c r="K56" s="43"/>
       <c r="L56" s="43"/>
-      <c r="M56" s="115" t="s">
+      <c r="M56" s="119" t="s">
         <v>261</v>
       </c>
-      <c r="N56" s="116"/>
-      <c r="O56" s="116"/>
+      <c r="N56" s="120"/>
+      <c r="O56" s="120"/>
       <c r="P56" s="74">
         <f>P55/5</f>
-        <v>31.068220000000004</v>
+        <v>31.13252</v>
       </c>
       <c r="Q56" s="43"/>
       <c r="R56" s="44"/>
@@ -4852,46 +4862,46 @@
     <mergeCell ref="J1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N10" r:id="rId1"/>
-    <hyperlink ref="N11" r:id="rId2"/>
-    <hyperlink ref="N12" r:id="rId3"/>
-    <hyperlink ref="N14" r:id="rId4"/>
-    <hyperlink ref="N13" r:id="rId5"/>
-    <hyperlink ref="N15" r:id="rId6"/>
-    <hyperlink ref="N16" r:id="rId7"/>
-    <hyperlink ref="N18" r:id="rId8"/>
-    <hyperlink ref="N19" r:id="rId9"/>
-    <hyperlink ref="N20" r:id="rId10"/>
-    <hyperlink ref="N21" r:id="rId11"/>
-    <hyperlink ref="N22" r:id="rId12"/>
-    <hyperlink ref="N23" r:id="rId13"/>
-    <hyperlink ref="N25" r:id="rId14"/>
-    <hyperlink ref="N28" r:id="rId15"/>
-    <hyperlink ref="N29" r:id="rId16"/>
-    <hyperlink ref="N32" r:id="rId17"/>
-    <hyperlink ref="N30" r:id="rId18"/>
-    <hyperlink ref="N31" r:id="rId19"/>
-    <hyperlink ref="N33" r:id="rId20"/>
-    <hyperlink ref="N34" r:id="rId21"/>
-    <hyperlink ref="N37" r:id="rId22"/>
-    <hyperlink ref="N41" r:id="rId23"/>
-    <hyperlink ref="N38" r:id="rId24"/>
-    <hyperlink ref="N39" r:id="rId25"/>
-    <hyperlink ref="N40" r:id="rId26"/>
-    <hyperlink ref="N43" r:id="rId27"/>
-    <hyperlink ref="N45" r:id="rId28"/>
-    <hyperlink ref="N47" r:id="rId29"/>
-    <hyperlink ref="N49" r:id="rId30"/>
-    <hyperlink ref="N50" r:id="rId31"/>
-    <hyperlink ref="N51" r:id="rId32"/>
-    <hyperlink ref="N52" r:id="rId33"/>
-    <hyperlink ref="N53" r:id="rId34"/>
-    <hyperlink ref="N54" r:id="rId35"/>
-    <hyperlink ref="N36" r:id="rId36"/>
-    <hyperlink ref="N24" r:id="rId37"/>
-    <hyperlink ref="N26" r:id="rId38"/>
-    <hyperlink ref="N35" r:id="rId39"/>
-    <hyperlink ref="N17" r:id="rId40"/>
+    <hyperlink ref="N10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N29" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N32" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N30" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N31" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N33" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N34" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N37" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N41" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N39" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N43" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N45" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N47" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N49" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N50" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N52" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N53" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N54" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N36" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N24" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N26" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N35" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N17" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>

--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68604370-23AC-4D9E-83B7-34A41F64DBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC7446-3BFB-49C3-9C45-EF973E40F11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5550" yWindow="2655" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="291">
   <si>
     <t>Component list</t>
   </si>
@@ -900,6 +900,9 @@
   </si>
   <si>
     <t>C126492</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
   </si>
 </sst>
 </file>
@@ -911,7 +914,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1075,6 +1078,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1502,7 +1514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1784,9 +1796,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1818,6 +1827,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2215,8 +2248,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="122"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="129"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2232,15 +2265,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="117"/>
-      <c r="R2" s="118"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="125"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2264,7 +2297,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="115"/>
+      <c r="R3" s="122"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2288,7 +2321,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="116"/>
+      <c r="R4" s="123"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2312,7 +2345,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="116"/>
+      <c r="R5" s="123"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2332,7 +2365,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="116"/>
+      <c r="R6" s="123"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2352,7 +2385,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="116"/>
+      <c r="R7" s="123"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2372,7 +2405,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="116"/>
+      <c r="R8" s="123"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2446,7 +2479,7 @@
       <c r="F10" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="G10" s="106" t="s">
+      <c r="G10" s="105" t="s">
         <v>200</v>
       </c>
       <c r="H10" s="98" t="s">
@@ -2455,7 +2488,7 @@
       <c r="I10" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="J10" s="113" t="s">
+      <c r="J10" s="112" t="s">
         <v>175</v>
       </c>
       <c r="K10" s="54">
@@ -2496,7 +2529,7 @@
       <c r="E11" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="108" t="s">
+      <c r="F11" s="107" t="s">
         <v>123</v>
       </c>
       <c r="G11" s="52" t="s">
@@ -2823,7 +2856,7 @@
       <c r="H17" s="62" t="s">
         <v>285</v>
       </c>
-      <c r="I17" s="111" t="s">
+      <c r="I17" s="110" t="s">
         <v>289</v>
       </c>
       <c r="J17" s="53" t="s">
@@ -2839,7 +2872,7 @@
       <c r="M17" s="36">
         <v>50</v>
       </c>
-      <c r="N17" s="112" t="s">
+      <c r="N17" s="111" t="s">
         <v>209</v>
       </c>
       <c r="O17" s="37">
@@ -3657,7 +3690,7 @@
       <c r="E33" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="F33" s="108" t="s">
+      <c r="F33" s="107" t="s">
         <v>133</v>
       </c>
       <c r="G33" s="52" t="s">
@@ -3710,7 +3743,7 @@
       <c r="E34" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="F34" s="109" t="s">
+      <c r="F34" s="108" t="s">
         <v>134</v>
       </c>
       <c r="G34" s="53" t="s">
@@ -3922,7 +3955,7 @@
       <c r="E38" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="F38" s="108" t="s">
+      <c r="F38" s="107" t="s">
         <v>136</v>
       </c>
       <c r="G38" s="52" t="s">
@@ -3975,7 +4008,7 @@
       <c r="E39" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="109" t="s">
+      <c r="F39" s="108" t="s">
         <v>137</v>
       </c>
       <c r="G39" s="53" t="s">
@@ -4028,7 +4061,7 @@
       <c r="E40" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="F40" s="108" t="s">
+      <c r="F40" s="107" t="s">
         <v>138</v>
       </c>
       <c r="G40" s="52" t="s">
@@ -4125,48 +4158,50 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="D42" s="107" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="52" t="s">
+      <c r="E42" s="114" t="s">
         <v>108</v>
       </c>
-      <c r="F42" s="63" t="s">
+      <c r="F42" s="115" t="s">
         <v>201</v>
       </c>
-      <c r="G42" s="58"/>
-      <c r="H42" s="103" t="s">
+      <c r="G42" s="116"/>
+      <c r="H42" s="117" t="s">
         <v>201</v>
       </c>
-      <c r="I42" s="63" t="s">
+      <c r="I42" s="115" t="s">
         <v>255</v>
       </c>
-      <c r="J42" s="58" t="s">
+      <c r="J42" s="116" t="s">
         <v>201</v>
       </c>
-      <c r="K42" s="55">
+      <c r="K42" s="118">
         <v>3</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="119">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="M42" s="65" t="s">
+      <c r="M42" s="120" t="s">
         <v>200</v>
       </c>
-      <c r="N42" s="65" t="s">
+      <c r="N42" s="120" t="s">
         <v>201</v>
       </c>
-      <c r="O42" s="65" t="s">
+      <c r="O42" s="120" t="s">
         <v>200</v>
       </c>
-      <c r="P42" s="65" t="s">
+      <c r="P42" s="120" t="s">
         <v>201</v>
       </c>
-      <c r="Q42" s="65"/>
+      <c r="Q42" s="121" t="s">
+        <v>290</v>
+      </c>
       <c r="R42" s="65"/>
     </row>
     <row r="43" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
@@ -4396,7 +4431,7 @@
       <c r="G47" s="82" t="s">
         <v>200</v>
       </c>
-      <c r="H47" s="104" t="s">
+      <c r="H47" s="103" t="s">
         <v>167</v>
       </c>
       <c r="I47" s="81" t="s">
@@ -4502,7 +4537,7 @@
       <c r="G49" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="H49" s="114" t="s">
+      <c r="H49" s="113" t="s">
         <v>169</v>
       </c>
       <c r="I49" s="62" t="s">
@@ -4758,22 +4793,22 @@
       <c r="D54" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="110" t="s">
+      <c r="E54" s="109" t="s">
         <v>199</v>
       </c>
       <c r="F54" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="G54" s="107" t="s">
+      <c r="G54" s="106" t="s">
         <v>200</v>
       </c>
-      <c r="H54" s="105" t="s">
+      <c r="H54" s="104" t="s">
         <v>173</v>
       </c>
       <c r="I54" s="64" t="s">
         <v>251</v>
       </c>
-      <c r="J54" s="110" t="s">
+      <c r="J54" s="109" t="s">
         <v>198</v>
       </c>
       <c r="K54" s="57">
@@ -4814,11 +4849,11 @@
       <c r="J55" s="66"/>
       <c r="K55" s="66"/>
       <c r="L55" s="66"/>
-      <c r="M55" s="119" t="s">
+      <c r="M55" s="126" t="s">
         <v>260</v>
       </c>
-      <c r="N55" s="120"/>
-      <c r="O55" s="120"/>
+      <c r="N55" s="127"/>
+      <c r="O55" s="127"/>
       <c r="P55" s="75">
         <f>SUM(P10:P54)</f>
         <v>155.6626</v>
@@ -4841,11 +4876,11 @@
       <c r="J56" s="43"/>
       <c r="K56" s="43"/>
       <c r="L56" s="43"/>
-      <c r="M56" s="119" t="s">
+      <c r="M56" s="126" t="s">
         <v>261</v>
       </c>
-      <c r="N56" s="120"/>
-      <c r="O56" s="120"/>
+      <c r="N56" s="127"/>
+      <c r="O56" s="127"/>
       <c r="P56" s="74">
         <f>P55/5</f>
         <v>31.13252</v>

--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC7446-3BFB-49C3-9C45-EF973E40F11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="293">
   <si>
     <t>Component list</t>
   </si>
@@ -800,12 +799,6 @@
     <t>--------</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewer Remarks </t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
@@ -903,18 +896,30 @@
   </si>
   <si>
     <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>Remarks (Iftikhar)</t>
+  </si>
+  <si>
+    <t>Remarks (Faizan)</t>
+  </si>
+  <si>
+    <t>Quote added from Lulu</t>
+  </si>
+  <si>
+    <t>Quote changed after receiving better rates from Lulu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1087,6 +1092,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1514,7 +1536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1878,6 +1900,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1918,7 +1961,7 @@
         <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7484868C-6378-4A14-8499-0201EF52182D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7484868C-6378-4A14-8499-0201EF52182D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2214,7 +2257,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2235,7 +2278,7 @@
     <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2440,7 +2483,7 @@
         <v>205</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M9" s="32" t="s">
         <v>206</v>
@@ -2452,13 +2495,13 @@
         <v>208</v>
       </c>
       <c r="P9" s="32" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q9" s="32" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
@@ -2521,7 +2564,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D11" s="61" t="s">
         <v>51</v>
@@ -2680,7 +2723,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D14" s="62" t="s">
         <v>54</v>
@@ -2733,7 +2776,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D15" s="61" t="s">
         <v>55</v>
@@ -2839,28 +2882,28 @@
         <v>8</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E17" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="D17" s="62" t="s">
+      <c r="F17" s="62" t="s">
         <v>282</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>283</v>
-      </c>
-      <c r="F17" s="62" t="s">
-        <v>284</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>200</v>
       </c>
       <c r="H17" s="62" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I17" s="110" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K17" s="56">
         <v>1</v>
@@ -2891,7 +2934,7 @@
         <v>9</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D18" s="61" t="s">
         <v>218</v>
@@ -3102,52 +3145,52 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="114" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="D22" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="52" t="s">
+      <c r="E22" s="114" t="s">
         <v>199</v>
       </c>
-      <c r="F22" s="61" t="s">
+      <c r="F22" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="130" t="s">
         <v>155</v>
       </c>
-      <c r="I22" s="61" t="s">
+      <c r="I22" s="107" t="s">
         <v>223</v>
       </c>
-      <c r="J22" s="58" t="s">
+      <c r="J22" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="K22" s="55">
+      <c r="K22" s="118">
         <v>1</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="119">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="119">
         <v>20</v>
       </c>
-      <c r="N22" s="70" t="s">
+      <c r="N22" s="131" t="s">
         <v>209</v>
       </c>
-      <c r="O22" s="35">
-        <v>4.8399999999999999E-2</v>
-      </c>
-      <c r="P22" s="35">
+      <c r="O22" s="132"/>
+      <c r="P22" s="132">
         <f t="shared" si="2"/>
-        <v>0.96799999999999997</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
+      <c r="R22" s="134" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="23" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -3212,22 +3255,22 @@
         <v>20</v>
       </c>
       <c r="D24" s="97" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E24" s="52" t="s">
         <v>97</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G24" s="58" t="s">
         <v>200</v>
       </c>
       <c r="H24" s="99" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I24" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J24" s="58" t="s">
         <v>200</v>
@@ -3274,7 +3317,7 @@
         <v>98</v>
       </c>
       <c r="G25" s="59" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H25" s="100" t="s">
         <v>153</v>
@@ -3318,22 +3361,22 @@
         <v>22</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E26" s="52" t="s">
         <v>99</v>
       </c>
       <c r="F26" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="H26" s="99" t="s">
+        <v>263</v>
+      </c>
+      <c r="I26" s="61" t="s">
         <v>267</v>
-      </c>
-      <c r="G26" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="H26" s="99" t="s">
-        <v>265</v>
-      </c>
-      <c r="I26" s="61" t="s">
-        <v>269</v>
       </c>
       <c r="J26" s="58" t="s">
         <v>200</v>
@@ -3380,13 +3423,13 @@
         <v>100</v>
       </c>
       <c r="G27" s="96" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H27" s="101" t="s">
         <v>152</v>
       </c>
       <c r="I27" s="90" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J27" s="88" t="s">
         <v>184</v>
@@ -3399,18 +3442,24 @@
         <v>5</v>
       </c>
       <c r="M27" s="92">
-        <v>7</v>
-      </c>
-      <c r="N27" s="93"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="94">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="N27" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="O27" s="94">
+        <v>0.48</v>
+      </c>
+      <c r="P27" s="135">
+        <f>O27*M27</f>
+        <v>2.88</v>
       </c>
       <c r="Q27" s="95" t="s">
-        <v>277</v>
-      </c>
-      <c r="R27" s="94"/>
+        <v>275</v>
+      </c>
+      <c r="R27" s="133" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -3791,22 +3840,22 @@
         <v>31</v>
       </c>
       <c r="D35" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="F35" s="61" t="s">
         <v>270</v>
-      </c>
-      <c r="E35" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="F35" s="61" t="s">
-        <v>272</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>200</v>
       </c>
       <c r="H35" s="102" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J35" s="52" t="s">
         <v>189</v>
@@ -3947,7 +3996,7 @@
         <v>29</v>
       </c>
       <c r="C38" s="52" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D38" s="61" t="s">
         <v>72</v>
@@ -4200,7 +4249,7 @@
         <v>201</v>
       </c>
       <c r="Q42" s="121" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="R42" s="65"/>
     </row>
@@ -4211,7 +4260,7 @@
         <v>34</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D43" s="62" t="s">
         <v>77</v>
@@ -4297,16 +4346,22 @@
       <c r="M44" s="92">
         <v>6</v>
       </c>
-      <c r="N44" s="93"/>
-      <c r="O44" s="94"/>
-      <c r="P44" s="94">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="N44" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="O44" s="94">
+        <v>3.94</v>
+      </c>
+      <c r="P44" s="135">
+        <f>O44*M44</f>
+        <v>23.64</v>
       </c>
       <c r="Q44" s="95" t="s">
-        <v>277</v>
-      </c>
-      <c r="R44" s="94"/>
+        <v>275</v>
+      </c>
+      <c r="R44" s="133" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
@@ -4401,14 +4456,20 @@
       <c r="M46" s="92">
         <v>6</v>
       </c>
-      <c r="N46" s="93"/>
-      <c r="O46" s="94"/>
+      <c r="N46" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="O46" s="94">
+        <v>1.575</v>
+      </c>
       <c r="P46" s="94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="Q46" s="95"/>
-      <c r="R46" s="94"/>
+      <c r="R46" s="133" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="47" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
@@ -4451,19 +4512,21 @@
         <v>6</v>
       </c>
       <c r="N47" s="85" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="O47" s="86">
-        <v>12.0063</v>
+        <v>7.88</v>
       </c>
       <c r="P47" s="86">
         <f t="shared" si="2"/>
-        <v>72.037800000000004</v>
+        <v>47.28</v>
       </c>
       <c r="Q47" s="87" t="s">
-        <v>275</v>
-      </c>
-      <c r="R47" s="86"/>
+        <v>273</v>
+      </c>
+      <c r="R47" s="136" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
@@ -4505,16 +4568,22 @@
       <c r="M48" s="92">
         <v>6</v>
       </c>
-      <c r="N48" s="93"/>
-      <c r="O48" s="94"/>
+      <c r="N48" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="O48" s="94">
+        <v>12.6</v>
+      </c>
       <c r="P48" s="94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="Q48" s="95" t="s">
-        <v>277</v>
-      </c>
-      <c r="R48" s="94"/>
+        <v>275</v>
+      </c>
+      <c r="R48" s="133" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
@@ -4850,13 +4919,13 @@
       <c r="K55" s="66"/>
       <c r="L55" s="66"/>
       <c r="M55" s="126" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N55" s="127"/>
       <c r="O55" s="127"/>
       <c r="P55" s="75">
         <f>SUM(P10:P54)</f>
-        <v>155.6626</v>
+        <v>241.5068</v>
       </c>
       <c r="Q55" s="66"/>
       <c r="R55" s="67"/>
@@ -4877,13 +4946,13 @@
       <c r="K56" s="43"/>
       <c r="L56" s="43"/>
       <c r="M56" s="126" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N56" s="127"/>
       <c r="O56" s="127"/>
       <c r="P56" s="74">
         <f>P55/5</f>
-        <v>31.13252</v>
+        <v>48.301360000000003</v>
       </c>
       <c r="Q56" s="43"/>
       <c r="R56" s="44"/>
@@ -4897,46 +4966,46 @@
     <mergeCell ref="J1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="N11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="N14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="N13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="N18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="N22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="N25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="N29" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="N32" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N30" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="N31" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N33" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="N34" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="N37" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N41" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="N38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N39" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N43" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N45" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="N47" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="N49" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="N50" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="N51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N52" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="N53" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="N54" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="N36" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="N24" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N26" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="N35" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="N17" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N10" r:id="rId1"/>
+    <hyperlink ref="N11" r:id="rId2"/>
+    <hyperlink ref="N12" r:id="rId3"/>
+    <hyperlink ref="N14" r:id="rId4"/>
+    <hyperlink ref="N13" r:id="rId5"/>
+    <hyperlink ref="N15" r:id="rId6"/>
+    <hyperlink ref="N16" r:id="rId7"/>
+    <hyperlink ref="N18" r:id="rId8"/>
+    <hyperlink ref="N19" r:id="rId9"/>
+    <hyperlink ref="N20" r:id="rId10"/>
+    <hyperlink ref="N21" r:id="rId11"/>
+    <hyperlink ref="N22" r:id="rId12"/>
+    <hyperlink ref="N23" r:id="rId13"/>
+    <hyperlink ref="N25" r:id="rId14"/>
+    <hyperlink ref="N28" r:id="rId15"/>
+    <hyperlink ref="N29" r:id="rId16"/>
+    <hyperlink ref="N32" r:id="rId17"/>
+    <hyperlink ref="N30" r:id="rId18"/>
+    <hyperlink ref="N31" r:id="rId19"/>
+    <hyperlink ref="N33" r:id="rId20"/>
+    <hyperlink ref="N34" r:id="rId21"/>
+    <hyperlink ref="N37" r:id="rId22"/>
+    <hyperlink ref="N41" r:id="rId23"/>
+    <hyperlink ref="N38" r:id="rId24"/>
+    <hyperlink ref="N39" r:id="rId25"/>
+    <hyperlink ref="N40" r:id="rId26"/>
+    <hyperlink ref="N43" r:id="rId27"/>
+    <hyperlink ref="N45" r:id="rId28"/>
+    <hyperlink ref="N47" r:id="rId29" display="LCSC"/>
+    <hyperlink ref="N49" r:id="rId30"/>
+    <hyperlink ref="N50" r:id="rId31"/>
+    <hyperlink ref="N51" r:id="rId32"/>
+    <hyperlink ref="N52" r:id="rId33"/>
+    <hyperlink ref="N53" r:id="rId34"/>
+    <hyperlink ref="N54" r:id="rId35"/>
+    <hyperlink ref="N36" r:id="rId36"/>
+    <hyperlink ref="N24" r:id="rId37"/>
+    <hyperlink ref="N26" r:id="rId38"/>
+    <hyperlink ref="N35" r:id="rId39"/>
+    <hyperlink ref="N17" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>

--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25501"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD9DA3-6257-4937-98B2-352A059D23E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="295">
   <si>
     <t>Component list</t>
   </si>
@@ -667,9 +668,6 @@
     <t>C307331</t>
   </si>
   <si>
-    <t>C2922482</t>
-  </si>
-  <si>
     <t>C412302</t>
   </si>
   <si>
@@ -908,12 +906,21 @@
   </si>
   <si>
     <t>Quote changed after receiving better rates from Lulu</t>
+  </si>
+  <si>
+    <t>GRM188R61E106MA73D</t>
+  </si>
+  <si>
+    <t>C91606</t>
+  </si>
+  <si>
+    <t>Part changed, orignal discontinued</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1538,20 +1545,20 @@
   </cellStyleXfs>
   <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1561,18 +1568,18 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1587,7 +1594,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1597,7 +1604,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1633,8 +1640,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1643,23 +1650,23 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1711,8 +1718,8 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1874,6 +1881,27 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1900,27 +1928,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1961,7 +1968,7 @@
         <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7484868C-6378-4A14-8499-0201EF52182D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7484868C-6378-4A14-8499-0201EF52182D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2257,31 +2264,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="6" max="6" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" customWidth="1"/>
     <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="2"/>
@@ -2291,10 +2298,10 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="129"/>
-    </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="135"/>
+      <c r="K1" s="136"/>
+    </row>
+    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="10" t="s">
@@ -2308,17 +2315,17 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="125"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="132"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="12" t="s">
@@ -2340,9 +2347,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="122"/>
-    </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R3" s="129"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="12" t="s">
@@ -2364,9 +2371,9 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="123"/>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R4" s="130"/>
+    </row>
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="12" t="s">
@@ -2388,9 +2395,9 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="123"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R5" s="130"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="15"/>
@@ -2408,9 +2415,9 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="123"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R6" s="130"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="17"/>
@@ -2428,9 +2435,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="123"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="130"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="38"/>
       <c r="C8" s="39"/>
@@ -2448,9 +2455,9 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="123"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="130"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="76" t="s">
         <v>4</v>
@@ -2483,7 +2490,7 @@
         <v>205</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M9" s="32" t="s">
         <v>206</v>
@@ -2495,16 +2502,16 @@
         <v>208</v>
       </c>
       <c r="P9" s="32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q9" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="R9" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="R9" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="78">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2557,14 +2564,14 @@
       <c r="Q10" s="42"/>
       <c r="R10" s="42"/>
     </row>
-    <row r="11" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="78">
         <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D11" s="61" t="s">
         <v>51</v>
@@ -2610,7 +2617,7 @@
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="78">
         <f t="shared" si="0"/>
@@ -2629,13 +2636,13 @@
         <v>124</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>200</v>
+        <v>292</v>
       </c>
       <c r="H12" s="100" t="s">
         <v>150</v>
       </c>
       <c r="I12" s="62" t="s">
-        <v>212</v>
+        <v>293</v>
       </c>
       <c r="J12" s="53" t="s">
         <v>177</v>
@@ -2648,22 +2655,24 @@
         <v>5</v>
       </c>
       <c r="M12" s="30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N12" s="71" t="s">
         <v>209</v>
       </c>
       <c r="O12" s="34">
-        <v>1.3599999999999999E-2</v>
+        <v>3.2800000000000003E-2</v>
       </c>
       <c r="P12" s="34">
         <f t="shared" si="2"/>
-        <v>0.27199999999999996</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R12" s="34" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="78">
         <f t="shared" si="0"/>
@@ -2688,7 +2697,7 @@
         <v>151</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J13" s="52" t="s">
         <v>178</v>
@@ -2716,14 +2725,14 @@
       <c r="Q13" s="35"/>
       <c r="R13" s="35"/>
     </row>
-    <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="78">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D14" s="62" t="s">
         <v>54</v>
@@ -2741,7 +2750,7 @@
         <v>152</v>
       </c>
       <c r="I14" s="62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J14" s="53" t="s">
         <v>179</v>
@@ -2769,14 +2778,14 @@
       <c r="Q14" s="34"/>
       <c r="R14" s="34"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="78">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D15" s="61" t="s">
         <v>55</v>
@@ -2794,7 +2803,7 @@
         <v>151</v>
       </c>
       <c r="I15" s="61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J15" s="52" t="s">
         <v>180</v>
@@ -2822,7 +2831,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="35"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="78">
         <f t="shared" si="0"/>
@@ -2847,7 +2856,7 @@
         <v>149</v>
       </c>
       <c r="I16" s="62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J16" s="53" t="s">
         <v>181</v>
@@ -2875,35 +2884,35 @@
       <c r="Q16" s="34"/>
       <c r="R16" s="34"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="78">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="62" t="s">
         <v>279</v>
       </c>
-      <c r="D17" s="62" t="s">
+      <c r="E17" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="F17" s="62" t="s">
         <v>281</v>
-      </c>
-      <c r="F17" s="62" t="s">
-        <v>282</v>
       </c>
       <c r="G17" s="59" t="s">
         <v>200</v>
       </c>
       <c r="H17" s="62" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I17" s="110" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K17" s="56">
         <v>1</v>
@@ -2927,23 +2936,23 @@
       <c r="Q17" s="34"/>
       <c r="R17" s="34"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="78">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D18" s="61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" s="52" t="s">
         <v>91</v>
       </c>
       <c r="F18" s="61" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>200</v>
@@ -2952,7 +2961,7 @@
         <v>151</v>
       </c>
       <c r="I18" s="61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J18" s="52" t="s">
         <v>182</v>
@@ -2980,7 +2989,7 @@
       <c r="Q18" s="35"/>
       <c r="R18" s="35"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="78">
         <f t="shared" si="0"/>
@@ -3005,7 +3014,7 @@
         <v>149</v>
       </c>
       <c r="I19" s="62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J19" s="53" t="s">
         <v>183</v>
@@ -3033,7 +3042,7 @@
       <c r="Q19" s="34"/>
       <c r="R19" s="34"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="78">
         <f t="shared" si="0"/>
@@ -3058,7 +3067,7 @@
         <v>153</v>
       </c>
       <c r="I20" s="61" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J20" s="58" t="s">
         <v>200</v>
@@ -3086,7 +3095,7 @@
       <c r="Q20" s="35"/>
       <c r="R20" s="35"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="78">
         <f t="shared" si="0"/>
@@ -3111,7 +3120,7 @@
         <v>154</v>
       </c>
       <c r="I21" s="62" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J21" s="59" t="s">
         <v>200</v>
@@ -3139,7 +3148,7 @@
       <c r="Q21" s="34"/>
       <c r="R21" s="34"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="78">
         <f t="shared" si="0"/>
@@ -3160,11 +3169,11 @@
       <c r="G22" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="H22" s="130" t="s">
+      <c r="H22" s="122" t="s">
         <v>155</v>
       </c>
       <c r="I22" s="107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J22" s="116" t="s">
         <v>200</v>
@@ -3179,20 +3188,20 @@
       <c r="M22" s="119">
         <v>20</v>
       </c>
-      <c r="N22" s="131" t="s">
+      <c r="N22" s="123" t="s">
         <v>209</v>
       </c>
-      <c r="O22" s="132"/>
-      <c r="P22" s="132">
+      <c r="O22" s="124"/>
+      <c r="P22" s="124">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="134" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="R22" s="126" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="78">
         <f t="shared" si="0"/>
@@ -3217,7 +3226,7 @@
         <v>156</v>
       </c>
       <c r="I23" s="62" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J23" s="59" t="s">
         <v>200</v>
@@ -3245,7 +3254,7 @@
       <c r="Q23" s="34"/>
       <c r="R23" s="34"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="78">
         <f t="shared" si="0"/>
@@ -3255,22 +3264,22 @@
         <v>20</v>
       </c>
       <c r="D24" s="97" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E24" s="52" t="s">
         <v>97</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G24" s="58" t="s">
         <v>200</v>
       </c>
       <c r="H24" s="99" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I24" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J24" s="58" t="s">
         <v>200</v>
@@ -3298,7 +3307,7 @@
       <c r="Q24" s="35"/>
       <c r="R24" s="35"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="78">
         <f t="shared" si="0"/>
@@ -3317,13 +3326,13 @@
         <v>98</v>
       </c>
       <c r="G25" s="59" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H25" s="100" t="s">
         <v>153</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J25" s="59" t="s">
         <v>200</v>
@@ -3351,7 +3360,7 @@
       <c r="Q25" s="34"/>
       <c r="R25" s="34"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="78">
         <f t="shared" si="0"/>
@@ -3361,22 +3370,22 @@
         <v>22</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E26" s="52" t="s">
         <v>99</v>
       </c>
       <c r="F26" s="63" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G26" s="58" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H26" s="99" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I26" s="61" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J26" s="58" t="s">
         <v>200</v>
@@ -3404,7 +3413,7 @@
       <c r="Q26" s="35"/>
       <c r="R26" s="35"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="78">
         <f t="shared" si="0"/>
@@ -3423,13 +3432,13 @@
         <v>100</v>
       </c>
       <c r="G27" s="96" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H27" s="101" t="s">
         <v>152</v>
       </c>
       <c r="I27" s="90" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J27" s="88" t="s">
         <v>184</v>
@@ -3450,18 +3459,18 @@
       <c r="O27" s="94">
         <v>0.48</v>
       </c>
-      <c r="P27" s="135">
+      <c r="P27" s="127">
         <f>O27*M27</f>
         <v>2.88</v>
       </c>
       <c r="Q27" s="95" t="s">
-        <v>275</v>
-      </c>
-      <c r="R27" s="133" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="R27" s="125" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="78">
         <f t="shared" si="0"/>
@@ -3486,7 +3495,7 @@
         <v>157</v>
       </c>
       <c r="I28" s="62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J28" s="53" t="s">
         <v>185</v>
@@ -3514,7 +3523,7 @@
       <c r="Q28" s="34"/>
       <c r="R28" s="34"/>
     </row>
-    <row r="29" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="78">
         <f t="shared" si="0"/>
@@ -3539,7 +3548,7 @@
         <v>158</v>
       </c>
       <c r="I29" s="61" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J29" s="52" t="s">
         <v>186</v>
@@ -3567,7 +3576,7 @@
       <c r="Q29" s="35"/>
       <c r="R29" s="35"/>
     </row>
-    <row r="30" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="78">
         <f t="shared" si="0"/>
@@ -3592,7 +3601,7 @@
         <v>149</v>
       </c>
       <c r="I30" s="62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J30" s="53" t="s">
         <v>187</v>
@@ -3620,7 +3629,7 @@
       <c r="Q30" s="34"/>
       <c r="R30" s="34"/>
     </row>
-    <row r="31" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="78">
         <f t="shared" si="0"/>
@@ -3645,7 +3654,7 @@
         <v>149</v>
       </c>
       <c r="I31" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J31" s="58" t="s">
         <v>201</v>
@@ -3673,7 +3682,7 @@
       <c r="Q31" s="35"/>
       <c r="R31" s="35"/>
     </row>
-    <row r="32" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="78">
         <f t="shared" si="0"/>
@@ -3696,7 +3705,7 @@
         <v>159</v>
       </c>
       <c r="I32" s="62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J32" s="53" t="s">
         <v>188</v>
@@ -3724,7 +3733,7 @@
       <c r="Q32" s="34"/>
       <c r="R32" s="34"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="78">
         <f t="shared" si="0"/>
@@ -3743,13 +3752,13 @@
         <v>133</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H33" s="99" t="s">
         <v>160</v>
       </c>
       <c r="I33" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J33" s="58" t="s">
         <v>201</v>
@@ -3777,7 +3786,7 @@
       <c r="Q33" s="35"/>
       <c r="R33" s="35"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="78">
         <f t="shared" si="0"/>
@@ -3796,13 +3805,13 @@
         <v>134</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H34" s="100" t="s">
         <v>160</v>
       </c>
       <c r="I34" s="62" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J34" s="59" t="s">
         <v>201</v>
@@ -3830,7 +3839,7 @@
       <c r="Q34" s="34"/>
       <c r="R34" s="34"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="78">
         <f t="shared" si="0"/>
@@ -3840,22 +3849,22 @@
         <v>31</v>
       </c>
       <c r="D35" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="E35" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="E35" s="52" t="s">
+      <c r="F35" s="61" t="s">
         <v>269</v>
-      </c>
-      <c r="F35" s="61" t="s">
-        <v>270</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>200</v>
       </c>
       <c r="H35" s="102" t="s">
+        <v>270</v>
+      </c>
+      <c r="I35" s="61" t="s">
         <v>271</v>
-      </c>
-      <c r="I35" s="61" t="s">
-        <v>272</v>
       </c>
       <c r="J35" s="52" t="s">
         <v>189</v>
@@ -3883,7 +3892,7 @@
       <c r="Q35" s="35"/>
       <c r="R35" s="35"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="78">
         <f t="shared" si="0"/>
@@ -3893,13 +3902,13 @@
         <v>32</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E36" s="53" t="s">
         <v>107</v>
       </c>
       <c r="F36" s="62" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G36" s="59" t="s">
         <v>200</v>
@@ -3908,7 +3917,7 @@
         <v>151</v>
       </c>
       <c r="I36" s="62" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J36" s="53" t="s">
         <v>190</v>
@@ -3936,7 +3945,7 @@
       <c r="Q36" s="34"/>
       <c r="R36" s="34"/>
     </row>
-    <row r="37" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="78">
         <f t="shared" si="0"/>
@@ -3961,7 +3970,7 @@
         <v>151</v>
       </c>
       <c r="I37" s="61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J37" s="52" t="s">
         <v>191</v>
@@ -3989,14 +3998,14 @@
       <c r="Q37" s="35"/>
       <c r="R37" s="35"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="78">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D38" s="61" t="s">
         <v>72</v>
@@ -4008,13 +4017,13 @@
         <v>136</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H38" s="99" t="s">
         <v>161</v>
       </c>
       <c r="I38" s="61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J38" s="52" t="s">
         <v>192</v>
@@ -4042,7 +4051,7 @@
       <c r="Q38" s="35"/>
       <c r="R38" s="35"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="78">
         <f t="shared" si="0"/>
@@ -4061,13 +4070,13 @@
         <v>137</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H39" s="100" t="s">
         <v>161</v>
       </c>
       <c r="I39" s="62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J39" s="53" t="s">
         <v>193</v>
@@ -4095,7 +4104,7 @@
       <c r="Q39" s="34"/>
       <c r="R39" s="34"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="78">
         <f t="shared" si="0"/>
@@ -4114,13 +4123,13 @@
         <v>138</v>
       </c>
       <c r="G40" s="52" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H40" s="99" t="s">
         <v>162</v>
       </c>
       <c r="I40" s="61" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J40" s="52" t="s">
         <v>194</v>
@@ -4148,7 +4157,7 @@
       <c r="Q40" s="35"/>
       <c r="R40" s="35"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="78">
         <f t="shared" si="0"/>
@@ -4173,7 +4182,7 @@
         <v>151</v>
       </c>
       <c r="I41" s="62" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J41" s="53" t="s">
         <v>195</v>
@@ -4201,7 +4210,7 @@
       <c r="Q41" s="34"/>
       <c r="R41" s="34"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="78">
         <f t="shared" si="0"/>
@@ -4224,7 +4233,7 @@
         <v>201</v>
       </c>
       <c r="I42" s="115" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J42" s="116" t="s">
         <v>201</v>
@@ -4249,18 +4258,18 @@
         <v>201</v>
       </c>
       <c r="Q42" s="121" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R42" s="65"/>
     </row>
-    <row r="43" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="78">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D43" s="62" t="s">
         <v>77</v>
@@ -4278,7 +4287,7 @@
         <v>163</v>
       </c>
       <c r="I43" s="62" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J43" s="59" t="s">
         <v>201</v>
@@ -4306,7 +4315,7 @@
       <c r="Q43" s="34"/>
       <c r="R43" s="34"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="78">
         <f t="shared" si="0"/>
@@ -4325,13 +4334,13 @@
         <v>140</v>
       </c>
       <c r="G44" s="96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H44" s="101" t="s">
         <v>164</v>
       </c>
       <c r="I44" s="90" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J44" s="96" t="s">
         <v>201</v>
@@ -4352,18 +4361,18 @@
       <c r="O44" s="94">
         <v>3.94</v>
       </c>
-      <c r="P44" s="135">
+      <c r="P44" s="127">
         <f>O44*M44</f>
         <v>23.64</v>
       </c>
       <c r="Q44" s="95" t="s">
-        <v>275</v>
-      </c>
-      <c r="R44" s="133" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="R44" s="125" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="78">
         <f t="shared" si="0"/>
@@ -4388,7 +4397,7 @@
         <v>165</v>
       </c>
       <c r="I45" s="62" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J45" s="59" t="s">
         <v>201</v>
@@ -4416,7 +4425,7 @@
       <c r="Q45" s="34"/>
       <c r="R45" s="34"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="78">
         <f t="shared" si="0"/>
@@ -4441,7 +4450,7 @@
         <v>166</v>
       </c>
       <c r="I46" s="90" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J46" s="96" t="s">
         <v>201</v>
@@ -4467,11 +4476,11 @@
         <v>9.4499999999999993</v>
       </c>
       <c r="Q46" s="95"/>
-      <c r="R46" s="133" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="R46" s="125" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="78">
         <f t="shared" si="0"/>
@@ -4496,7 +4505,7 @@
         <v>167</v>
       </c>
       <c r="I47" s="81" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J47" s="82" t="s">
         <v>201</v>
@@ -4522,13 +4531,13 @@
         <v>47.28</v>
       </c>
       <c r="Q47" s="87" t="s">
-        <v>273</v>
-      </c>
-      <c r="R47" s="136" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="R47" s="128" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="78">
         <f t="shared" si="0"/>
@@ -4579,13 +4588,13 @@
         <v>75.599999999999994</v>
       </c>
       <c r="Q48" s="95" t="s">
-        <v>275</v>
-      </c>
-      <c r="R48" s="133" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="R48" s="125" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="78">
         <f t="shared" si="0"/>
@@ -4610,7 +4619,7 @@
         <v>169</v>
       </c>
       <c r="I49" s="62" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J49" s="59" t="s">
         <v>201</v>
@@ -4638,7 +4647,7 @@
       <c r="Q49" s="34"/>
       <c r="R49" s="34"/>
     </row>
-    <row r="50" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="78">
         <f t="shared" si="0"/>
@@ -4663,7 +4672,7 @@
         <v>170</v>
       </c>
       <c r="I50" s="61" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J50" s="58" t="s">
         <v>201</v>
@@ -4691,7 +4700,7 @@
       <c r="Q50" s="35"/>
       <c r="R50" s="35"/>
     </row>
-    <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="78">
         <f t="shared" si="0"/>
@@ -4716,7 +4725,7 @@
         <v>171</v>
       </c>
       <c r="I51" s="62" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J51" s="59" t="s">
         <v>201</v>
@@ -4744,7 +4753,7 @@
       <c r="Q51" s="34"/>
       <c r="R51" s="34"/>
     </row>
-    <row r="52" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="78">
         <f t="shared" si="0"/>
@@ -4769,7 +4778,7 @@
         <v>172</v>
       </c>
       <c r="I52" s="61" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J52" s="52" t="s">
         <v>196</v>
@@ -4797,7 +4806,7 @@
       <c r="Q52" s="35"/>
       <c r="R52" s="35"/>
     </row>
-    <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="78">
         <f t="shared" si="0"/>
@@ -4822,7 +4831,7 @@
         <v>172</v>
       </c>
       <c r="I53" s="62" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J53" s="53" t="s">
         <v>197</v>
@@ -4850,7 +4859,7 @@
       <c r="Q53" s="34"/>
       <c r="R53" s="34"/>
     </row>
-    <row r="54" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="78">
         <f t="shared" si="0"/>
@@ -4875,7 +4884,7 @@
         <v>173</v>
       </c>
       <c r="I54" s="64" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J54" s="109" t="s">
         <v>198</v>
@@ -4903,7 +4912,7 @@
       <c r="Q54" s="46"/>
       <c r="R54" s="46"/>
     </row>
-    <row r="55" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="47"/>
       <c r="C55" s="48" t="s">
@@ -4918,19 +4927,19 @@
       <c r="J55" s="66"/>
       <c r="K55" s="66"/>
       <c r="L55" s="66"/>
-      <c r="M55" s="126" t="s">
-        <v>258</v>
-      </c>
-      <c r="N55" s="127"/>
-      <c r="O55" s="127"/>
+      <c r="M55" s="133" t="s">
+        <v>257</v>
+      </c>
+      <c r="N55" s="134"/>
+      <c r="O55" s="134"/>
       <c r="P55" s="75">
         <f>SUM(P10:P54)</f>
-        <v>241.5068</v>
+        <v>241.56279999999998</v>
       </c>
       <c r="Q55" s="66"/>
       <c r="R55" s="67"/>
     </row>
-    <row r="56" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="24"/>
       <c r="C56" s="8" t="s">
@@ -4945,14 +4954,14 @@
       <c r="J56" s="43"/>
       <c r="K56" s="43"/>
       <c r="L56" s="43"/>
-      <c r="M56" s="126" t="s">
-        <v>259</v>
-      </c>
-      <c r="N56" s="127"/>
-      <c r="O56" s="127"/>
+      <c r="M56" s="133" t="s">
+        <v>258</v>
+      </c>
+      <c r="N56" s="134"/>
+      <c r="O56" s="134"/>
       <c r="P56" s="74">
         <f>P55/5</f>
-        <v>48.301360000000003</v>
+        <v>48.312559999999998</v>
       </c>
       <c r="Q56" s="43"/>
       <c r="R56" s="44"/>
@@ -4966,46 +4975,46 @@
     <mergeCell ref="J1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N10" r:id="rId1"/>
-    <hyperlink ref="N11" r:id="rId2"/>
-    <hyperlink ref="N12" r:id="rId3"/>
-    <hyperlink ref="N14" r:id="rId4"/>
-    <hyperlink ref="N13" r:id="rId5"/>
-    <hyperlink ref="N15" r:id="rId6"/>
-    <hyperlink ref="N16" r:id="rId7"/>
-    <hyperlink ref="N18" r:id="rId8"/>
-    <hyperlink ref="N19" r:id="rId9"/>
-    <hyperlink ref="N20" r:id="rId10"/>
-    <hyperlink ref="N21" r:id="rId11"/>
-    <hyperlink ref="N22" r:id="rId12"/>
-    <hyperlink ref="N23" r:id="rId13"/>
-    <hyperlink ref="N25" r:id="rId14"/>
-    <hyperlink ref="N28" r:id="rId15"/>
-    <hyperlink ref="N29" r:id="rId16"/>
-    <hyperlink ref="N32" r:id="rId17"/>
-    <hyperlink ref="N30" r:id="rId18"/>
-    <hyperlink ref="N31" r:id="rId19"/>
-    <hyperlink ref="N33" r:id="rId20"/>
-    <hyperlink ref="N34" r:id="rId21"/>
-    <hyperlink ref="N37" r:id="rId22"/>
-    <hyperlink ref="N41" r:id="rId23"/>
-    <hyperlink ref="N38" r:id="rId24"/>
-    <hyperlink ref="N39" r:id="rId25"/>
-    <hyperlink ref="N40" r:id="rId26"/>
-    <hyperlink ref="N43" r:id="rId27"/>
-    <hyperlink ref="N45" r:id="rId28"/>
-    <hyperlink ref="N47" r:id="rId29" display="LCSC"/>
-    <hyperlink ref="N49" r:id="rId30"/>
-    <hyperlink ref="N50" r:id="rId31"/>
-    <hyperlink ref="N51" r:id="rId32"/>
-    <hyperlink ref="N52" r:id="rId33"/>
-    <hyperlink ref="N53" r:id="rId34"/>
-    <hyperlink ref="N54" r:id="rId35"/>
-    <hyperlink ref="N36" r:id="rId36"/>
-    <hyperlink ref="N24" r:id="rId37"/>
-    <hyperlink ref="N26" r:id="rId38"/>
-    <hyperlink ref="N35" r:id="rId39"/>
-    <hyperlink ref="N17" r:id="rId40"/>
+    <hyperlink ref="N10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N16" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N19" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N20" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N21" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N22" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N23" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N25" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N29" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N32" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N30" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N31" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N33" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N34" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N37" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N41" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N38" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N39" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N40" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N43" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N47" r:id="rId28" display="LCSC" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N49" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N50" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N51" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N52" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N53" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N54" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N24" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N26" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N35" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N17" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N12" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>

--- a/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/eSpark_BOM-Control-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD9DA3-6257-4937-98B2-352A059D23E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B24F849-96BA-4166-9238-A4B2485374F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2632,7 +2632,7 @@
       <c r="E12" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="108" t="s">
         <v>124</v>
       </c>
       <c r="G12" s="59" t="s">
